--- a/kronshtatsky/floors/floor_table.xlsx
+++ b/kronshtatsky/floors/floor_table.xlsx
@@ -9,7 +9,8 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12012" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12012" firstSheet="3" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16032" windowHeight="8232" firstSheet="4" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -17,8 +18,10 @@
     <sheet name="1-Пл" sheetId="2" r:id="rId3"/>
     <sheet name="1-пом" sheetId="3" r:id="rId4"/>
     <sheet name="2-Пл" sheetId="4" r:id="rId5"/>
-    <sheet name="Из КП" sheetId="7" r:id="rId6"/>
-    <sheet name="2-пом" sheetId="5" r:id="rId7"/>
+    <sheet name="3.1-Нал" sheetId="8" r:id="rId6"/>
+    <sheet name="3.1-Пом" sheetId="10" r:id="rId7"/>
+    <sheet name="Из КП" sheetId="7" r:id="rId8"/>
+    <sheet name="2-пом" sheetId="5" r:id="rId9"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -30,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="495">
   <si>
     <t>№ пом.</t>
   </si>
@@ -1405,6 +1408,119 @@
   </si>
   <si>
     <t>Устройство покрытия пола СКБ с затиркой и укрытием ДВП / из керамогранитной плитки до 0,2м2/шт</t>
+  </si>
+  <si>
+    <t>Устройство наливных полов СКБ / толщ. до 10 мм</t>
+  </si>
+  <si>
+    <t>Тип</t>
+  </si>
+  <si>
+    <t>Пом</t>
+  </si>
+  <si>
+    <t>Объем, м2.</t>
+  </si>
+  <si>
+    <t>1.26</t>
+  </si>
+  <si>
+    <t>2.02</t>
+  </si>
+  <si>
+    <t>2.03</t>
+  </si>
+  <si>
+    <t>2.04</t>
+  </si>
+  <si>
+    <t>2.05</t>
+  </si>
+  <si>
+    <t>2.06</t>
+  </si>
+  <si>
+    <t>2.07</t>
+  </si>
+  <si>
+    <t>2.37</t>
+  </si>
+  <si>
+    <t>2.40</t>
+  </si>
+  <si>
+    <t>2.41</t>
+  </si>
+  <si>
+    <t>2.42</t>
+  </si>
+  <si>
+    <t>2.44</t>
+  </si>
+  <si>
+    <t>2.45</t>
+  </si>
+  <si>
+    <t>2.47</t>
+  </si>
+  <si>
+    <t>2.49</t>
+  </si>
+  <si>
+    <t>2.51</t>
+  </si>
+  <si>
+    <t>2.56</t>
+  </si>
+  <si>
+    <t>3.01</t>
+  </si>
+  <si>
+    <t>3.02</t>
+  </si>
+  <si>
+    <t>3.03</t>
+  </si>
+  <si>
+    <t>3.04</t>
+  </si>
+  <si>
+    <t>3.05</t>
+  </si>
+  <si>
+    <t>3.08</t>
+  </si>
+  <si>
+    <t>3.23</t>
+  </si>
+  <si>
+    <t>3.25</t>
+  </si>
+  <si>
+    <t>3.28</t>
+  </si>
+  <si>
+    <t>3.29</t>
+  </si>
+  <si>
+    <t>3.33</t>
+  </si>
+  <si>
+    <t>3.35</t>
+  </si>
+  <si>
+    <t>3.41</t>
+  </si>
+  <si>
+    <t>Итог:</t>
+  </si>
+  <si>
+    <t>АРОР "Черновые отделочные работы" от 19.02.2026. 
+Тип П-9, П-10.</t>
+  </si>
+  <si>
+    <t>АРОР "Черновые отделочные работы" от 19.02.2026. 
+Тип П-13</t>
   </si>
 </sst>
 </file>
@@ -1415,7 +1531,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1485,17 +1601,30 @@
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <i/>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="14"/>
       <color rgb="FF800000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1612,7 +1741,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1686,18 +1815,6 @@
     <xf numFmtId="165" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1722,6 +1839,42 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1851,20 +2004,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Таблица1" displayName="Таблица1" ref="A2:D216" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
-  <autoFilter ref="A2:D216">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="П-10"/>
-        <filter val="П-11"/>
-        <filter val="П-12"/>
-        <filter val="П-13"/>
-        <filter val="П-14"/>
-        <filter val="П-15"/>
-        <filter val="П-8"/>
-        <filter val="П-9"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:D216"/>
   <tableColumns count="4">
     <tableColumn id="1" name="№ п. п." dataDxfId="3"/>
     <tableColumn id="2" name="№ пом." dataDxfId="2"/>
@@ -2159,11 +2299,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="43" t="s">
         <v>195</v>
       </c>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
       <c r="O1" s="1" t="s">
         <v>378</v>
       </c>
@@ -2194,7 +2334,7 @@
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
     </row>
-    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>15</v>
       </c>
@@ -2222,7 +2362,7 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>18</v>
       </c>
@@ -2250,7 +2390,7 @@
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
     </row>
-    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>12</v>
       </c>
@@ -2278,7 +2418,7 @@
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
     </row>
-    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>19</v>
       </c>
@@ -2306,7 +2446,7 @@
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
     </row>
-    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>20</v>
       </c>
@@ -2334,7 +2474,7 @@
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
     </row>
-    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>21</v>
       </c>
@@ -2362,7 +2502,7 @@
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
     </row>
-    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>22</v>
       </c>
@@ -2390,7 +2530,7 @@
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
     </row>
-    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>25</v>
       </c>
@@ -2418,7 +2558,7 @@
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
     </row>
-    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>1</v>
       </c>
@@ -2446,7 +2586,7 @@
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
     </row>
-    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>2</v>
       </c>
@@ -2474,7 +2614,7 @@
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
     </row>
-    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>3</v>
       </c>
@@ -2502,7 +2642,7 @@
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
     </row>
-    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>16</v>
       </c>
@@ -2530,7 +2670,7 @@
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
     </row>
-    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15" s="6">
         <v>0.13</v>
@@ -2556,7 +2696,7 @@
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
     </row>
-    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>4</v>
       </c>
@@ -2584,7 +2724,7 @@
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
     </row>
-    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>26</v>
       </c>
@@ -2612,7 +2752,7 @@
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
     </row>
-    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>27</v>
       </c>
@@ -2640,7 +2780,7 @@
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
     </row>
-    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>13</v>
       </c>
@@ -2668,7 +2808,7 @@
       <c r="P19" s="2"/>
       <c r="Q19" s="2"/>
     </row>
-    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -2696,7 +2836,7 @@
       <c r="P20" s="2"/>
       <c r="Q20" s="2"/>
     </row>
-    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>5</v>
       </c>
@@ -2724,7 +2864,7 @@
       <c r="P21" s="2"/>
       <c r="Q21" s="2"/>
     </row>
-    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>6</v>
       </c>
@@ -2752,7 +2892,7 @@
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
     </row>
-    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>7</v>
       </c>
@@ -2780,7 +2920,7 @@
       <c r="P23" s="2"/>
       <c r="Q23" s="2"/>
     </row>
-    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>8</v>
       </c>
@@ -2808,7 +2948,7 @@
       <c r="P24" s="2"/>
       <c r="Q24" s="2"/>
     </row>
-    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -2836,7 +2976,7 @@
       <c r="P25" s="2"/>
       <c r="Q25" s="2"/>
     </row>
-    <row r="26" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -2864,7 +3004,7 @@
       <c r="P26" s="2"/>
       <c r="Q26" s="2"/>
     </row>
-    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>9</v>
       </c>
@@ -2892,7 +3032,7 @@
       <c r="P27" s="2"/>
       <c r="Q27" s="2"/>
     </row>
-    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>14</v>
       </c>
@@ -2920,7 +3060,7 @@
       <c r="P28" s="2"/>
       <c r="Q28" s="2"/>
     </row>
-    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>10</v>
       </c>
@@ -2948,7 +3088,7 @@
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
     </row>
-    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>11</v>
       </c>
@@ -2976,7 +3116,7 @@
       <c r="P30" s="2"/>
       <c r="Q30" s="2"/>
     </row>
-    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>28</v>
       </c>
@@ -4807,7 +4947,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="82" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>29</v>
       </c>
@@ -5118,7 +5258,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="89" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>30</v>
       </c>
@@ -5300,7 +5440,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="93" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>31</v>
       </c>
@@ -5611,7 +5751,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="100" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>32</v>
       </c>
@@ -10904,7 +11044,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="216" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A216" s="2">
         <v>54</v>
       </c>
@@ -11810,11 +11950,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="44" t="s">
         <v>396</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="34"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="46"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
@@ -12040,6 +12180,479 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" style="22" customWidth="1"/>
+    <col min="2" max="2" width="33.44140625" style="22" customWidth="1"/>
+    <col min="3" max="3" width="35.44140625" style="22" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="22" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" style="22" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="47" t="s">
+        <v>389</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="49"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>392</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="54" x14ac:dyDescent="0.35">
+      <c r="A3" s="17">
+        <v>1</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>458</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>493</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="E3" s="20">
+        <f>'3.1-Пом'!C8</f>
+        <v>289.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="54" x14ac:dyDescent="0.35">
+      <c r="A4" s="17">
+        <v>2</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>458</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>494</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="E4" s="20">
+        <f>'3.1-Пом'!C35</f>
+        <v>1386.8000000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C35"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.21875" style="41" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" style="51" customWidth="1"/>
+    <col min="3" max="3" width="9.21875" style="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="41"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="39" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1" s="50" t="s">
+        <v>459</v>
+      </c>
+      <c r="C1" s="40" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="42" t="s">
+        <v>462</v>
+      </c>
+      <c r="B2" s="50" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="40">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="42" t="s">
+        <v>471</v>
+      </c>
+      <c r="B3" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="40">
+        <v>39.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="42" t="s">
+        <v>474</v>
+      </c>
+      <c r="B4" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="40">
+        <v>39.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="42" t="s">
+        <v>477</v>
+      </c>
+      <c r="B5" s="50" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="40">
+        <v>47.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="42" t="s">
+        <v>478</v>
+      </c>
+      <c r="B6" s="50" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="40">
+        <v>47.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="42" t="s">
+        <v>491</v>
+      </c>
+      <c r="B7" s="50" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="40">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="40"/>
+      <c r="B8" s="50" t="s">
+        <v>492</v>
+      </c>
+      <c r="C8" s="52">
+        <f>SUM(C2:C7)</f>
+        <v>289.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="39" t="s">
+        <v>460</v>
+      </c>
+      <c r="B10" s="50" t="s">
+        <v>459</v>
+      </c>
+      <c r="C10" s="40" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="42" t="s">
+        <v>463</v>
+      </c>
+      <c r="B11" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="40">
+        <v>89.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="42" t="s">
+        <v>464</v>
+      </c>
+      <c r="B12" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="40">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="42" t="s">
+        <v>465</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="40">
+        <v>64.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="42" t="s">
+        <v>466</v>
+      </c>
+      <c r="B14" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="40">
+        <v>64.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="42" t="s">
+        <v>467</v>
+      </c>
+      <c r="B15" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="40">
+        <v>64.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="42" t="s">
+        <v>468</v>
+      </c>
+      <c r="B16" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="40">
+        <v>63.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="42" t="s">
+        <v>469</v>
+      </c>
+      <c r="B17" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="40">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="42" t="s">
+        <v>470</v>
+      </c>
+      <c r="B18" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="40">
+        <v>39.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="42" t="s">
+        <v>472</v>
+      </c>
+      <c r="B19" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="40">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="42" t="s">
+        <v>473</v>
+      </c>
+      <c r="B20" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="40">
+        <v>39.25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="42" t="s">
+        <v>475</v>
+      </c>
+      <c r="B21" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="40">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="42" t="s">
+        <v>476</v>
+      </c>
+      <c r="B22" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="40">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="B23" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="40">
+        <v>63.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="42" t="s">
+        <v>480</v>
+      </c>
+      <c r="B24" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="40">
+        <v>88.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="42" t="s">
+        <v>481</v>
+      </c>
+      <c r="B25" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="40">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="42" t="s">
+        <v>482</v>
+      </c>
+      <c r="B26" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="40">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="42" t="s">
+        <v>483</v>
+      </c>
+      <c r="B27" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="40">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="42" t="s">
+        <v>484</v>
+      </c>
+      <c r="B28" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="40">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="42" t="s">
+        <v>485</v>
+      </c>
+      <c r="B29" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="40">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="42" t="s">
+        <v>486</v>
+      </c>
+      <c r="B30" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="40">
+        <v>78.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="42" t="s">
+        <v>487</v>
+      </c>
+      <c r="B31" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="40">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="42" t="s">
+        <v>488</v>
+      </c>
+      <c r="B32" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="40">
+        <v>78.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="42" t="s">
+        <v>489</v>
+      </c>
+      <c r="B33" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="40">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="42" t="s">
+        <v>490</v>
+      </c>
+      <c r="B34" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="40">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="40"/>
+      <c r="B35" s="50" t="s">
+        <v>492</v>
+      </c>
+      <c r="C35" s="52">
+        <f>SUM(C11:C34)</f>
+        <v>1386.8000000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12050,466 +12663,466 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="54" x14ac:dyDescent="0.3">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="33" t="s">
         <v>457</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="31" t="s">
         <v>445</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="31" t="s">
         <v>395</v>
       </c>
-      <c r="D1" s="36">
+      <c r="D1" s="32">
         <v>1</v>
       </c>
-      <c r="E1" s="36">
+      <c r="E1" s="32">
         <v>370.9</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="54" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="33" t="s">
         <v>446</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="31" t="s">
         <v>444</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="31" t="s">
         <v>395</v>
       </c>
-      <c r="D2" s="36">
+      <c r="D2" s="32">
         <v>1</v>
       </c>
-      <c r="E2" s="36">
+      <c r="E2" s="32">
         <v>1132.5</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="36" x14ac:dyDescent="0.3">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="38" t="s">
         <v>452</v>
       </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="39" t="s">
+      <c r="B3" s="31"/>
+      <c r="C3" s="35" t="s">
         <v>447</v>
       </c>
-      <c r="D3" s="38">
+      <c r="D3" s="34">
         <v>1.2</v>
       </c>
-      <c r="E3" s="41">
+      <c r="E3" s="37">
         <v>1359</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="72" x14ac:dyDescent="0.3">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="36" t="s">
         <v>451</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="31" t="s">
         <v>456</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="35" t="s">
         <v>395</v>
       </c>
-      <c r="D4" s="38">
+      <c r="D4" s="34">
         <v>1.2</v>
       </c>
-      <c r="E4" s="41">
+      <c r="E4" s="37">
         <v>1359</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="36" t="s">
         <v>449</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="39" t="s">
+      <c r="B5" s="31"/>
+      <c r="C5" s="35" t="s">
         <v>447</v>
       </c>
-      <c r="D5" s="38">
+      <c r="D5" s="34">
         <v>0.25</v>
       </c>
-      <c r="E5" s="41">
+      <c r="E5" s="37">
         <v>283.125</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="36" x14ac:dyDescent="0.3">
-      <c r="A6" s="40" t="s">
+      <c r="A6" s="36" t="s">
         <v>448</v>
       </c>
-      <c r="B6" s="35"/>
-      <c r="C6" s="39" t="s">
+      <c r="B6" s="31"/>
+      <c r="C6" s="35" t="s">
         <v>447</v>
       </c>
-      <c r="D6" s="38">
+      <c r="D6" s="34">
         <v>0.15</v>
       </c>
-      <c r="E6" s="38">
+      <c r="E6" s="34">
         <v>169.875</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="54" x14ac:dyDescent="0.3">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="33" t="s">
         <v>446</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="31" t="s">
         <v>443</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="C7" s="31" t="s">
         <v>395</v>
       </c>
-      <c r="D7" s="36">
+      <c r="D7" s="32">
         <v>1</v>
       </c>
-      <c r="E7" s="36">
+      <c r="E7" s="32">
         <v>31.2</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="36" x14ac:dyDescent="0.3">
-      <c r="A8" s="40" t="s">
+      <c r="A8" s="36" t="s">
         <v>448</v>
       </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="39" t="s">
+      <c r="B8" s="31"/>
+      <c r="C8" s="35" t="s">
         <v>447</v>
       </c>
-      <c r="D8" s="38">
+      <c r="D8" s="34">
         <v>0.15</v>
       </c>
-      <c r="E8" s="38">
+      <c r="E8" s="34">
         <v>4.68</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="36" t="s">
         <v>449</v>
       </c>
-      <c r="B9" s="35"/>
-      <c r="C9" s="39" t="s">
+      <c r="B9" s="31"/>
+      <c r="C9" s="35" t="s">
         <v>447</v>
       </c>
-      <c r="D9" s="38">
+      <c r="D9" s="34">
         <v>0.25</v>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="37">
         <v>7.8</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="54" x14ac:dyDescent="0.3">
-      <c r="A10" s="40" t="s">
+      <c r="A10" s="36" t="s">
         <v>451</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="31" t="s">
         <v>455</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="35" t="s">
         <v>395</v>
       </c>
-      <c r="D10" s="38">
+      <c r="D10" s="34">
         <v>1.2</v>
       </c>
-      <c r="E10" s="41">
+      <c r="E10" s="37">
         <v>37.44</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="36" x14ac:dyDescent="0.3">
-      <c r="A11" s="42" t="s">
+      <c r="A11" s="38" t="s">
         <v>452</v>
       </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="39" t="s">
+      <c r="B11" s="31"/>
+      <c r="C11" s="35" t="s">
         <v>447</v>
       </c>
-      <c r="D11" s="38">
+      <c r="D11" s="34">
         <v>1.2</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="37">
         <v>37.44</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="54" x14ac:dyDescent="0.3">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="33" t="s">
         <v>446</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="31" t="s">
         <v>442</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="31" t="s">
         <v>395</v>
       </c>
-      <c r="D12" s="36">
+      <c r="D12" s="32">
         <v>1</v>
       </c>
-      <c r="E12" s="36">
+      <c r="E12" s="32">
         <v>560.4</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="36" x14ac:dyDescent="0.3">
-      <c r="A13" s="42" t="s">
+      <c r="A13" s="38" t="s">
         <v>452</v>
       </c>
-      <c r="B13" s="35"/>
-      <c r="C13" s="39" t="s">
+      <c r="B13" s="31"/>
+      <c r="C13" s="35" t="s">
         <v>447</v>
       </c>
-      <c r="D13" s="38">
+      <c r="D13" s="34">
         <v>1.2</v>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="37">
         <v>672.48</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="54" x14ac:dyDescent="0.3">
-      <c r="A14" s="40" t="s">
+      <c r="A14" s="36" t="s">
         <v>451</v>
       </c>
-      <c r="B14" s="35" t="s">
+      <c r="B14" s="31" t="s">
         <v>454</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="35" t="s">
         <v>395</v>
       </c>
-      <c r="D14" s="38">
+      <c r="D14" s="34">
         <v>1.2</v>
       </c>
-      <c r="E14" s="41">
+      <c r="E14" s="37">
         <v>672.48</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="A15" s="40" t="s">
+      <c r="A15" s="36" t="s">
         <v>449</v>
       </c>
-      <c r="B15" s="35"/>
-      <c r="C15" s="39" t="s">
+      <c r="B15" s="31"/>
+      <c r="C15" s="35" t="s">
         <v>447</v>
       </c>
-      <c r="D15" s="38">
+      <c r="D15" s="34">
         <v>0.25</v>
       </c>
-      <c r="E15" s="41">
+      <c r="E15" s="37">
         <v>140.1</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="36" x14ac:dyDescent="0.3">
-      <c r="A16" s="40" t="s">
+      <c r="A16" s="36" t="s">
         <v>448</v>
       </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="39" t="s">
+      <c r="B16" s="31"/>
+      <c r="C16" s="35" t="s">
         <v>447</v>
       </c>
-      <c r="D16" s="38">
+      <c r="D16" s="34">
         <v>0.15</v>
       </c>
-      <c r="E16" s="38">
+      <c r="E16" s="34">
         <v>84.06</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="54" x14ac:dyDescent="0.3">
-      <c r="A17" s="37" t="s">
+      <c r="A17" s="33" t="s">
         <v>446</v>
       </c>
-      <c r="B17" s="35" t="s">
+      <c r="B17" s="31" t="s">
         <v>441</v>
       </c>
-      <c r="C17" s="35" t="s">
+      <c r="C17" s="31" t="s">
         <v>395</v>
       </c>
-      <c r="D17" s="36">
+      <c r="D17" s="32">
         <v>1</v>
       </c>
-      <c r="E17" s="36">
+      <c r="E17" s="32">
         <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="36" x14ac:dyDescent="0.3">
-      <c r="A18" s="40" t="s">
+      <c r="A18" s="36" t="s">
         <v>448</v>
       </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="39" t="s">
+      <c r="B18" s="31"/>
+      <c r="C18" s="35" t="s">
         <v>447</v>
       </c>
-      <c r="D18" s="38">
+      <c r="D18" s="34">
         <v>0.15</v>
       </c>
-      <c r="E18" s="38">
+      <c r="E18" s="34">
         <v>4.2</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="A19" s="40" t="s">
+      <c r="A19" s="36" t="s">
         <v>449</v>
       </c>
-      <c r="B19" s="35"/>
-      <c r="C19" s="39" t="s">
+      <c r="B19" s="31"/>
+      <c r="C19" s="35" t="s">
         <v>447</v>
       </c>
-      <c r="D19" s="38">
+      <c r="D19" s="34">
         <v>0.25</v>
       </c>
-      <c r="E19" s="41">
+      <c r="E19" s="37">
         <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="54" x14ac:dyDescent="0.3">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="36" t="s">
         <v>451</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="B20" s="31" t="s">
         <v>453</v>
       </c>
-      <c r="C20" s="39" t="s">
+      <c r="C20" s="35" t="s">
         <v>395</v>
       </c>
-      <c r="D20" s="38">
+      <c r="D20" s="34">
         <v>1.2</v>
       </c>
-      <c r="E20" s="41">
+      <c r="E20" s="37">
         <v>33.6</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="36" x14ac:dyDescent="0.3">
-      <c r="A21" s="42" t="s">
+      <c r="A21" s="38" t="s">
         <v>452</v>
       </c>
-      <c r="B21" s="35"/>
-      <c r="C21" s="39" t="s">
+      <c r="B21" s="31"/>
+      <c r="C21" s="35" t="s">
         <v>447</v>
       </c>
-      <c r="D21" s="38">
+      <c r="D21" s="34">
         <v>1.2</v>
       </c>
-      <c r="E21" s="41">
+      <c r="E21" s="37">
         <v>33.6</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="54" x14ac:dyDescent="0.3">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="33" t="s">
         <v>446</v>
       </c>
-      <c r="B22" s="35" t="s">
+      <c r="B22" s="31" t="s">
         <v>440</v>
       </c>
-      <c r="C22" s="35" t="s">
+      <c r="C22" s="31" t="s">
         <v>395</v>
       </c>
-      <c r="D22" s="36">
+      <c r="D22" s="32">
         <v>1</v>
       </c>
-      <c r="E22" s="36">
+      <c r="E22" s="32">
         <v>207.1</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="36" x14ac:dyDescent="0.3">
-      <c r="A23" s="42" t="s">
+      <c r="A23" s="38" t="s">
         <v>452</v>
       </c>
-      <c r="B23" s="35"/>
-      <c r="C23" s="39" t="s">
+      <c r="B23" s="31"/>
+      <c r="C23" s="35" t="s">
         <v>447</v>
       </c>
-      <c r="D23" s="38">
+      <c r="D23" s="34">
         <v>1.2</v>
       </c>
-      <c r="E23" s="41">
+      <c r="E23" s="37">
         <v>248.52</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="54" x14ac:dyDescent="0.3">
-      <c r="A24" s="40" t="s">
+      <c r="A24" s="36" t="s">
         <v>451</v>
       </c>
-      <c r="B24" s="35" t="s">
+      <c r="B24" s="31" t="s">
         <v>450</v>
       </c>
-      <c r="C24" s="39" t="s">
+      <c r="C24" s="35" t="s">
         <v>395</v>
       </c>
-      <c r="D24" s="38">
+      <c r="D24" s="34">
         <v>1.2</v>
       </c>
-      <c r="E24" s="41">
+      <c r="E24" s="37">
         <v>248.52</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="A25" s="40" t="s">
+      <c r="A25" s="36" t="s">
         <v>449</v>
       </c>
-      <c r="B25" s="35"/>
-      <c r="C25" s="39" t="s">
+      <c r="B25" s="31"/>
+      <c r="C25" s="35" t="s">
         <v>447</v>
       </c>
-      <c r="D25" s="38">
+      <c r="D25" s="34">
         <v>0.25</v>
       </c>
-      <c r="E25" s="41">
+      <c r="E25" s="37">
         <v>51.774999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="36" x14ac:dyDescent="0.3">
-      <c r="A26" s="40" t="s">
+      <c r="A26" s="36" t="s">
         <v>448</v>
       </c>
-      <c r="B26" s="35"/>
-      <c r="C26" s="39" t="s">
+      <c r="B26" s="31"/>
+      <c r="C26" s="35" t="s">
         <v>447</v>
       </c>
-      <c r="D26" s="38">
+      <c r="D26" s="34">
         <v>0.15</v>
       </c>
-      <c r="E26" s="38">
+      <c r="E26" s="34">
         <v>31.065000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="54" x14ac:dyDescent="0.3">
-      <c r="A27" s="37" t="s">
+      <c r="A27" s="33" t="s">
         <v>446</v>
       </c>
-      <c r="B27" s="35" t="s">
+      <c r="B27" s="31" t="s">
         <v>439</v>
       </c>
-      <c r="C27" s="35" t="s">
+      <c r="C27" s="31" t="s">
         <v>395</v>
       </c>
-      <c r="D27" s="36">
+      <c r="D27" s="32">
         <v>1</v>
       </c>
-      <c r="E27" s="36">
+      <c r="E27" s="32">
         <v>207.5</v>
       </c>
     </row>
     <row r="34" spans="2:2" ht="18" x14ac:dyDescent="0.3">
-      <c r="B34" s="35" t="s">
+      <c r="B34" s="31" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="35" spans="2:2" ht="18" x14ac:dyDescent="0.3">
-      <c r="B35" s="35" t="s">
+      <c r="B35" s="31" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="36" spans="2:2" ht="18" x14ac:dyDescent="0.3">
-      <c r="B36" s="35" t="s">
+      <c r="B36" s="31" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="37" spans="2:2" ht="18" x14ac:dyDescent="0.3">
-      <c r="B37" s="35" t="s">
+      <c r="B37" s="31" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="38" spans="2:2" ht="18" x14ac:dyDescent="0.3">
-      <c r="B38" s="35" t="s">
+      <c r="B38" s="31" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="39" spans="2:2" ht="18" x14ac:dyDescent="0.3">
-      <c r="B39" s="35" t="s">
+      <c r="B39" s="31" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="40" spans="2:2" ht="36" x14ac:dyDescent="0.3">
-      <c r="B40" s="35" t="s">
+      <c r="B40" s="31" t="s">
         <v>439</v>
       </c>
     </row>
@@ -12518,7 +13131,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
@@ -12530,11 +13143,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="44" t="s">
         <v>396</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="34"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="46"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">

--- a/kronshtatsky/floors/floor_table.xlsx
+++ b/kronshtatsky/floors/floor_table.xlsx
@@ -9,19 +9,20 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12012" firstSheet="3" activeTab="5"/>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16032" windowHeight="8232" firstSheet="4" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16056" windowHeight="8520" firstSheet="5" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="Тип Плиты" sheetId="6" r:id="rId2"/>
     <sheet name="1-Пл" sheetId="2" r:id="rId3"/>
-    <sheet name="1-пом" sheetId="3" r:id="rId4"/>
-    <sheet name="2-Пл" sheetId="4" r:id="rId5"/>
-    <sheet name="3.1-Нал" sheetId="8" r:id="rId6"/>
-    <sheet name="3.1-Пом" sheetId="10" r:id="rId7"/>
-    <sheet name="Из КП" sheetId="7" r:id="rId8"/>
-    <sheet name="2-пом" sheetId="5" r:id="rId9"/>
+    <sheet name="Лист3" sheetId="12" r:id="rId4"/>
+    <sheet name="1-пом" sheetId="3" r:id="rId5"/>
+    <sheet name="2-Пл" sheetId="4" r:id="rId6"/>
+    <sheet name="3.1-Нал" sheetId="8" r:id="rId7"/>
+    <sheet name="3.1-Пом" sheetId="10" r:id="rId8"/>
+    <sheet name="4.Защ_вин" sheetId="11" r:id="rId9"/>
+    <sheet name="Из КП" sheetId="7" r:id="rId10"/>
+    <sheet name="2-пом" sheetId="5" r:id="rId11"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="503">
   <si>
     <t>№ пом.</t>
   </si>
@@ -1521,17 +1522,45 @@
   <si>
     <t>АРОР "Черновые отделочные работы" от 19.02.2026. 
 Тип П-13</t>
+  </si>
+  <si>
+    <t>Площадь,
+м2.</t>
+  </si>
+  <si>
+    <t>№ 
+пом.</t>
+  </si>
+  <si>
+    <t>Защитные мероприятия по защите линолеума и виниловая плитки от повреждений (доска ДВП)</t>
+  </si>
+  <si>
+    <t>Л-7</t>
+  </si>
+  <si>
+    <t>Л-1</t>
+  </si>
+  <si>
+    <t>Л-4</t>
+  </si>
+  <si>
+    <t>л-7</t>
+  </si>
+  <si>
+    <t>л-1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="2">
+  <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.0\ _₽_-;\-* #,##0.0\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1626,8 +1655,55 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="4" tint="-0.249977111117893"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1652,8 +1728,14 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1737,11 +1819,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1847,6 +1950,13 @@
     <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1868,18 +1978,76 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Финансовый" xfId="1" builtinId="3"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="7">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2003,13 +2171,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Таблица1" displayName="Таблица1" ref="A2:D216" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
-  <autoFilter ref="A2:D216"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Таблица1" displayName="Таблица1" ref="A2:D216" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A2:D216">
+    <filterColumn colId="1">
+      <colorFilter dxfId="0" cellColor="0"/>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" name="№ п. п." dataDxfId="3"/>
-    <tableColumn id="2" name="№ пом." dataDxfId="2"/>
-    <tableColumn id="3" name="Тип пола" dataDxfId="1"/>
-    <tableColumn id="4" name="Площадь, м2." dataDxfId="0"/>
+    <tableColumn id="1" name="№ п. п." dataDxfId="4"/>
+    <tableColumn id="2" name="№ пом." dataDxfId="3"/>
+    <tableColumn id="3" name="Тип пола" dataDxfId="2"/>
+    <tableColumn id="4" name="Площадь, м2." dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2299,11 +2471,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="I1" s="43" t="s">
+      <c r="I1" s="46" t="s">
         <v>195</v>
       </c>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
       <c r="O1" s="1" t="s">
         <v>378</v>
       </c>
@@ -2334,7 +2506,7 @@
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>15</v>
       </c>
@@ -2362,7 +2534,7 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>18</v>
       </c>
@@ -2390,7 +2562,7 @@
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>12</v>
       </c>
@@ -2418,7 +2590,7 @@
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>19</v>
       </c>
@@ -2446,7 +2618,7 @@
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>20</v>
       </c>
@@ -2474,7 +2646,7 @@
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>21</v>
       </c>
@@ -2502,7 +2674,7 @@
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>22</v>
       </c>
@@ -2530,7 +2702,7 @@
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>25</v>
       </c>
@@ -2558,7 +2730,7 @@
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>1</v>
       </c>
@@ -2586,7 +2758,7 @@
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>2</v>
       </c>
@@ -2614,7 +2786,7 @@
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>3</v>
       </c>
@@ -2642,7 +2814,7 @@
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>16</v>
       </c>
@@ -2670,7 +2842,7 @@
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15" s="6">
         <v>0.13</v>
@@ -2696,7 +2868,7 @@
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>4</v>
       </c>
@@ -2724,7 +2896,7 @@
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>26</v>
       </c>
@@ -2752,7 +2924,7 @@
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>27</v>
       </c>
@@ -2780,7 +2952,7 @@
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>13</v>
       </c>
@@ -2808,7 +2980,7 @@
       <c r="P19" s="2"/>
       <c r="Q19" s="2"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -2836,7 +3008,7 @@
       <c r="P20" s="2"/>
       <c r="Q20" s="2"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>5</v>
       </c>
@@ -2864,7 +3036,7 @@
       <c r="P21" s="2"/>
       <c r="Q21" s="2"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>6</v>
       </c>
@@ -2892,7 +3064,7 @@
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>7</v>
       </c>
@@ -2920,7 +3092,7 @@
       <c r="P23" s="2"/>
       <c r="Q23" s="2"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>8</v>
       </c>
@@ -2948,7 +3120,7 @@
       <c r="P24" s="2"/>
       <c r="Q24" s="2"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -2976,7 +3148,7 @@
       <c r="P25" s="2"/>
       <c r="Q25" s="2"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -3004,7 +3176,7 @@
       <c r="P26" s="2"/>
       <c r="Q26" s="2"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>9</v>
       </c>
@@ -3032,7 +3204,7 @@
       <c r="P27" s="2"/>
       <c r="Q27" s="2"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>14</v>
       </c>
@@ -3060,7 +3232,7 @@
       <c r="P28" s="2"/>
       <c r="Q28" s="2"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>10</v>
       </c>
@@ -3088,7 +3260,7 @@
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>11</v>
       </c>
@@ -3116,7 +3288,7 @@
       <c r="P30" s="2"/>
       <c r="Q30" s="2"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>28</v>
       </c>
@@ -3141,7 +3313,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>33</v>
       </c>
@@ -3177,7 +3349,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>94</v>
       </c>
@@ -3210,7 +3382,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>34</v>
       </c>
@@ -3245,7 +3417,7 @@
       <c r="A35" s="2">
         <v>55</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35" s="53">
         <v>1.05</v>
       </c>
       <c r="C35" s="2" t="s">
@@ -3274,7 +3446,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>95</v>
       </c>
@@ -3307,7 +3479,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>35</v>
       </c>
@@ -3343,7 +3515,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>36</v>
       </c>
@@ -3383,7 +3555,7 @@
       <c r="A39" s="2">
         <v>56</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B39" s="53">
         <v>1.0900000000000001</v>
       </c>
       <c r="C39" s="2" t="s">
@@ -3416,7 +3588,7 @@
       <c r="A40" s="2">
         <v>57</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B40" s="53">
         <v>1.1000000000000001</v>
       </c>
       <c r="C40" s="2" t="s">
@@ -3449,7 +3621,7 @@
       <c r="A41" s="2">
         <v>58</v>
       </c>
-      <c r="B41" s="3">
+      <c r="B41" s="53">
         <v>1.1100000000000001</v>
       </c>
       <c r="C41" s="2" t="s">
@@ -3482,7 +3654,7 @@
       <c r="A42" s="2">
         <v>59</v>
       </c>
-      <c r="B42" s="3">
+      <c r="B42" s="53">
         <v>1.1200000000000001</v>
       </c>
       <c r="C42" s="2" t="s">
@@ -3511,7 +3683,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>96</v>
       </c>
@@ -3544,7 +3716,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>97</v>
       </c>
@@ -3577,7 +3749,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>98</v>
       </c>
@@ -3610,7 +3782,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>99</v>
       </c>
@@ -3643,7 +3815,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>37</v>
       </c>
@@ -3679,7 +3851,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>38</v>
       </c>
@@ -3719,7 +3891,7 @@
       <c r="A49" s="2">
         <v>60</v>
       </c>
-      <c r="B49" s="3">
+      <c r="B49" s="53">
         <v>1.19</v>
       </c>
       <c r="C49" s="2" t="s">
@@ -3748,7 +3920,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>61</v>
       </c>
@@ -3781,7 +3953,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>100</v>
       </c>
@@ -3814,7 +3986,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>101</v>
       </c>
@@ -3847,7 +4019,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>102</v>
       </c>
@@ -3880,7 +4052,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>62</v>
       </c>
@@ -3913,7 +4085,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>63</v>
       </c>
@@ -3946,7 +4118,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>64</v>
       </c>
@@ -3979,7 +4151,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>65</v>
       </c>
@@ -4016,7 +4188,7 @@
       <c r="A58" s="2">
         <v>66</v>
       </c>
-      <c r="B58" s="3">
+      <c r="B58" s="53">
         <v>1.28</v>
       </c>
       <c r="C58" s="2" t="s">
@@ -4049,7 +4221,7 @@
       <c r="A59" s="2">
         <v>39</v>
       </c>
-      <c r="B59" s="3">
+      <c r="B59" s="53">
         <v>1.29</v>
       </c>
       <c r="C59" s="2" t="s">
@@ -4081,7 +4253,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>67</v>
       </c>
@@ -4114,7 +4286,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>68</v>
       </c>
@@ -4147,7 +4319,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>40</v>
       </c>
@@ -4183,7 +4355,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>41</v>
       </c>
@@ -4219,7 +4391,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>42</v>
       </c>
@@ -4255,7 +4427,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>43</v>
       </c>
@@ -4291,7 +4463,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>44</v>
       </c>
@@ -4327,7 +4499,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>45</v>
       </c>
@@ -4363,7 +4535,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>46</v>
       </c>
@@ -4399,7 +4571,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>103</v>
       </c>
@@ -4432,7 +4604,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>104</v>
       </c>
@@ -4465,7 +4637,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>105</v>
       </c>
@@ -4498,7 +4670,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>106</v>
       </c>
@@ -4542,7 +4714,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>47</v>
       </c>
@@ -4589,7 +4761,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>107</v>
       </c>
@@ -4633,7 +4805,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>48</v>
       </c>
@@ -4680,7 +4852,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>69</v>
       </c>
@@ -4724,7 +4896,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>108</v>
       </c>
@@ -4768,7 +4940,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>49</v>
       </c>
@@ -4815,7 +4987,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>109</v>
       </c>
@@ -4859,7 +5031,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>110</v>
       </c>
@@ -4903,7 +5075,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>111</v>
       </c>
@@ -4947,7 +5119,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>29</v>
       </c>
@@ -4994,7 +5166,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>112</v>
       </c>
@@ -5038,7 +5210,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>113</v>
       </c>
@@ -5082,7 +5254,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>114</v>
       </c>
@@ -5126,7 +5298,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>115</v>
       </c>
@@ -5170,7 +5342,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>116</v>
       </c>
@@ -5214,7 +5386,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>70</v>
       </c>
@@ -5258,7 +5430,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>30</v>
       </c>
@@ -5305,7 +5477,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>50</v>
       </c>
@@ -5356,7 +5528,7 @@
       <c r="A91" s="2">
         <v>71</v>
       </c>
-      <c r="B91" s="3">
+      <c r="B91" s="53">
         <v>1.61</v>
       </c>
       <c r="C91" s="2" t="s">
@@ -5396,7 +5568,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>117</v>
       </c>
@@ -5440,7 +5612,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>31</v>
       </c>
@@ -5491,7 +5663,7 @@
       <c r="A94" s="2">
         <v>84</v>
       </c>
-      <c r="B94" s="3">
+      <c r="B94" s="53">
         <v>1.64</v>
       </c>
       <c r="C94" s="2" t="s">
@@ -5531,7 +5703,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>118</v>
       </c>
@@ -5575,7 +5747,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>119</v>
       </c>
@@ -5623,7 +5795,7 @@
       <c r="A97" s="2">
         <v>85</v>
       </c>
-      <c r="B97" s="3">
+      <c r="B97" s="53">
         <v>1.67</v>
       </c>
       <c r="C97" s="2" t="s">
@@ -5667,7 +5839,7 @@
       <c r="A98" s="2">
         <v>86</v>
       </c>
-      <c r="B98" s="3">
+      <c r="B98" s="53">
         <v>1.68</v>
       </c>
       <c r="C98" s="2" t="s">
@@ -5711,7 +5883,7 @@
       <c r="A99" s="2">
         <v>87</v>
       </c>
-      <c r="B99" s="3">
+      <c r="B99" s="53">
         <v>1.69</v>
       </c>
       <c r="C99" s="2" t="s">
@@ -5751,7 +5923,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>32</v>
       </c>
@@ -5798,7 +5970,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>120</v>
       </c>
@@ -5842,7 +6014,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>121</v>
       </c>
@@ -5890,7 +6062,7 @@
       <c r="A103" s="2">
         <v>88</v>
       </c>
-      <c r="B103" s="3">
+      <c r="B103" s="53">
         <v>1.73</v>
       </c>
       <c r="C103" s="2" t="s">
@@ -5934,7 +6106,7 @@
       <c r="A104" s="2">
         <v>89</v>
       </c>
-      <c r="B104" s="3">
+      <c r="B104" s="53">
         <v>1.74</v>
       </c>
       <c r="C104" s="2" t="s">
@@ -5974,7 +6146,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>122</v>
       </c>
@@ -6018,7 +6190,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
         <v>72</v>
       </c>
@@ -6066,7 +6238,7 @@
       <c r="A107" s="2">
         <v>73</v>
       </c>
-      <c r="B107" s="3">
+      <c r="B107" s="53">
         <v>1.77</v>
       </c>
       <c r="C107" s="2" t="s">
@@ -6107,7 +6279,7 @@
       </c>
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B108" s="3">
+      <c r="B108" s="53">
         <v>1.78</v>
       </c>
       <c r="C108" s="2" t="s">
@@ -6147,7 +6319,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
         <v>51</v>
       </c>
@@ -6194,7 +6366,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
         <v>52</v>
       </c>
@@ -6241,7 +6413,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
         <v>53</v>
       </c>
@@ -6288,7 +6460,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
         <v>74</v>
       </c>
@@ -6336,7 +6508,7 @@
       <c r="A113" s="2">
         <v>143</v>
       </c>
-      <c r="B113" s="3">
+      <c r="B113" s="53">
         <v>2.0099999999999998</v>
       </c>
       <c r="C113" s="2" t="s">
@@ -6383,7 +6555,7 @@
       <c r="A114" s="2">
         <v>144</v>
       </c>
-      <c r="B114" s="3">
+      <c r="B114" s="53">
         <v>2.02</v>
       </c>
       <c r="C114" s="2" t="s">
@@ -6430,7 +6602,7 @@
       <c r="A115" s="2">
         <v>145</v>
       </c>
-      <c r="B115" s="3">
+      <c r="B115" s="53">
         <v>2.0299999999999998</v>
       </c>
       <c r="C115" s="2" t="s">
@@ -6477,7 +6649,7 @@
       <c r="A116" s="2">
         <v>146</v>
       </c>
-      <c r="B116" s="3">
+      <c r="B116" s="53">
         <v>2.04</v>
       </c>
       <c r="C116" s="2" t="s">
@@ -6524,7 +6696,7 @@
       <c r="A117" s="2">
         <v>147</v>
       </c>
-      <c r="B117" s="3">
+      <c r="B117" s="53">
         <v>2.0499999999999998</v>
       </c>
       <c r="C117" s="2" t="s">
@@ -6571,7 +6743,7 @@
       <c r="A118" s="2">
         <v>148</v>
       </c>
-      <c r="B118" s="3">
+      <c r="B118" s="53">
         <v>2.06</v>
       </c>
       <c r="C118" s="2" t="s">
@@ -6618,7 +6790,7 @@
       <c r="A119" s="2">
         <v>149</v>
       </c>
-      <c r="B119" s="3">
+      <c r="B119" s="53">
         <v>2.0699999999999998</v>
       </c>
       <c r="C119" s="2" t="s">
@@ -6665,7 +6837,7 @@
       <c r="A120" s="2">
         <v>75</v>
       </c>
-      <c r="B120" s="3">
+      <c r="B120" s="53">
         <v>2.08</v>
       </c>
       <c r="C120" s="2" t="s">
@@ -6705,7 +6877,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
         <v>185</v>
       </c>
@@ -6749,7 +6921,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
         <v>186</v>
       </c>
@@ -6793,7 +6965,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
         <v>187</v>
       </c>
@@ -6841,7 +7013,7 @@
       <c r="A124" s="2">
         <v>150</v>
       </c>
-      <c r="B124" s="3">
+      <c r="B124" s="53">
         <v>2.12</v>
       </c>
       <c r="C124" s="2" t="s">
@@ -6884,7 +7056,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
         <v>188</v>
       </c>
@@ -6928,7 +7100,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
         <v>189</v>
       </c>
@@ -6976,7 +7148,7 @@
       <c r="A127" s="2">
         <v>151</v>
       </c>
-      <c r="B127" s="3">
+      <c r="B127" s="53">
         <v>2.15</v>
       </c>
       <c r="C127" s="2" t="s">
@@ -7019,7 +7191,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
         <v>190</v>
       </c>
@@ -7063,7 +7235,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
         <v>191</v>
       </c>
@@ -7107,7 +7279,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
         <v>152</v>
       </c>
@@ -7158,7 +7330,7 @@
       <c r="A131" s="2">
         <v>184</v>
       </c>
-      <c r="B131" s="3">
+      <c r="B131" s="53">
         <v>2.19</v>
       </c>
       <c r="C131" s="2" t="s">
@@ -7198,7 +7370,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
         <v>192</v>
       </c>
@@ -7246,7 +7418,7 @@
       <c r="A133" s="2">
         <v>153</v>
       </c>
-      <c r="B133" s="3">
+      <c r="B133" s="53">
         <v>2.21</v>
       </c>
       <c r="C133" s="2" t="s">
@@ -7289,7 +7461,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
         <v>193</v>
       </c>
@@ -7333,7 +7505,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="2">
         <v>194</v>
       </c>
@@ -7377,7 +7549,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="2">
         <v>195</v>
       </c>
@@ -7421,7 +7593,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="2">
         <v>196</v>
       </c>
@@ -7465,7 +7637,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
         <v>197</v>
       </c>
@@ -7513,7 +7685,7 @@
       <c r="A139" s="2">
         <v>76</v>
       </c>
-      <c r="B139" s="3">
+      <c r="B139" s="53">
         <v>2.27</v>
       </c>
       <c r="C139" s="2" t="s">
@@ -7557,7 +7729,7 @@
       <c r="A140" s="2">
         <v>154</v>
       </c>
-      <c r="B140" s="3">
+      <c r="B140" s="53">
         <v>2.2799999999999998</v>
       </c>
       <c r="C140" s="2" t="s">
@@ -7600,7 +7772,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
         <v>155</v>
       </c>
@@ -7651,7 +7823,7 @@
       <c r="A142" s="2">
         <v>77</v>
       </c>
-      <c r="B142" s="3">
+      <c r="B142" s="53">
         <v>2.2999999999999998</v>
       </c>
       <c r="C142" s="2" t="s">
@@ -7691,7 +7863,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="2">
         <v>123</v>
       </c>
@@ -7738,7 +7910,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="2">
         <v>124</v>
       </c>
@@ -7785,7 +7957,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="2">
         <v>125</v>
       </c>
@@ -7832,7 +8004,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
         <v>126</v>
       </c>
@@ -7879,7 +8051,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="2">
         <v>127</v>
       </c>
@@ -7926,7 +8098,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="2">
         <v>128</v>
       </c>
@@ -7977,7 +8149,7 @@
       <c r="A149" s="2">
         <v>156</v>
       </c>
-      <c r="B149" s="3">
+      <c r="B149" s="53">
         <v>2.37</v>
       </c>
       <c r="C149" s="2" t="s">
@@ -8020,7 +8192,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="2">
         <v>198</v>
       </c>
@@ -8064,7 +8236,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="2">
         <v>199</v>
       </c>
@@ -8112,7 +8284,7 @@
       <c r="A152" s="2">
         <v>157</v>
       </c>
-      <c r="B152" s="3">
+      <c r="B152" s="53">
         <v>2.4</v>
       </c>
       <c r="C152" s="2" t="s">
@@ -8159,7 +8331,7 @@
       <c r="A153" s="2">
         <v>90</v>
       </c>
-      <c r="B153" s="3">
+      <c r="B153" s="53">
         <v>2.41</v>
       </c>
       <c r="C153" s="2" t="s">
@@ -8203,7 +8375,7 @@
       <c r="A154" s="2">
         <v>158</v>
       </c>
-      <c r="B154" s="3">
+      <c r="B154" s="53">
         <v>2.42</v>
       </c>
       <c r="C154" s="2" t="s">
@@ -8246,7 +8418,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
         <v>200</v>
       </c>
@@ -8294,7 +8466,7 @@
       <c r="A156" s="2">
         <v>159</v>
       </c>
-      <c r="B156" s="3">
+      <c r="B156" s="53">
         <v>2.44</v>
       </c>
       <c r="C156" s="2" t="s">
@@ -8341,7 +8513,7 @@
       <c r="A157" s="2">
         <v>91</v>
       </c>
-      <c r="B157" s="3">
+      <c r="B157" s="53">
         <v>2.4500000000000002</v>
       </c>
       <c r="C157" s="2" t="s">
@@ -8381,7 +8553,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="2">
         <v>201</v>
       </c>
@@ -8429,7 +8601,7 @@
       <c r="A159" s="2">
         <v>160</v>
       </c>
-      <c r="B159" s="3">
+      <c r="B159" s="53">
         <v>2.4700000000000002</v>
       </c>
       <c r="C159" s="2" t="s">
@@ -8476,7 +8648,7 @@
       <c r="A160" s="2">
         <v>161</v>
       </c>
-      <c r="B160" s="3">
+      <c r="B160" s="53">
         <v>2.48</v>
       </c>
       <c r="C160" s="2" t="s">
@@ -8523,7 +8695,7 @@
       <c r="A161" s="2">
         <v>162</v>
       </c>
-      <c r="B161" s="3">
+      <c r="B161" s="53">
         <v>2.4900000000000002</v>
       </c>
       <c r="C161" s="2" t="s">
@@ -8570,7 +8742,7 @@
       <c r="A162" s="2">
         <v>163</v>
       </c>
-      <c r="B162" s="3">
+      <c r="B162" s="53">
         <v>2.5</v>
       </c>
       <c r="C162" s="2" t="s">
@@ -8614,7 +8786,7 @@
       <c r="A163" s="2">
         <v>78</v>
       </c>
-      <c r="B163" s="3">
+      <c r="B163" s="53">
         <v>2.5099999999999998</v>
       </c>
       <c r="C163" s="2" t="s">
@@ -8654,7 +8826,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="2">
         <v>202</v>
       </c>
@@ -8698,7 +8870,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="2">
         <v>129</v>
       </c>
@@ -8745,7 +8917,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="2">
         <v>130</v>
       </c>
@@ -8792,7 +8964,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="2">
         <v>131</v>
       </c>
@@ -8843,7 +9015,7 @@
       <c r="A168" s="2">
         <v>79</v>
       </c>
-      <c r="B168" s="3">
+      <c r="B168" s="53">
         <v>2.56</v>
       </c>
       <c r="C168" s="2" t="s">
@@ -8883,7 +9055,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="2">
         <v>132</v>
       </c>
@@ -8934,7 +9106,7 @@
       <c r="A170" s="2">
         <v>164</v>
       </c>
-      <c r="B170" s="3">
+      <c r="B170" s="53">
         <v>2.58</v>
       </c>
       <c r="C170" s="2" t="s">
@@ -8981,7 +9153,7 @@
       <c r="A171" s="2">
         <v>165</v>
       </c>
-      <c r="B171" s="3">
+      <c r="B171" s="53">
         <v>3.01</v>
       </c>
       <c r="C171" s="2" t="s">
@@ -9028,7 +9200,7 @@
       <c r="A172" s="2">
         <v>166</v>
       </c>
-      <c r="B172" s="3">
+      <c r="B172" s="53">
         <v>3.02</v>
       </c>
       <c r="C172" s="2" t="s">
@@ -9075,7 +9247,7 @@
       <c r="A173" s="2">
         <v>167</v>
       </c>
-      <c r="B173" s="3">
+      <c r="B173" s="53">
         <v>3.03</v>
       </c>
       <c r="C173" s="2" t="s">
@@ -9122,7 +9294,7 @@
       <c r="A174" s="2">
         <v>168</v>
       </c>
-      <c r="B174" s="3">
+      <c r="B174" s="53">
         <v>3.04</v>
       </c>
       <c r="C174" s="2" t="s">
@@ -9169,7 +9341,7 @@
       <c r="A175" s="2">
         <v>169</v>
       </c>
-      <c r="B175" s="3">
+      <c r="B175" s="53">
         <v>3.05</v>
       </c>
       <c r="C175" s="2" t="s">
@@ -9216,7 +9388,7 @@
       <c r="A176" s="2">
         <v>170</v>
       </c>
-      <c r="B176" s="3">
+      <c r="B176" s="53">
         <v>3.06</v>
       </c>
       <c r="C176" s="2" t="s">
@@ -9263,7 +9435,7 @@
       <c r="A177" s="2">
         <v>171</v>
       </c>
-      <c r="B177" s="3">
+      <c r="B177" s="53">
         <v>3.07</v>
       </c>
       <c r="C177" s="2" t="s">
@@ -9310,7 +9482,7 @@
       <c r="A178" s="2">
         <v>172</v>
       </c>
-      <c r="B178" s="3">
+      <c r="B178" s="53">
         <v>3.08</v>
       </c>
       <c r="C178" s="2" t="s">
@@ -9353,7 +9525,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="2">
         <v>203</v>
       </c>
@@ -9397,7 +9569,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="2">
         <v>204</v>
       </c>
@@ -9441,7 +9613,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="2">
         <v>205</v>
       </c>
@@ -9489,7 +9661,7 @@
       <c r="A182" s="2">
         <v>173</v>
       </c>
-      <c r="B182" s="3">
+      <c r="B182" s="53">
         <v>3.12</v>
       </c>
       <c r="C182" s="2" t="s">
@@ -9536,7 +9708,7 @@
       <c r="A183" s="2">
         <v>174</v>
       </c>
-      <c r="B183" s="3">
+      <c r="B183" s="53">
         <v>3.13</v>
       </c>
       <c r="C183" s="2" t="s">
@@ -9579,7 +9751,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="2">
         <v>206</v>
       </c>
@@ -9623,7 +9795,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="2">
         <v>207</v>
       </c>
@@ -9667,7 +9839,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="2">
         <v>133</v>
       </c>
@@ -9714,7 +9886,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="2">
         <v>134</v>
       </c>
@@ -9765,7 +9937,7 @@
       <c r="A188" s="2">
         <v>175</v>
       </c>
-      <c r="B188" s="3">
+      <c r="B188" s="53">
         <v>3.18</v>
       </c>
       <c r="C188" s="2" t="s">
@@ -9812,7 +9984,7 @@
       <c r="A189" s="2">
         <v>80</v>
       </c>
-      <c r="B189" s="3">
+      <c r="B189" s="53">
         <v>3.19</v>
       </c>
       <c r="C189" s="2" t="s">
@@ -9852,7 +10024,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="2">
         <v>135</v>
       </c>
@@ -9899,7 +10071,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="2">
         <v>136</v>
       </c>
@@ -9946,7 +10118,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="2">
         <v>137</v>
       </c>
@@ -9997,7 +10169,7 @@
       <c r="A193" s="2">
         <v>176</v>
       </c>
-      <c r="B193" s="3">
+      <c r="B193" s="53">
         <v>3.23</v>
       </c>
       <c r="C193" s="2" t="s">
@@ -10040,7 +10212,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="2">
         <v>208</v>
       </c>
@@ -10088,7 +10260,7 @@
       <c r="A195" s="2">
         <v>177</v>
       </c>
-      <c r="B195" s="3">
+      <c r="B195" s="53">
         <v>3.25</v>
       </c>
       <c r="C195" s="2" t="s">
@@ -10135,7 +10307,7 @@
       <c r="A196" s="2">
         <v>92</v>
       </c>
-      <c r="B196" s="3">
+      <c r="B196" s="53">
         <v>3.26</v>
       </c>
       <c r="C196" s="2" t="s">
@@ -10175,7 +10347,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="2">
         <v>209</v>
       </c>
@@ -10223,7 +10395,7 @@
       <c r="A198" s="2">
         <v>178</v>
       </c>
-      <c r="B198" s="3">
+      <c r="B198" s="53">
         <v>3.28</v>
       </c>
       <c r="C198" s="2" t="s">
@@ -10270,7 +10442,7 @@
       <c r="A199" s="2">
         <v>179</v>
       </c>
-      <c r="B199" s="3">
+      <c r="B199" s="53">
         <v>3.29</v>
       </c>
       <c r="C199" s="2" t="s">
@@ -10317,7 +10489,7 @@
       <c r="A200" s="2">
         <v>93</v>
       </c>
-      <c r="B200" s="3">
+      <c r="B200" s="53">
         <v>3.3</v>
       </c>
       <c r="C200" s="2" t="s">
@@ -10357,7 +10529,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="2">
         <v>210</v>
       </c>
@@ -10401,7 +10573,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="2">
         <v>211</v>
       </c>
@@ -10449,7 +10621,7 @@
       <c r="A203" s="2">
         <v>180</v>
       </c>
-      <c r="B203" s="3">
+      <c r="B203" s="53">
         <v>3.33</v>
       </c>
       <c r="C203" s="2" t="s">
@@ -10496,7 +10668,7 @@
       <c r="A204" s="2">
         <v>181</v>
       </c>
-      <c r="B204" s="3">
+      <c r="B204" s="53">
         <v>3.34</v>
       </c>
       <c r="C204" s="2" t="s">
@@ -10543,7 +10715,7 @@
       <c r="A205" s="2">
         <v>182</v>
       </c>
-      <c r="B205" s="3">
+      <c r="B205" s="53">
         <v>3.35</v>
       </c>
       <c r="C205" s="2" t="s">
@@ -10586,7 +10758,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="2">
         <v>138</v>
       </c>
@@ -10633,7 +10805,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="2">
         <v>139</v>
       </c>
@@ -10680,7 +10852,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="2">
         <v>140</v>
       </c>
@@ -10727,7 +10899,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="209" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="2">
         <v>141</v>
       </c>
@@ -10774,7 +10946,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="210" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="2">
         <v>212</v>
       </c>
@@ -10822,7 +10994,7 @@
       <c r="A211" s="2">
         <v>81</v>
       </c>
-      <c r="B211" s="3">
+      <c r="B211" s="53">
         <v>3.41</v>
       </c>
       <c r="C211" s="2" t="s">
@@ -10866,7 +11038,7 @@
       <c r="A212" s="2">
         <v>82</v>
       </c>
-      <c r="B212" s="3">
+      <c r="B212" s="53">
         <v>3.42</v>
       </c>
       <c r="C212" s="2" t="s">
@@ -10906,7 +11078,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="213" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="2">
         <v>142</v>
       </c>
@@ -10957,7 +11129,7 @@
       <c r="A214" s="2">
         <v>83</v>
       </c>
-      <c r="B214" s="3">
+      <c r="B214" s="53">
         <v>3.44</v>
       </c>
       <c r="C214" s="2" t="s">
@@ -11001,7 +11173,7 @@
       <c r="A215" s="2">
         <v>183</v>
       </c>
-      <c r="B215" s="3">
+      <c r="B215" s="53">
         <v>3.45</v>
       </c>
       <c r="C215" s="2" t="s">
@@ -11044,7 +11216,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="216" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="2">
         <v>54</v>
       </c>
@@ -11704,6 +11876,775 @@
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E40"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="55.6640625" customWidth="1"/>
+    <col min="2" max="2" width="46.5546875" customWidth="1"/>
+    <col min="3" max="4" width="16.44140625" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="54" x14ac:dyDescent="0.3">
+      <c r="A1" s="33" t="s">
+        <v>457</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>445</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>395</v>
+      </c>
+      <c r="D1" s="32">
+        <v>1</v>
+      </c>
+      <c r="E1" s="32">
+        <v>370.9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="54" x14ac:dyDescent="0.3">
+      <c r="A2" s="33" t="s">
+        <v>446</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>444</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>395</v>
+      </c>
+      <c r="D2" s="32">
+        <v>1</v>
+      </c>
+      <c r="E2" s="32">
+        <v>1132.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="A3" s="38" t="s">
+        <v>452</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="35" t="s">
+        <v>447</v>
+      </c>
+      <c r="D3" s="34">
+        <v>1.2</v>
+      </c>
+      <c r="E3" s="37">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" s="36" t="s">
+        <v>451</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>456</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>395</v>
+      </c>
+      <c r="D4" s="34">
+        <v>1.2</v>
+      </c>
+      <c r="E4" s="37">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="A5" s="36" t="s">
+        <v>449</v>
+      </c>
+      <c r="B5" s="31"/>
+      <c r="C5" s="35" t="s">
+        <v>447</v>
+      </c>
+      <c r="D5" s="34">
+        <v>0.25</v>
+      </c>
+      <c r="E5" s="37">
+        <v>283.125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="A6" s="36" t="s">
+        <v>448</v>
+      </c>
+      <c r="B6" s="31"/>
+      <c r="C6" s="35" t="s">
+        <v>447</v>
+      </c>
+      <c r="D6" s="34">
+        <v>0.15</v>
+      </c>
+      <c r="E6" s="34">
+        <v>169.875</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="54" x14ac:dyDescent="0.3">
+      <c r="A7" s="33" t="s">
+        <v>446</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>443</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>395</v>
+      </c>
+      <c r="D7" s="32">
+        <v>1</v>
+      </c>
+      <c r="E7" s="32">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="A8" s="36" t="s">
+        <v>448</v>
+      </c>
+      <c r="B8" s="31"/>
+      <c r="C8" s="35" t="s">
+        <v>447</v>
+      </c>
+      <c r="D8" s="34">
+        <v>0.15</v>
+      </c>
+      <c r="E8" s="34">
+        <v>4.68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="A9" s="36" t="s">
+        <v>449</v>
+      </c>
+      <c r="B9" s="31"/>
+      <c r="C9" s="35" t="s">
+        <v>447</v>
+      </c>
+      <c r="D9" s="34">
+        <v>0.25</v>
+      </c>
+      <c r="E9" s="37">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="54" x14ac:dyDescent="0.3">
+      <c r="A10" s="36" t="s">
+        <v>451</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>455</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>395</v>
+      </c>
+      <c r="D10" s="34">
+        <v>1.2</v>
+      </c>
+      <c r="E10" s="37">
+        <v>37.44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="A11" s="38" t="s">
+        <v>452</v>
+      </c>
+      <c r="B11" s="31"/>
+      <c r="C11" s="35" t="s">
+        <v>447</v>
+      </c>
+      <c r="D11" s="34">
+        <v>1.2</v>
+      </c>
+      <c r="E11" s="37">
+        <v>37.44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="54" x14ac:dyDescent="0.3">
+      <c r="A12" s="33" t="s">
+        <v>446</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>442</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>395</v>
+      </c>
+      <c r="D12" s="32">
+        <v>1</v>
+      </c>
+      <c r="E12" s="32">
+        <v>560.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="A13" s="38" t="s">
+        <v>452</v>
+      </c>
+      <c r="B13" s="31"/>
+      <c r="C13" s="35" t="s">
+        <v>447</v>
+      </c>
+      <c r="D13" s="34">
+        <v>1.2</v>
+      </c>
+      <c r="E13" s="37">
+        <v>672.48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="54" x14ac:dyDescent="0.3">
+      <c r="A14" s="36" t="s">
+        <v>451</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>454</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>395</v>
+      </c>
+      <c r="D14" s="34">
+        <v>1.2</v>
+      </c>
+      <c r="E14" s="37">
+        <v>672.48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="A15" s="36" t="s">
+        <v>449</v>
+      </c>
+      <c r="B15" s="31"/>
+      <c r="C15" s="35" t="s">
+        <v>447</v>
+      </c>
+      <c r="D15" s="34">
+        <v>0.25</v>
+      </c>
+      <c r="E15" s="37">
+        <v>140.1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="A16" s="36" t="s">
+        <v>448</v>
+      </c>
+      <c r="B16" s="31"/>
+      <c r="C16" s="35" t="s">
+        <v>447</v>
+      </c>
+      <c r="D16" s="34">
+        <v>0.15</v>
+      </c>
+      <c r="E16" s="34">
+        <v>84.06</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="54" x14ac:dyDescent="0.3">
+      <c r="A17" s="33" t="s">
+        <v>446</v>
+      </c>
+      <c r="B17" s="31" t="s">
+        <v>441</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>395</v>
+      </c>
+      <c r="D17" s="32">
+        <v>1</v>
+      </c>
+      <c r="E17" s="32">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="A18" s="36" t="s">
+        <v>448</v>
+      </c>
+      <c r="B18" s="31"/>
+      <c r="C18" s="35" t="s">
+        <v>447</v>
+      </c>
+      <c r="D18" s="34">
+        <v>0.15</v>
+      </c>
+      <c r="E18" s="34">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="A19" s="36" t="s">
+        <v>449</v>
+      </c>
+      <c r="B19" s="31"/>
+      <c r="C19" s="35" t="s">
+        <v>447</v>
+      </c>
+      <c r="D19" s="34">
+        <v>0.25</v>
+      </c>
+      <c r="E19" s="37">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="54" x14ac:dyDescent="0.3">
+      <c r="A20" s="36" t="s">
+        <v>451</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>453</v>
+      </c>
+      <c r="C20" s="35" t="s">
+        <v>395</v>
+      </c>
+      <c r="D20" s="34">
+        <v>1.2</v>
+      </c>
+      <c r="E20" s="37">
+        <v>33.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="A21" s="38" t="s">
+        <v>452</v>
+      </c>
+      <c r="B21" s="31"/>
+      <c r="C21" s="35" t="s">
+        <v>447</v>
+      </c>
+      <c r="D21" s="34">
+        <v>1.2</v>
+      </c>
+      <c r="E21" s="37">
+        <v>33.6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="54" x14ac:dyDescent="0.3">
+      <c r="A22" s="33" t="s">
+        <v>446</v>
+      </c>
+      <c r="B22" s="31" t="s">
+        <v>440</v>
+      </c>
+      <c r="C22" s="31" t="s">
+        <v>395</v>
+      </c>
+      <c r="D22" s="32">
+        <v>1</v>
+      </c>
+      <c r="E22" s="32">
+        <v>207.1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="A23" s="38" t="s">
+        <v>452</v>
+      </c>
+      <c r="B23" s="31"/>
+      <c r="C23" s="35" t="s">
+        <v>447</v>
+      </c>
+      <c r="D23" s="34">
+        <v>1.2</v>
+      </c>
+      <c r="E23" s="37">
+        <v>248.52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="54" x14ac:dyDescent="0.3">
+      <c r="A24" s="36" t="s">
+        <v>451</v>
+      </c>
+      <c r="B24" s="31" t="s">
+        <v>450</v>
+      </c>
+      <c r="C24" s="35" t="s">
+        <v>395</v>
+      </c>
+      <c r="D24" s="34">
+        <v>1.2</v>
+      </c>
+      <c r="E24" s="37">
+        <v>248.52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="A25" s="36" t="s">
+        <v>449</v>
+      </c>
+      <c r="B25" s="31"/>
+      <c r="C25" s="35" t="s">
+        <v>447</v>
+      </c>
+      <c r="D25" s="34">
+        <v>0.25</v>
+      </c>
+      <c r="E25" s="37">
+        <v>51.774999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="A26" s="36" t="s">
+        <v>448</v>
+      </c>
+      <c r="B26" s="31"/>
+      <c r="C26" s="35" t="s">
+        <v>447</v>
+      </c>
+      <c r="D26" s="34">
+        <v>0.15</v>
+      </c>
+      <c r="E26" s="34">
+        <v>31.065000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="54" x14ac:dyDescent="0.3">
+      <c r="A27" s="33" t="s">
+        <v>446</v>
+      </c>
+      <c r="B27" s="31" t="s">
+        <v>439</v>
+      </c>
+      <c r="C27" s="31" t="s">
+        <v>395</v>
+      </c>
+      <c r="D27" s="32">
+        <v>1</v>
+      </c>
+      <c r="E27" s="32">
+        <v>207.5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B34" s="31" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B35" s="31" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B36" s="31" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B37" s="31" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B38" s="31" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B39" s="31" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" ht="36" x14ac:dyDescent="0.3">
+      <c r="B40" s="31" t="s">
+        <v>439</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="22"/>
+    <col min="2" max="2" width="40" style="26" customWidth="1"/>
+    <col min="3" max="3" width="12" style="28" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="47" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="49"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="21" t="s">
+        <v>390</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>398</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="21">
+        <v>1</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>411</v>
+      </c>
+      <c r="C3" s="27">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="36" x14ac:dyDescent="0.35">
+      <c r="A4" s="21">
+        <v>2</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="27">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="21">
+        <v>3</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>412</v>
+      </c>
+      <c r="C5" s="27">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="21">
+        <v>4</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>413</v>
+      </c>
+      <c r="C6" s="27">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="36" x14ac:dyDescent="0.35">
+      <c r="A7" s="21">
+        <v>5</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="27">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="16.8" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="21">
+        <v>6</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>414</v>
+      </c>
+      <c r="C8" s="27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="36" x14ac:dyDescent="0.35">
+      <c r="A9" s="21">
+        <v>7</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>415</v>
+      </c>
+      <c r="C9" s="27">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="21">
+        <v>8</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>416</v>
+      </c>
+      <c r="C10" s="27">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="21">
+        <v>9</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>417</v>
+      </c>
+      <c r="C11" s="27">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="21">
+        <v>10</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>418</v>
+      </c>
+      <c r="C12" s="27">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="21">
+        <v>11</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>419</v>
+      </c>
+      <c r="C13" s="27">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="21">
+        <v>12</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>420</v>
+      </c>
+      <c r="C14" s="27">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="36" x14ac:dyDescent="0.35">
+      <c r="A15" s="21">
+        <v>13</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>421</v>
+      </c>
+      <c r="C15" s="27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="21">
+        <v>14</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" s="27">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="36" x14ac:dyDescent="0.35">
+      <c r="A17" s="21">
+        <v>15</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="C17" s="27">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="21">
+        <v>16</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>422</v>
+      </c>
+      <c r="C18" s="27">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="21">
+        <v>17</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>423</v>
+      </c>
+      <c r="C19" s="27">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="21">
+        <v>18</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>424</v>
+      </c>
+      <c r="C20" s="27">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="36" x14ac:dyDescent="0.35">
+      <c r="A21" s="21">
+        <v>19</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="C21" s="27">
+        <v>5.74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="21">
+        <v>20</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="C22" s="27">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="36" x14ac:dyDescent="0.35">
+      <c r="A23" s="21">
+        <v>21</v>
+      </c>
+      <c r="B23" s="24" t="s">
+        <v>425</v>
+      </c>
+      <c r="C23" s="27">
+        <v>5.74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="36" x14ac:dyDescent="0.35">
+      <c r="A24" s="21">
+        <v>22</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>426</v>
+      </c>
+      <c r="C24" s="27">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="21"/>
+      <c r="B25" s="25" t="s">
+        <v>400</v>
+      </c>
+      <c r="C25" s="27">
+        <f>SUM(C3:C24)</f>
+        <v>256.98</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -11940,6 +12881,227 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B6:C36"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C6" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>21</v>
+      </c>
+      <c r="C7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>58</v>
+      </c>
+      <c r="C8">
+        <v>76.2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>27</v>
+      </c>
+      <c r="C9">
+        <v>19.100000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>28</v>
+      </c>
+      <c r="C10">
+        <v>201.1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>63.7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <v>90.2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13">
+        <v>40.1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>4</v>
+      </c>
+      <c r="C14">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>5</v>
+      </c>
+      <c r="C15">
+        <v>65.400000000000006</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>64.099999999999994</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B17">
+        <v>30</v>
+      </c>
+      <c r="C17">
+        <v>115.4</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <v>7</v>
+      </c>
+      <c r="C18">
+        <v>64.3</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B19">
+        <v>8</v>
+      </c>
+      <c r="C19">
+        <v>79.7</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B20">
+        <v>15</v>
+      </c>
+      <c r="C20">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B22">
+        <v>51</v>
+      </c>
+      <c r="C22" s="72">
+        <v>37.1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B23">
+        <v>37</v>
+      </c>
+      <c r="C23">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B24">
+        <v>40</v>
+      </c>
+      <c r="C24">
+        <v>51.3</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B25">
+        <v>41</v>
+      </c>
+      <c r="C25">
+        <v>56.6</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B26">
+        <v>42</v>
+      </c>
+      <c r="C26">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B27">
+        <v>44</v>
+      </c>
+      <c r="C27">
+        <v>51.3</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B28">
+        <v>45</v>
+      </c>
+      <c r="C28">
+        <v>56.3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B29">
+        <v>56</v>
+      </c>
+      <c r="C29" s="72">
+        <v>60.9</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B30">
+        <v>49</v>
+      </c>
+      <c r="C30">
+        <v>75.2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B31">
+        <v>50</v>
+      </c>
+      <c r="C31" s="72">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B32">
+        <v>48</v>
+      </c>
+      <c r="C32" s="72">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C36" t="s">
+        <v>502</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
@@ -11950,11 +13112,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="47" t="s">
         <v>396</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="46"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="49"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
@@ -12117,7 +13279,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12178,9 +13340,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="22" customWidth="1"/>
@@ -12192,13 +13354,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="50" t="s">
         <v>389</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="49"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="52"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
@@ -12253,6 +13415,7 @@
         <v>1386.8000000000002</v>
       </c>
     </row>
+    <row r="6" spans="1:5" ht="10.8" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
@@ -12262,13 +13425,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.21875" style="41" customWidth="1"/>
-    <col min="2" max="2" width="7.109375" style="51" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" style="44" customWidth="1"/>
     <col min="3" max="3" width="9.21875" style="41" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="8.88671875" style="41"/>
   </cols>
@@ -12277,7 +13440,7 @@
       <c r="A1" s="39" t="s">
         <v>460</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="43" t="s">
         <v>459</v>
       </c>
       <c r="C1" s="40" t="s">
@@ -12288,7 +13451,7 @@
       <c r="A2" s="42" t="s">
         <v>462</v>
       </c>
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="43" t="s">
         <v>13</v>
       </c>
       <c r="C2" s="40">
@@ -12299,7 +13462,7 @@
       <c r="A3" s="42" t="s">
         <v>471</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="43" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="40">
@@ -12310,7 +13473,7 @@
       <c r="A4" s="42" t="s">
         <v>474</v>
       </c>
-      <c r="B4" s="50" t="s">
+      <c r="B4" s="43" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="40">
@@ -12321,7 +13484,7 @@
       <c r="A5" s="42" t="s">
         <v>477</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="43" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="40">
@@ -12332,7 +13495,7 @@
       <c r="A6" s="42" t="s">
         <v>478</v>
       </c>
-      <c r="B6" s="50" t="s">
+      <c r="B6" s="43" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="40">
@@ -12343,7 +13506,7 @@
       <c r="A7" s="42" t="s">
         <v>491</v>
       </c>
-      <c r="B7" s="50" t="s">
+      <c r="B7" s="43" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="40">
@@ -12352,10 +13515,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="40"/>
-      <c r="B8" s="50" t="s">
+      <c r="B8" s="43" t="s">
         <v>492</v>
       </c>
-      <c r="C8" s="52">
+      <c r="C8" s="45">
         <f>SUM(C2:C7)</f>
         <v>289.5</v>
       </c>
@@ -12364,7 +13527,7 @@
       <c r="A10" s="39" t="s">
         <v>460</v>
       </c>
-      <c r="B10" s="50" t="s">
+      <c r="B10" s="43" t="s">
         <v>459</v>
       </c>
       <c r="C10" s="40" t="s">
@@ -12375,7 +13538,7 @@
       <c r="A11" s="42" t="s">
         <v>463</v>
       </c>
-      <c r="B11" s="50" t="s">
+      <c r="B11" s="43" t="s">
         <v>17</v>
       </c>
       <c r="C11" s="40">
@@ -12386,7 +13549,7 @@
       <c r="A12" s="42" t="s">
         <v>464</v>
       </c>
-      <c r="B12" s="50" t="s">
+      <c r="B12" s="43" t="s">
         <v>17</v>
       </c>
       <c r="C12" s="40">
@@ -12397,7 +13560,7 @@
       <c r="A13" s="42" t="s">
         <v>465</v>
       </c>
-      <c r="B13" s="50" t="s">
+      <c r="B13" s="43" t="s">
         <v>17</v>
       </c>
       <c r="C13" s="40">
@@ -12408,7 +13571,7 @@
       <c r="A14" s="42" t="s">
         <v>466</v>
       </c>
-      <c r="B14" s="50" t="s">
+      <c r="B14" s="43" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="40">
@@ -12419,7 +13582,7 @@
       <c r="A15" s="42" t="s">
         <v>467</v>
       </c>
-      <c r="B15" s="50" t="s">
+      <c r="B15" s="43" t="s">
         <v>17</v>
       </c>
       <c r="C15" s="40">
@@ -12430,7 +13593,7 @@
       <c r="A16" s="42" t="s">
         <v>468</v>
       </c>
-      <c r="B16" s="50" t="s">
+      <c r="B16" s="43" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="40">
@@ -12441,7 +13604,7 @@
       <c r="A17" s="42" t="s">
         <v>469</v>
       </c>
-      <c r="B17" s="50" t="s">
+      <c r="B17" s="43" t="s">
         <v>17</v>
       </c>
       <c r="C17" s="40">
@@ -12452,7 +13615,7 @@
       <c r="A18" s="42" t="s">
         <v>470</v>
       </c>
-      <c r="B18" s="50" t="s">
+      <c r="B18" s="43" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="40">
@@ -12463,7 +13626,7 @@
       <c r="A19" s="42" t="s">
         <v>472</v>
       </c>
-      <c r="B19" s="50" t="s">
+      <c r="B19" s="43" t="s">
         <v>17</v>
       </c>
       <c r="C19" s="40">
@@ -12474,7 +13637,7 @@
       <c r="A20" s="42" t="s">
         <v>473</v>
       </c>
-      <c r="B20" s="50" t="s">
+      <c r="B20" s="43" t="s">
         <v>17</v>
       </c>
       <c r="C20" s="40">
@@ -12485,7 +13648,7 @@
       <c r="A21" s="42" t="s">
         <v>475</v>
       </c>
-      <c r="B21" s="50" t="s">
+      <c r="B21" s="43" t="s">
         <v>17</v>
       </c>
       <c r="C21" s="40">
@@ -12496,7 +13659,7 @@
       <c r="A22" s="42" t="s">
         <v>476</v>
       </c>
-      <c r="B22" s="50" t="s">
+      <c r="B22" s="43" t="s">
         <v>17</v>
       </c>
       <c r="C22" s="40">
@@ -12507,7 +13670,7 @@
       <c r="A23" s="42" t="s">
         <v>479</v>
       </c>
-      <c r="B23" s="50" t="s">
+      <c r="B23" s="43" t="s">
         <v>17</v>
       </c>
       <c r="C23" s="40">
@@ -12518,7 +13681,7 @@
       <c r="A24" s="42" t="s">
         <v>480</v>
       </c>
-      <c r="B24" s="50" t="s">
+      <c r="B24" s="43" t="s">
         <v>17</v>
       </c>
       <c r="C24" s="40">
@@ -12529,7 +13692,7 @@
       <c r="A25" s="42" t="s">
         <v>481</v>
       </c>
-      <c r="B25" s="50" t="s">
+      <c r="B25" s="43" t="s">
         <v>17</v>
       </c>
       <c r="C25" s="40">
@@ -12540,7 +13703,7 @@
       <c r="A26" s="42" t="s">
         <v>482</v>
       </c>
-      <c r="B26" s="50" t="s">
+      <c r="B26" s="43" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="40">
@@ -12551,7 +13714,7 @@
       <c r="A27" s="42" t="s">
         <v>483</v>
       </c>
-      <c r="B27" s="50" t="s">
+      <c r="B27" s="43" t="s">
         <v>17</v>
       </c>
       <c r="C27" s="40">
@@ -12562,7 +13725,7 @@
       <c r="A28" s="42" t="s">
         <v>484</v>
       </c>
-      <c r="B28" s="50" t="s">
+      <c r="B28" s="43" t="s">
         <v>17</v>
       </c>
       <c r="C28" s="40">
@@ -12573,7 +13736,7 @@
       <c r="A29" s="42" t="s">
         <v>485</v>
       </c>
-      <c r="B29" s="50" t="s">
+      <c r="B29" s="43" t="s">
         <v>17</v>
       </c>
       <c r="C29" s="40">
@@ -12584,7 +13747,7 @@
       <c r="A30" s="42" t="s">
         <v>486</v>
       </c>
-      <c r="B30" s="50" t="s">
+      <c r="B30" s="43" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="40">
@@ -12595,7 +13758,7 @@
       <c r="A31" s="42" t="s">
         <v>487</v>
       </c>
-      <c r="B31" s="50" t="s">
+      <c r="B31" s="43" t="s">
         <v>17</v>
       </c>
       <c r="C31" s="40">
@@ -12606,7 +13769,7 @@
       <c r="A32" s="42" t="s">
         <v>488</v>
       </c>
-      <c r="B32" s="50" t="s">
+      <c r="B32" s="43" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="40">
@@ -12617,7 +13780,7 @@
       <c r="A33" s="42" t="s">
         <v>489</v>
       </c>
-      <c r="B33" s="50" t="s">
+      <c r="B33" s="43" t="s">
         <v>17</v>
       </c>
       <c r="C33" s="40">
@@ -12628,7 +13791,7 @@
       <c r="A34" s="42" t="s">
         <v>490</v>
       </c>
-      <c r="B34" s="50" t="s">
+      <c r="B34" s="43" t="s">
         <v>17</v>
       </c>
       <c r="C34" s="40">
@@ -12637,10 +13800,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="40"/>
-      <c r="B35" s="50" t="s">
+      <c r="B35" s="43" t="s">
         <v>492</v>
       </c>
-      <c r="C35" s="52">
+      <c r="C35" s="45">
         <f>SUM(C11:C34)</f>
         <v>1386.8000000000002</v>
       </c>
@@ -12651,770 +13814,874 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E40"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="55.6640625" customWidth="1"/>
-    <col min="2" max="2" width="46.5546875" customWidth="1"/>
-    <col min="3" max="4" width="16.44140625" customWidth="1"/>
-    <col min="5" max="5" width="16.77734375" customWidth="1"/>
+    <col min="1" max="1" width="7.21875" style="57" customWidth="1"/>
+    <col min="2" max="2" width="7.88671875" style="57" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" style="57" customWidth="1"/>
+    <col min="4" max="4" width="4.109375" style="57" customWidth="1"/>
+    <col min="5" max="5" width="7.109375" style="57" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" style="57" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" style="57" customWidth="1"/>
+    <col min="8" max="8" width="5.33203125" style="57" customWidth="1"/>
+    <col min="9" max="9" width="7.88671875" style="57" customWidth="1"/>
+    <col min="10" max="10" width="8.21875" style="57" customWidth="1"/>
+    <col min="11" max="11" width="9.88671875" style="57" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="57"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="54" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
-        <v>457</v>
-      </c>
-      <c r="B1" s="31" t="s">
-        <v>445</v>
-      </c>
-      <c r="C1" s="31" t="s">
+    <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="65" t="s">
+        <v>389</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+    </row>
+    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="55" t="s">
+        <v>390</v>
+      </c>
+      <c r="B2" s="66" t="s">
+        <v>391</v>
+      </c>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="56" t="s">
+        <v>393</v>
+      </c>
+      <c r="H2" s="70" t="s">
+        <v>394</v>
+      </c>
+      <c r="I2" s="70"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+    </row>
+    <row r="3" spans="1:11" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="64">
+        <v>1</v>
+      </c>
+      <c r="B3" s="69" t="s">
+        <v>497</v>
+      </c>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="64" t="s">
         <v>395</v>
       </c>
-      <c r="D1" s="32">
+      <c r="H3" s="71">
+        <f>C21+G30+K31</f>
+        <v>4099.5</v>
+      </c>
+      <c r="I3" s="71"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+    </row>
+    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="67"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+    </row>
+    <row r="5" spans="1:11" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="54" t="s">
+        <v>496</v>
+      </c>
+      <c r="B5" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="32">
-        <v>370.9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="54" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
-        <v>446</v>
-      </c>
-      <c r="B2" s="31" t="s">
-        <v>444</v>
-      </c>
-      <c r="C2" s="31" t="s">
-        <v>395</v>
-      </c>
-      <c r="D2" s="32">
+      <c r="C5" s="54" t="s">
+        <v>495</v>
+      </c>
+      <c r="D5" s="67"/>
+      <c r="E5" s="54" t="s">
+        <v>496</v>
+      </c>
+      <c r="F5" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="32">
-        <v>1132.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="36" x14ac:dyDescent="0.3">
-      <c r="A3" s="38" t="s">
-        <v>452</v>
-      </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="35" t="s">
-        <v>447</v>
-      </c>
-      <c r="D3" s="34">
-        <v>1.2</v>
-      </c>
-      <c r="E3" s="37">
-        <v>1359</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="72" x14ac:dyDescent="0.3">
-      <c r="A4" s="36" t="s">
-        <v>451</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>456</v>
-      </c>
-      <c r="C4" s="35" t="s">
-        <v>395</v>
-      </c>
-      <c r="D4" s="34">
-        <v>1.2</v>
-      </c>
-      <c r="E4" s="37">
-        <v>1359</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="A5" s="36" t="s">
-        <v>449</v>
-      </c>
-      <c r="B5" s="31"/>
-      <c r="C5" s="35" t="s">
-        <v>447</v>
-      </c>
-      <c r="D5" s="34">
-        <v>0.25</v>
-      </c>
-      <c r="E5" s="37">
-        <v>283.125</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="36" x14ac:dyDescent="0.3">
-      <c r="A6" s="36" t="s">
-        <v>448</v>
-      </c>
-      <c r="B6" s="31"/>
-      <c r="C6" s="35" t="s">
-        <v>447</v>
-      </c>
-      <c r="D6" s="34">
-        <v>0.15</v>
-      </c>
-      <c r="E6" s="34">
-        <v>169.875</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="54" x14ac:dyDescent="0.3">
-      <c r="A7" s="33" t="s">
-        <v>446</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>443</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>395</v>
-      </c>
-      <c r="D7" s="32">
+      <c r="G5" s="54" t="s">
+        <v>495</v>
+      </c>
+      <c r="H5" s="67"/>
+      <c r="I5" s="54" t="s">
+        <v>496</v>
+      </c>
+      <c r="J5" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="32">
-        <v>31.2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="36" x14ac:dyDescent="0.3">
-      <c r="A8" s="36" t="s">
-        <v>448</v>
-      </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="35" t="s">
-        <v>447</v>
-      </c>
-      <c r="D8" s="34">
-        <v>0.15</v>
-      </c>
-      <c r="E8" s="34">
-        <v>4.68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="A9" s="36" t="s">
-        <v>449</v>
-      </c>
-      <c r="B9" s="31"/>
-      <c r="C9" s="35" t="s">
-        <v>447</v>
-      </c>
-      <c r="D9" s="34">
-        <v>0.25</v>
-      </c>
-      <c r="E9" s="37">
-        <v>7.8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="54" x14ac:dyDescent="0.3">
-      <c r="A10" s="36" t="s">
-        <v>451</v>
-      </c>
-      <c r="B10" s="31" t="s">
-        <v>455</v>
-      </c>
-      <c r="C10" s="35" t="s">
-        <v>395</v>
-      </c>
-      <c r="D10" s="34">
-        <v>1.2</v>
-      </c>
-      <c r="E10" s="37">
-        <v>37.44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="36" x14ac:dyDescent="0.3">
-      <c r="A11" s="38" t="s">
-        <v>452</v>
-      </c>
-      <c r="B11" s="31"/>
-      <c r="C11" s="35" t="s">
-        <v>447</v>
-      </c>
-      <c r="D11" s="34">
-        <v>1.2</v>
-      </c>
-      <c r="E11" s="37">
-        <v>37.44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="54" x14ac:dyDescent="0.3">
-      <c r="A12" s="33" t="s">
-        <v>446</v>
-      </c>
-      <c r="B12" s="31" t="s">
-        <v>442</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>395</v>
-      </c>
-      <c r="D12" s="32">
-        <v>1</v>
-      </c>
-      <c r="E12" s="32">
-        <v>560.4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="36" x14ac:dyDescent="0.3">
-      <c r="A13" s="38" t="s">
-        <v>452</v>
-      </c>
-      <c r="B13" s="31"/>
-      <c r="C13" s="35" t="s">
-        <v>447</v>
-      </c>
-      <c r="D13" s="34">
-        <v>1.2</v>
-      </c>
-      <c r="E13" s="37">
-        <v>672.48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="54" x14ac:dyDescent="0.3">
-      <c r="A14" s="36" t="s">
-        <v>451</v>
-      </c>
-      <c r="B14" s="31" t="s">
-        <v>454</v>
-      </c>
-      <c r="C14" s="35" t="s">
-        <v>395</v>
-      </c>
-      <c r="D14" s="34">
-        <v>1.2</v>
-      </c>
-      <c r="E14" s="37">
-        <v>672.48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="A15" s="36" t="s">
-        <v>449</v>
-      </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="35" t="s">
-        <v>447</v>
-      </c>
-      <c r="D15" s="34">
-        <v>0.25</v>
-      </c>
-      <c r="E15" s="37">
-        <v>140.1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="36" x14ac:dyDescent="0.3">
-      <c r="A16" s="36" t="s">
-        <v>448</v>
-      </c>
-      <c r="B16" s="31"/>
-      <c r="C16" s="35" t="s">
-        <v>447</v>
-      </c>
-      <c r="D16" s="34">
-        <v>0.15</v>
-      </c>
-      <c r="E16" s="34">
-        <v>84.06</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="54" x14ac:dyDescent="0.3">
-      <c r="A17" s="33" t="s">
-        <v>446</v>
-      </c>
-      <c r="B17" s="31" t="s">
-        <v>441</v>
-      </c>
-      <c r="C17" s="31" t="s">
-        <v>395</v>
-      </c>
-      <c r="D17" s="32">
-        <v>1</v>
-      </c>
-      <c r="E17" s="32">
+      <c r="K5" s="54" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="58">
+        <v>1.05</v>
+      </c>
+      <c r="B6" s="59" t="s">
+        <v>498</v>
+      </c>
+      <c r="C6" s="59">
+        <v>22.1</v>
+      </c>
+      <c r="D6" s="67"/>
+      <c r="E6" s="60">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="F6" s="61" t="s">
+        <v>498</v>
+      </c>
+      <c r="G6" s="61">
+        <v>62.6</v>
+      </c>
+      <c r="H6" s="67"/>
+      <c r="I6" s="60">
+        <v>3.01</v>
+      </c>
+      <c r="J6" s="61" t="s">
+        <v>498</v>
+      </c>
+      <c r="K6" s="61">
+        <v>62.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="60">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="B7" s="61" t="s">
+        <v>498</v>
+      </c>
+      <c r="C7" s="61">
+        <v>61.9</v>
+      </c>
+      <c r="D7" s="67"/>
+      <c r="E7" s="58">
+        <v>2.02</v>
+      </c>
+      <c r="F7" s="59" t="s">
+        <v>498</v>
+      </c>
+      <c r="G7" s="59">
+        <v>89</v>
+      </c>
+      <c r="H7" s="67"/>
+      <c r="I7" s="58">
+        <v>3.02</v>
+      </c>
+      <c r="J7" s="59" t="s">
+        <v>498</v>
+      </c>
+      <c r="K7" s="59">
+        <v>89.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="58">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8" s="59" t="s">
+        <v>498</v>
+      </c>
+      <c r="C8" s="59">
+        <v>63.3</v>
+      </c>
+      <c r="D8" s="67"/>
+      <c r="E8" s="60">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="F8" s="61" t="s">
+        <v>498</v>
+      </c>
+      <c r="G8" s="61">
+        <v>39.4</v>
+      </c>
+      <c r="H8" s="67"/>
+      <c r="I8" s="60">
+        <v>3.03</v>
+      </c>
+      <c r="J8" s="61" t="s">
+        <v>498</v>
+      </c>
+      <c r="K8" s="61">
+        <v>29.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="60">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="B9" s="61" t="s">
+        <v>498</v>
+      </c>
+      <c r="C9" s="61">
+        <v>63.4</v>
+      </c>
+      <c r="D9" s="67"/>
+      <c r="E9" s="58">
+        <v>2.04</v>
+      </c>
+      <c r="F9" s="59" t="s">
+        <v>498</v>
+      </c>
+      <c r="G9" s="59">
+        <v>63</v>
+      </c>
+      <c r="H9" s="67"/>
+      <c r="I9" s="58">
+        <v>3.04</v>
+      </c>
+      <c r="J9" s="59" t="s">
+        <v>498</v>
+      </c>
+      <c r="K9" s="59">
+        <v>64.599999999999994</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="58">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="B10" s="59" t="s">
+        <v>498</v>
+      </c>
+      <c r="C10" s="59">
+        <v>131.19999999999999</v>
+      </c>
+      <c r="D10" s="67"/>
+      <c r="E10" s="60">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="F10" s="61" t="s">
+        <v>498</v>
+      </c>
+      <c r="G10" s="61">
+        <v>64.400000000000006</v>
+      </c>
+      <c r="H10" s="67"/>
+      <c r="I10" s="60">
+        <v>3.05</v>
+      </c>
+      <c r="J10" s="61" t="s">
+        <v>498</v>
+      </c>
+      <c r="K10" s="61">
+        <v>63.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="60">
+        <v>1.19</v>
+      </c>
+      <c r="B11" s="61" t="s">
+        <v>499</v>
+      </c>
+      <c r="C11" s="61">
+        <v>20.7</v>
+      </c>
+      <c r="D11" s="67"/>
+      <c r="E11" s="58">
+        <v>2.06</v>
+      </c>
+      <c r="F11" s="59" t="s">
+        <v>498</v>
+      </c>
+      <c r="G11" s="59">
+        <v>63.3</v>
+      </c>
+      <c r="H11" s="67"/>
+      <c r="I11" s="58">
+        <v>3.06</v>
+      </c>
+      <c r="J11" s="59" t="s">
+        <v>498</v>
+      </c>
+      <c r="K11" s="59">
+        <v>65.400000000000006</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="58">
+        <v>1.61</v>
+      </c>
+      <c r="B12" s="59" t="s">
+        <v>499</v>
+      </c>
+      <c r="C12" s="59">
+        <v>16.8</v>
+      </c>
+      <c r="D12" s="67"/>
+      <c r="E12" s="60">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="F12" s="61" t="s">
+        <v>498</v>
+      </c>
+      <c r="G12" s="61">
+        <v>63.3</v>
+      </c>
+      <c r="H12" s="67"/>
+      <c r="I12" s="60">
+        <v>3.07</v>
+      </c>
+      <c r="J12" s="61" t="s">
+        <v>498</v>
+      </c>
+      <c r="K12" s="61">
+        <v>63.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="60">
+        <v>1.64</v>
+      </c>
+      <c r="B13" s="61" t="s">
+        <v>499</v>
+      </c>
+      <c r="C13" s="61">
+        <v>24</v>
+      </c>
+      <c r="D13" s="67"/>
+      <c r="E13" s="58">
+        <v>2.08</v>
+      </c>
+      <c r="F13" s="59" t="s">
+        <v>498</v>
+      </c>
+      <c r="G13" s="59">
+        <v>78.599999999999994</v>
+      </c>
+      <c r="H13" s="67"/>
+      <c r="I13" s="58">
+        <v>3.08</v>
+      </c>
+      <c r="J13" s="59" t="s">
+        <v>498</v>
+      </c>
+      <c r="K13" s="59">
+        <v>64.3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="58">
+        <v>1.67</v>
+      </c>
+      <c r="B14" s="59" t="s">
+        <v>499</v>
+      </c>
+      <c r="C14" s="59">
+        <v>51.3</v>
+      </c>
+      <c r="D14" s="67"/>
+      <c r="E14" s="60">
+        <v>2.12</v>
+      </c>
+      <c r="F14" s="61" t="s">
+        <v>498</v>
+      </c>
+      <c r="G14" s="61">
+        <v>27</v>
+      </c>
+      <c r="H14" s="67"/>
+      <c r="I14" s="60">
+        <v>3.12</v>
+      </c>
+      <c r="J14" s="61" t="s">
+        <v>15</v>
+      </c>
+      <c r="K14" s="61">
+        <v>244.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="60">
+        <v>1.68</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>499</v>
+      </c>
+      <c r="C15" s="61">
+        <v>54.6</v>
+      </c>
+      <c r="D15" s="67"/>
+      <c r="E15" s="58">
+        <v>2.15</v>
+      </c>
+      <c r="F15" s="59" t="s">
+        <v>498</v>
+      </c>
+      <c r="G15" s="59">
         <v>28</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="36" x14ac:dyDescent="0.3">
-      <c r="A18" s="36" t="s">
-        <v>448</v>
-      </c>
-      <c r="B18" s="31"/>
-      <c r="C18" s="35" t="s">
-        <v>447</v>
-      </c>
-      <c r="D18" s="34">
-        <v>0.15</v>
-      </c>
-      <c r="E18" s="34">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="A19" s="36" t="s">
-        <v>449</v>
-      </c>
-      <c r="B19" s="31"/>
-      <c r="C19" s="35" t="s">
-        <v>447</v>
-      </c>
-      <c r="D19" s="34">
-        <v>0.25</v>
-      </c>
-      <c r="E19" s="37">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="54" x14ac:dyDescent="0.3">
-      <c r="A20" s="36" t="s">
-        <v>451</v>
-      </c>
-      <c r="B20" s="31" t="s">
-        <v>453</v>
-      </c>
-      <c r="C20" s="35" t="s">
-        <v>395</v>
-      </c>
-      <c r="D20" s="34">
-        <v>1.2</v>
-      </c>
-      <c r="E20" s="37">
-        <v>33.6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="36" x14ac:dyDescent="0.3">
-      <c r="A21" s="38" t="s">
-        <v>452</v>
-      </c>
-      <c r="B21" s="31"/>
-      <c r="C21" s="35" t="s">
-        <v>447</v>
-      </c>
-      <c r="D21" s="34">
-        <v>1.2</v>
-      </c>
-      <c r="E21" s="37">
-        <v>33.6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="54" x14ac:dyDescent="0.3">
-      <c r="A22" s="33" t="s">
-        <v>446</v>
-      </c>
-      <c r="B22" s="31" t="s">
-        <v>440</v>
-      </c>
-      <c r="C22" s="31" t="s">
-        <v>395</v>
-      </c>
-      <c r="D22" s="32">
-        <v>1</v>
-      </c>
-      <c r="E22" s="32">
-        <v>207.1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="36" x14ac:dyDescent="0.3">
-      <c r="A23" s="38" t="s">
-        <v>452</v>
-      </c>
-      <c r="B23" s="31"/>
-      <c r="C23" s="35" t="s">
-        <v>447</v>
-      </c>
-      <c r="D23" s="34">
-        <v>1.2</v>
-      </c>
-      <c r="E23" s="37">
-        <v>248.52</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="54" x14ac:dyDescent="0.3">
-      <c r="A24" s="36" t="s">
-        <v>451</v>
-      </c>
-      <c r="B24" s="31" t="s">
-        <v>450</v>
-      </c>
-      <c r="C24" s="35" t="s">
-        <v>395</v>
-      </c>
-      <c r="D24" s="34">
-        <v>1.2</v>
-      </c>
-      <c r="E24" s="37">
-        <v>248.52</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="A25" s="36" t="s">
-        <v>449</v>
-      </c>
-      <c r="B25" s="31"/>
-      <c r="C25" s="35" t="s">
-        <v>447</v>
-      </c>
-      <c r="D25" s="34">
-        <v>0.25</v>
-      </c>
-      <c r="E25" s="37">
-        <v>51.774999999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="36" x14ac:dyDescent="0.3">
-      <c r="A26" s="36" t="s">
-        <v>448</v>
-      </c>
-      <c r="B26" s="31"/>
-      <c r="C26" s="35" t="s">
-        <v>447</v>
-      </c>
-      <c r="D26" s="34">
-        <v>0.15</v>
-      </c>
-      <c r="E26" s="34">
-        <v>31.065000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="54" x14ac:dyDescent="0.3">
-      <c r="A27" s="33" t="s">
-        <v>446</v>
-      </c>
-      <c r="B27" s="31" t="s">
-        <v>439</v>
-      </c>
-      <c r="C27" s="31" t="s">
-        <v>395</v>
-      </c>
-      <c r="D27" s="32">
-        <v>1</v>
-      </c>
-      <c r="E27" s="32">
-        <v>207.5</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" ht="18" x14ac:dyDescent="0.3">
-      <c r="B34" s="31" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" ht="18" x14ac:dyDescent="0.3">
-      <c r="B35" s="31" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2" ht="18" x14ac:dyDescent="0.3">
-      <c r="B36" s="31" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2" ht="18" x14ac:dyDescent="0.3">
-      <c r="B37" s="31" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2" ht="18" x14ac:dyDescent="0.3">
-      <c r="B38" s="31" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2" ht="18" x14ac:dyDescent="0.3">
-      <c r="B39" s="31" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2" ht="36" x14ac:dyDescent="0.3">
-      <c r="B40" s="31" t="s">
-        <v>439</v>
+      <c r="H15" s="67"/>
+      <c r="I15" s="58">
+        <v>3.13</v>
+      </c>
+      <c r="J15" s="59" t="s">
+        <v>498</v>
+      </c>
+      <c r="K15" s="59">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="58">
+        <v>1.69</v>
+      </c>
+      <c r="B16" s="59" t="s">
+        <v>499</v>
+      </c>
+      <c r="C16" s="59">
+        <v>18.5</v>
+      </c>
+      <c r="D16" s="67"/>
+      <c r="E16" s="60">
+        <v>2.19</v>
+      </c>
+      <c r="F16" s="61" t="s">
+        <v>500</v>
+      </c>
+      <c r="G16" s="61">
+        <v>359.3</v>
+      </c>
+      <c r="H16" s="67"/>
+      <c r="I16" s="60">
+        <v>3.18</v>
+      </c>
+      <c r="J16" s="61" t="s">
+        <v>498</v>
+      </c>
+      <c r="K16" s="61">
+        <v>107.2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="60">
+        <v>1.73</v>
+      </c>
+      <c r="B17" s="61" t="s">
+        <v>499</v>
+      </c>
+      <c r="C17" s="61">
+        <v>51.2</v>
+      </c>
+      <c r="D17" s="67"/>
+      <c r="E17" s="58">
+        <v>2.21</v>
+      </c>
+      <c r="F17" s="59" t="s">
+        <v>498</v>
+      </c>
+      <c r="G17" s="59">
+        <v>14</v>
+      </c>
+      <c r="H17" s="67"/>
+      <c r="I17" s="58">
+        <v>3.19</v>
+      </c>
+      <c r="J17" s="59" t="s">
+        <v>498</v>
+      </c>
+      <c r="K17" s="59">
+        <v>113.7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="58">
+        <v>1.74</v>
+      </c>
+      <c r="B18" s="59" t="s">
+        <v>499</v>
+      </c>
+      <c r="C18" s="59">
+        <v>55.3</v>
+      </c>
+      <c r="D18" s="67"/>
+      <c r="E18" s="60">
+        <v>2.27</v>
+      </c>
+      <c r="F18" s="61" t="s">
+        <v>498</v>
+      </c>
+      <c r="G18" s="61">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="H18" s="67"/>
+      <c r="I18" s="60">
+        <v>3.23</v>
+      </c>
+      <c r="J18" s="61" t="s">
+        <v>499</v>
+      </c>
+      <c r="K18" s="61">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="60">
+        <v>1.77</v>
+      </c>
+      <c r="B19" s="61" t="s">
+        <v>499</v>
+      </c>
+      <c r="C19" s="61">
+        <v>41.2</v>
+      </c>
+      <c r="D19" s="67"/>
+      <c r="E19" s="58">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="F19" s="59" t="s">
+        <v>498</v>
+      </c>
+      <c r="G19" s="59">
+        <v>192.9</v>
+      </c>
+      <c r="H19" s="67"/>
+      <c r="I19" s="58">
+        <v>3.25</v>
+      </c>
+      <c r="J19" s="59" t="s">
+        <v>499</v>
+      </c>
+      <c r="K19" s="59">
+        <v>52.1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="58">
+        <v>1.78</v>
+      </c>
+      <c r="B20" s="59" t="s">
+        <v>499</v>
+      </c>
+      <c r="C20" s="59">
+        <v>59.3</v>
+      </c>
+      <c r="D20" s="67"/>
+      <c r="E20" s="60">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F20" s="61" t="s">
+        <v>498</v>
+      </c>
+      <c r="G20" s="61">
+        <v>115.5</v>
+      </c>
+      <c r="H20" s="67"/>
+      <c r="I20" s="60">
+        <v>3.26</v>
+      </c>
+      <c r="J20" s="61" t="s">
+        <v>499</v>
+      </c>
+      <c r="K20" s="61">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B21" s="68" t="s">
+        <v>492</v>
+      </c>
+      <c r="C21" s="57">
+        <f>SUM(C6:C20)</f>
+        <v>734.8</v>
+      </c>
+      <c r="D21" s="67"/>
+      <c r="E21" s="58">
+        <v>2.37</v>
+      </c>
+      <c r="F21" s="59" t="s">
+        <v>499</v>
+      </c>
+      <c r="G21" s="59">
+        <v>21.6</v>
+      </c>
+      <c r="H21" s="67"/>
+      <c r="I21" s="58">
+        <v>3.28</v>
+      </c>
+      <c r="J21" s="59" t="s">
+        <v>499</v>
+      </c>
+      <c r="K21" s="59">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="67"/>
+      <c r="B22" s="67"/>
+      <c r="C22" s="67"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="60">
+        <v>2.4</v>
+      </c>
+      <c r="F22" s="61" t="s">
+        <v>499</v>
+      </c>
+      <c r="G22" s="61">
+        <v>51.3</v>
+      </c>
+      <c r="H22" s="67"/>
+      <c r="I22" s="60">
+        <v>3.29</v>
+      </c>
+      <c r="J22" s="61" t="s">
+        <v>499</v>
+      </c>
+      <c r="K22" s="61">
+        <v>51.6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="67"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="58">
+        <v>2.41</v>
+      </c>
+      <c r="F23" s="59" t="s">
+        <v>499</v>
+      </c>
+      <c r="G23" s="59">
+        <v>56.6</v>
+      </c>
+      <c r="H23" s="67"/>
+      <c r="I23" s="58">
+        <v>3.3</v>
+      </c>
+      <c r="J23" s="59" t="s">
+        <v>499</v>
+      </c>
+      <c r="K23" s="59">
+        <v>56.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="67"/>
+      <c r="B24" s="67"/>
+      <c r="C24" s="67"/>
+      <c r="D24" s="67"/>
+      <c r="E24" s="60">
+        <v>2.42</v>
+      </c>
+      <c r="F24" s="61" t="s">
+        <v>499</v>
+      </c>
+      <c r="G24" s="61">
+        <v>21.5</v>
+      </c>
+      <c r="H24" s="67"/>
+      <c r="I24" s="60">
+        <v>3.33</v>
+      </c>
+      <c r="J24" s="61" t="s">
+        <v>499</v>
+      </c>
+      <c r="K24" s="61">
+        <v>75.400000000000006</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="67"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="58">
+        <v>2.44</v>
+      </c>
+      <c r="F25" s="59" t="s">
+        <v>499</v>
+      </c>
+      <c r="G25" s="59">
+        <v>51.3</v>
+      </c>
+      <c r="H25" s="67"/>
+      <c r="I25" s="58">
+        <v>3.34</v>
+      </c>
+      <c r="J25" s="59" t="s">
+        <v>499</v>
+      </c>
+      <c r="K25" s="59">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="67"/>
+      <c r="B26" s="67"/>
+      <c r="C26" s="67"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="60">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="F26" s="61" t="s">
+        <v>499</v>
+      </c>
+      <c r="G26" s="61">
+        <v>56.3</v>
+      </c>
+      <c r="H26" s="67"/>
+      <c r="I26" s="60">
+        <v>3.35</v>
+      </c>
+      <c r="J26" s="61" t="s">
+        <v>499</v>
+      </c>
+      <c r="K26" s="61">
+        <v>74.900000000000006</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="67"/>
+      <c r="B27" s="67"/>
+      <c r="C27" s="67"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="58">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="F27" s="59" t="s">
+        <v>500</v>
+      </c>
+      <c r="G27" s="59">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="H27" s="67"/>
+      <c r="I27" s="58">
+        <v>3.41</v>
+      </c>
+      <c r="J27" s="59" t="s">
+        <v>499</v>
+      </c>
+      <c r="K27" s="59">
+        <v>36.4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="67"/>
+      <c r="B28" s="67"/>
+      <c r="C28" s="67"/>
+      <c r="D28" s="67"/>
+      <c r="E28" s="58">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="F28" s="59" t="s">
+        <v>499</v>
+      </c>
+      <c r="G28" s="59">
+        <v>75.2</v>
+      </c>
+      <c r="H28" s="67"/>
+      <c r="I28" s="60">
+        <v>3.42</v>
+      </c>
+      <c r="J28" s="61" t="s">
+        <v>499</v>
+      </c>
+      <c r="K28" s="61">
+        <v>59.7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="67"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="67"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="58">
+        <v>2.58</v>
+      </c>
+      <c r="F29" s="59" t="s">
+        <v>498</v>
+      </c>
+      <c r="G29" s="59">
+        <v>76.2</v>
+      </c>
+      <c r="H29" s="67"/>
+      <c r="I29" s="58">
+        <v>3.44</v>
+      </c>
+      <c r="J29" s="59" t="s">
+        <v>498</v>
+      </c>
+      <c r="K29" s="59">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="67"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="67"/>
+      <c r="D30" s="67"/>
+      <c r="F30" s="68" t="s">
+        <v>492</v>
+      </c>
+      <c r="G30" s="57">
+        <f>SUM(G6:G29)</f>
+        <v>1764.9999999999998</v>
+      </c>
+      <c r="H30" s="67"/>
+      <c r="I30" s="62">
+        <v>3.45</v>
+      </c>
+      <c r="J30" s="63" t="s">
+        <v>498</v>
+      </c>
+      <c r="K30" s="63">
+        <v>82.7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="67"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="67"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="67"/>
+      <c r="F31" s="67"/>
+      <c r="G31" s="67"/>
+      <c r="H31" s="67"/>
+      <c r="J31" s="68" t="s">
+        <v>492</v>
+      </c>
+      <c r="K31" s="57">
+        <f>SUM(K6:K30)</f>
+        <v>1599.7000000000003</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="8.88671875" style="22"/>
-    <col min="2" max="2" width="40" style="26" customWidth="1"/>
-    <col min="3" max="3" width="12" style="28" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="22"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="44" t="s">
-        <v>396</v>
-      </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="46"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="21" t="s">
-        <v>390</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>398</v>
-      </c>
-      <c r="C2" s="27" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="21">
-        <v>1</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>411</v>
-      </c>
-      <c r="C3" s="27">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="36" x14ac:dyDescent="0.35">
-      <c r="A4" s="21">
-        <v>2</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="27">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="21">
-        <v>3</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>412</v>
-      </c>
-      <c r="C5" s="27">
-        <v>28.9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="21">
-        <v>4</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>413</v>
-      </c>
-      <c r="C6" s="27">
-        <v>30.6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="36" x14ac:dyDescent="0.35">
-      <c r="A7" s="21">
-        <v>5</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="C7" s="27">
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="16.8" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="21">
-        <v>6</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>414</v>
-      </c>
-      <c r="C8" s="27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="36" x14ac:dyDescent="0.35">
-      <c r="A9" s="21">
-        <v>7</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>415</v>
-      </c>
-      <c r="C9" s="27">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="21">
-        <v>8</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>416</v>
-      </c>
-      <c r="C10" s="27">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="21">
-        <v>9</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>417</v>
-      </c>
-      <c r="C11" s="27">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="21">
-        <v>10</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>418</v>
-      </c>
-      <c r="C12" s="27">
-        <v>30.6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="21">
-        <v>11</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>419</v>
-      </c>
-      <c r="C13" s="27">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="21">
-        <v>12</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>420</v>
-      </c>
-      <c r="C14" s="27">
-        <v>30.6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="36" x14ac:dyDescent="0.35">
-      <c r="A15" s="21">
-        <v>13</v>
-      </c>
-      <c r="B15" s="24" t="s">
-        <v>421</v>
-      </c>
-      <c r="C15" s="27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="21">
-        <v>14</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="C16" s="27">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="36" x14ac:dyDescent="0.35">
-      <c r="A17" s="21">
-        <v>15</v>
-      </c>
-      <c r="B17" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="C17" s="27">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="21">
-        <v>16</v>
-      </c>
-      <c r="B18" s="24" t="s">
-        <v>422</v>
-      </c>
-      <c r="C18" s="27">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="21">
-        <v>17</v>
-      </c>
-      <c r="B19" s="24" t="s">
-        <v>423</v>
-      </c>
-      <c r="C19" s="27">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="21">
-        <v>18</v>
-      </c>
-      <c r="B20" s="24" t="s">
-        <v>424</v>
-      </c>
-      <c r="C20" s="27">
-        <v>30.6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="36" x14ac:dyDescent="0.35">
-      <c r="A21" s="21">
-        <v>19</v>
-      </c>
-      <c r="B21" s="24" t="s">
-        <v>155</v>
-      </c>
-      <c r="C21" s="27">
-        <v>5.74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="21">
-        <v>20</v>
-      </c>
-      <c r="B22" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="C22" s="27">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="36" x14ac:dyDescent="0.35">
-      <c r="A23" s="21">
-        <v>21</v>
-      </c>
-      <c r="B23" s="24" t="s">
-        <v>425</v>
-      </c>
-      <c r="C23" s="27">
-        <v>5.74</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="36" x14ac:dyDescent="0.35">
-      <c r="A24" s="21">
-        <v>22</v>
-      </c>
-      <c r="B24" s="24" t="s">
-        <v>426</v>
-      </c>
-      <c r="C24" s="27">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="21"/>
-      <c r="B25" s="25" t="s">
-        <v>400</v>
-      </c>
-      <c r="C25" s="27">
-        <f>SUM(C3:C24)</f>
-        <v>256.98</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+  <mergeCells count="11">
+    <mergeCell ref="H5:H31"/>
+    <mergeCell ref="E31:G31"/>
+    <mergeCell ref="D5:D31"/>
+    <mergeCell ref="A22:C31"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J1:K3"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/kronshtatsky/floors/floor_table.xlsx
+++ b/kronshtatsky/floors/floor_table.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16056" windowHeight="8520" firstSheet="5" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16056" windowHeight="8520" firstSheet="7" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,8 @@
     <sheet name="4.Защ_вин" sheetId="11" r:id="rId9"/>
     <sheet name="Из КП" sheetId="7" r:id="rId10"/>
     <sheet name="2-пом" sheetId="5" r:id="rId11"/>
+    <sheet name="5.1-Л4" sheetId="13" r:id="rId12"/>
+    <sheet name="5.2 Л-1" sheetId="15" r:id="rId13"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="509">
   <si>
     <t>№ пом.</t>
   </si>
@@ -1548,6 +1550,26 @@
   </si>
   <si>
     <t>л-1</t>
+  </si>
+  <si>
+    <t>2 этаж. Тип: Л-4</t>
+  </si>
+  <si>
+    <t>№ пом</t>
+  </si>
+  <si>
+    <t>2.19</t>
+  </si>
+  <si>
+    <t>№ п/п</t>
+  </si>
+  <si>
+    <t>Устройство покрытия пола из линолеума.
+Включая защиту ДВП</t>
+  </si>
+  <si>
+    <t>1, 2, 3 этажи. 
+Тип: Л-1</t>
   </si>
 </sst>
 </file>
@@ -1735,7 +1757,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1839,12 +1861,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1957,27 +2008,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2012,42 +2042,150 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Финансовый" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="7">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2122,6 +2260,14 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -2174,14 +2320,14 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Таблица1" displayName="Таблица1" ref="A2:D216" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A2:D216">
     <filterColumn colId="1">
-      <colorFilter dxfId="0" cellColor="0"/>
+      <colorFilter dxfId="4" cellColor="0"/>
     </filterColumn>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" name="№ п. п." dataDxfId="4"/>
-    <tableColumn id="2" name="№ пом." dataDxfId="3"/>
-    <tableColumn id="3" name="Тип пола" dataDxfId="2"/>
-    <tableColumn id="4" name="Площадь, м2." dataDxfId="1"/>
+    <tableColumn id="1" name="№ п. п." dataDxfId="3"/>
+    <tableColumn id="2" name="№ пом." dataDxfId="2"/>
+    <tableColumn id="3" name="Тип пола" dataDxfId="1"/>
+    <tableColumn id="4" name="Площадь, м2." dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2471,11 +2617,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="I1" s="46" t="s">
+      <c r="I1" s="67" t="s">
         <v>195</v>
       </c>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
       <c r="O1" s="1" t="s">
         <v>378</v>
       </c>
@@ -3417,7 +3563,7 @@
       <c r="A35" s="2">
         <v>55</v>
       </c>
-      <c r="B35" s="53">
+      <c r="B35" s="46">
         <v>1.05</v>
       </c>
       <c r="C35" s="2" t="s">
@@ -3555,7 +3701,7 @@
       <c r="A39" s="2">
         <v>56</v>
       </c>
-      <c r="B39" s="53">
+      <c r="B39" s="46">
         <v>1.0900000000000001</v>
       </c>
       <c r="C39" s="2" t="s">
@@ -3588,7 +3734,7 @@
       <c r="A40" s="2">
         <v>57</v>
       </c>
-      <c r="B40" s="53">
+      <c r="B40" s="46">
         <v>1.1000000000000001</v>
       </c>
       <c r="C40" s="2" t="s">
@@ -3621,7 +3767,7 @@
       <c r="A41" s="2">
         <v>58</v>
       </c>
-      <c r="B41" s="53">
+      <c r="B41" s="46">
         <v>1.1100000000000001</v>
       </c>
       <c r="C41" s="2" t="s">
@@ -3654,7 +3800,7 @@
       <c r="A42" s="2">
         <v>59</v>
       </c>
-      <c r="B42" s="53">
+      <c r="B42" s="46">
         <v>1.1200000000000001</v>
       </c>
       <c r="C42" s="2" t="s">
@@ -3891,7 +4037,7 @@
       <c r="A49" s="2">
         <v>60</v>
       </c>
-      <c r="B49" s="53">
+      <c r="B49" s="46">
         <v>1.19</v>
       </c>
       <c r="C49" s="2" t="s">
@@ -4188,7 +4334,7 @@
       <c r="A58" s="2">
         <v>66</v>
       </c>
-      <c r="B58" s="53">
+      <c r="B58" s="46">
         <v>1.28</v>
       </c>
       <c r="C58" s="2" t="s">
@@ -4221,7 +4367,7 @@
       <c r="A59" s="2">
         <v>39</v>
       </c>
-      <c r="B59" s="53">
+      <c r="B59" s="46">
         <v>1.29</v>
       </c>
       <c r="C59" s="2" t="s">
@@ -5528,7 +5674,7 @@
       <c r="A91" s="2">
         <v>71</v>
       </c>
-      <c r="B91" s="53">
+      <c r="B91" s="46">
         <v>1.61</v>
       </c>
       <c r="C91" s="2" t="s">
@@ -5663,7 +5809,7 @@
       <c r="A94" s="2">
         <v>84</v>
       </c>
-      <c r="B94" s="53">
+      <c r="B94" s="46">
         <v>1.64</v>
       </c>
       <c r="C94" s="2" t="s">
@@ -5795,7 +5941,7 @@
       <c r="A97" s="2">
         <v>85</v>
       </c>
-      <c r="B97" s="53">
+      <c r="B97" s="46">
         <v>1.67</v>
       </c>
       <c r="C97" s="2" t="s">
@@ -5839,7 +5985,7 @@
       <c r="A98" s="2">
         <v>86</v>
       </c>
-      <c r="B98" s="53">
+      <c r="B98" s="46">
         <v>1.68</v>
       </c>
       <c r="C98" s="2" t="s">
@@ -5883,7 +6029,7 @@
       <c r="A99" s="2">
         <v>87</v>
       </c>
-      <c r="B99" s="53">
+      <c r="B99" s="46">
         <v>1.69</v>
       </c>
       <c r="C99" s="2" t="s">
@@ -6062,7 +6208,7 @@
       <c r="A103" s="2">
         <v>88</v>
       </c>
-      <c r="B103" s="53">
+      <c r="B103" s="46">
         <v>1.73</v>
       </c>
       <c r="C103" s="2" t="s">
@@ -6106,7 +6252,7 @@
       <c r="A104" s="2">
         <v>89</v>
       </c>
-      <c r="B104" s="53">
+      <c r="B104" s="46">
         <v>1.74</v>
       </c>
       <c r="C104" s="2" t="s">
@@ -6238,7 +6384,7 @@
       <c r="A107" s="2">
         <v>73</v>
       </c>
-      <c r="B107" s="53">
+      <c r="B107" s="46">
         <v>1.77</v>
       </c>
       <c r="C107" s="2" t="s">
@@ -6279,7 +6425,7 @@
       </c>
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B108" s="53">
+      <c r="B108" s="46">
         <v>1.78</v>
       </c>
       <c r="C108" s="2" t="s">
@@ -6508,7 +6654,7 @@
       <c r="A113" s="2">
         <v>143</v>
       </c>
-      <c r="B113" s="53">
+      <c r="B113" s="46">
         <v>2.0099999999999998</v>
       </c>
       <c r="C113" s="2" t="s">
@@ -6555,7 +6701,7 @@
       <c r="A114" s="2">
         <v>144</v>
       </c>
-      <c r="B114" s="53">
+      <c r="B114" s="46">
         <v>2.02</v>
       </c>
       <c r="C114" s="2" t="s">
@@ -6602,7 +6748,7 @@
       <c r="A115" s="2">
         <v>145</v>
       </c>
-      <c r="B115" s="53">
+      <c r="B115" s="46">
         <v>2.0299999999999998</v>
       </c>
       <c r="C115" s="2" t="s">
@@ -6649,7 +6795,7 @@
       <c r="A116" s="2">
         <v>146</v>
       </c>
-      <c r="B116" s="53">
+      <c r="B116" s="46">
         <v>2.04</v>
       </c>
       <c r="C116" s="2" t="s">
@@ -6696,7 +6842,7 @@
       <c r="A117" s="2">
         <v>147</v>
       </c>
-      <c r="B117" s="53">
+      <c r="B117" s="46">
         <v>2.0499999999999998</v>
       </c>
       <c r="C117" s="2" t="s">
@@ -6743,7 +6889,7 @@
       <c r="A118" s="2">
         <v>148</v>
       </c>
-      <c r="B118" s="53">
+      <c r="B118" s="46">
         <v>2.06</v>
       </c>
       <c r="C118" s="2" t="s">
@@ -6790,7 +6936,7 @@
       <c r="A119" s="2">
         <v>149</v>
       </c>
-      <c r="B119" s="53">
+      <c r="B119" s="46">
         <v>2.0699999999999998</v>
       </c>
       <c r="C119" s="2" t="s">
@@ -6837,7 +6983,7 @@
       <c r="A120" s="2">
         <v>75</v>
       </c>
-      <c r="B120" s="53">
+      <c r="B120" s="46">
         <v>2.08</v>
       </c>
       <c r="C120" s="2" t="s">
@@ -7013,7 +7159,7 @@
       <c r="A124" s="2">
         <v>150</v>
       </c>
-      <c r="B124" s="53">
+      <c r="B124" s="46">
         <v>2.12</v>
       </c>
       <c r="C124" s="2" t="s">
@@ -7148,7 +7294,7 @@
       <c r="A127" s="2">
         <v>151</v>
       </c>
-      <c r="B127" s="53">
+      <c r="B127" s="46">
         <v>2.15</v>
       </c>
       <c r="C127" s="2" t="s">
@@ -7330,7 +7476,7 @@
       <c r="A131" s="2">
         <v>184</v>
       </c>
-      <c r="B131" s="53">
+      <c r="B131" s="46">
         <v>2.19</v>
       </c>
       <c r="C131" s="2" t="s">
@@ -7418,7 +7564,7 @@
       <c r="A133" s="2">
         <v>153</v>
       </c>
-      <c r="B133" s="53">
+      <c r="B133" s="46">
         <v>2.21</v>
       </c>
       <c r="C133" s="2" t="s">
@@ -7685,7 +7831,7 @@
       <c r="A139" s="2">
         <v>76</v>
       </c>
-      <c r="B139" s="53">
+      <c r="B139" s="46">
         <v>2.27</v>
       </c>
       <c r="C139" s="2" t="s">
@@ -7729,7 +7875,7 @@
       <c r="A140" s="2">
         <v>154</v>
       </c>
-      <c r="B140" s="53">
+      <c r="B140" s="46">
         <v>2.2799999999999998</v>
       </c>
       <c r="C140" s="2" t="s">
@@ -7823,7 +7969,7 @@
       <c r="A142" s="2">
         <v>77</v>
       </c>
-      <c r="B142" s="53">
+      <c r="B142" s="46">
         <v>2.2999999999999998</v>
       </c>
       <c r="C142" s="2" t="s">
@@ -8149,7 +8295,7 @@
       <c r="A149" s="2">
         <v>156</v>
       </c>
-      <c r="B149" s="53">
+      <c r="B149" s="46">
         <v>2.37</v>
       </c>
       <c r="C149" s="2" t="s">
@@ -8284,7 +8430,7 @@
       <c r="A152" s="2">
         <v>157</v>
       </c>
-      <c r="B152" s="53">
+      <c r="B152" s="46">
         <v>2.4</v>
       </c>
       <c r="C152" s="2" t="s">
@@ -8331,7 +8477,7 @@
       <c r="A153" s="2">
         <v>90</v>
       </c>
-      <c r="B153" s="53">
+      <c r="B153" s="46">
         <v>2.41</v>
       </c>
       <c r="C153" s="2" t="s">
@@ -8375,7 +8521,7 @@
       <c r="A154" s="2">
         <v>158</v>
       </c>
-      <c r="B154" s="53">
+      <c r="B154" s="46">
         <v>2.42</v>
       </c>
       <c r="C154" s="2" t="s">
@@ -8466,7 +8612,7 @@
       <c r="A156" s="2">
         <v>159</v>
       </c>
-      <c r="B156" s="53">
+      <c r="B156" s="46">
         <v>2.44</v>
       </c>
       <c r="C156" s="2" t="s">
@@ -8513,7 +8659,7 @@
       <c r="A157" s="2">
         <v>91</v>
       </c>
-      <c r="B157" s="53">
+      <c r="B157" s="46">
         <v>2.4500000000000002</v>
       </c>
       <c r="C157" s="2" t="s">
@@ -8601,7 +8747,7 @@
       <c r="A159" s="2">
         <v>160</v>
       </c>
-      <c r="B159" s="53">
+      <c r="B159" s="46">
         <v>2.4700000000000002</v>
       </c>
       <c r="C159" s="2" t="s">
@@ -8648,7 +8794,7 @@
       <c r="A160" s="2">
         <v>161</v>
       </c>
-      <c r="B160" s="53">
+      <c r="B160" s="46">
         <v>2.48</v>
       </c>
       <c r="C160" s="2" t="s">
@@ -8695,7 +8841,7 @@
       <c r="A161" s="2">
         <v>162</v>
       </c>
-      <c r="B161" s="53">
+      <c r="B161" s="46">
         <v>2.4900000000000002</v>
       </c>
       <c r="C161" s="2" t="s">
@@ -8742,7 +8888,7 @@
       <c r="A162" s="2">
         <v>163</v>
       </c>
-      <c r="B162" s="53">
+      <c r="B162" s="46">
         <v>2.5</v>
       </c>
       <c r="C162" s="2" t="s">
@@ -8786,7 +8932,7 @@
       <c r="A163" s="2">
         <v>78</v>
       </c>
-      <c r="B163" s="53">
+      <c r="B163" s="46">
         <v>2.5099999999999998</v>
       </c>
       <c r="C163" s="2" t="s">
@@ -9015,7 +9161,7 @@
       <c r="A168" s="2">
         <v>79</v>
       </c>
-      <c r="B168" s="53">
+      <c r="B168" s="46">
         <v>2.56</v>
       </c>
       <c r="C168" s="2" t="s">
@@ -9106,7 +9252,7 @@
       <c r="A170" s="2">
         <v>164</v>
       </c>
-      <c r="B170" s="53">
+      <c r="B170" s="46">
         <v>2.58</v>
       </c>
       <c r="C170" s="2" t="s">
@@ -9153,7 +9299,7 @@
       <c r="A171" s="2">
         <v>165</v>
       </c>
-      <c r="B171" s="53">
+      <c r="B171" s="46">
         <v>3.01</v>
       </c>
       <c r="C171" s="2" t="s">
@@ -9200,7 +9346,7 @@
       <c r="A172" s="2">
         <v>166</v>
       </c>
-      <c r="B172" s="53">
+      <c r="B172" s="46">
         <v>3.02</v>
       </c>
       <c r="C172" s="2" t="s">
@@ -9247,7 +9393,7 @@
       <c r="A173" s="2">
         <v>167</v>
       </c>
-      <c r="B173" s="53">
+      <c r="B173" s="46">
         <v>3.03</v>
       </c>
       <c r="C173" s="2" t="s">
@@ -9294,7 +9440,7 @@
       <c r="A174" s="2">
         <v>168</v>
       </c>
-      <c r="B174" s="53">
+      <c r="B174" s="46">
         <v>3.04</v>
       </c>
       <c r="C174" s="2" t="s">
@@ -9341,7 +9487,7 @@
       <c r="A175" s="2">
         <v>169</v>
       </c>
-      <c r="B175" s="53">
+      <c r="B175" s="46">
         <v>3.05</v>
       </c>
       <c r="C175" s="2" t="s">
@@ -9388,7 +9534,7 @@
       <c r="A176" s="2">
         <v>170</v>
       </c>
-      <c r="B176" s="53">
+      <c r="B176" s="46">
         <v>3.06</v>
       </c>
       <c r="C176" s="2" t="s">
@@ -9435,7 +9581,7 @@
       <c r="A177" s="2">
         <v>171</v>
       </c>
-      <c r="B177" s="53">
+      <c r="B177" s="46">
         <v>3.07</v>
       </c>
       <c r="C177" s="2" t="s">
@@ -9482,7 +9628,7 @@
       <c r="A178" s="2">
         <v>172</v>
       </c>
-      <c r="B178" s="53">
+      <c r="B178" s="46">
         <v>3.08</v>
       </c>
       <c r="C178" s="2" t="s">
@@ -9661,7 +9807,7 @@
       <c r="A182" s="2">
         <v>173</v>
       </c>
-      <c r="B182" s="53">
+      <c r="B182" s="46">
         <v>3.12</v>
       </c>
       <c r="C182" s="2" t="s">
@@ -9708,7 +9854,7 @@
       <c r="A183" s="2">
         <v>174</v>
       </c>
-      <c r="B183" s="53">
+      <c r="B183" s="46">
         <v>3.13</v>
       </c>
       <c r="C183" s="2" t="s">
@@ -9937,7 +10083,7 @@
       <c r="A188" s="2">
         <v>175</v>
       </c>
-      <c r="B188" s="53">
+      <c r="B188" s="46">
         <v>3.18</v>
       </c>
       <c r="C188" s="2" t="s">
@@ -9984,7 +10130,7 @@
       <c r="A189" s="2">
         <v>80</v>
       </c>
-      <c r="B189" s="53">
+      <c r="B189" s="46">
         <v>3.19</v>
       </c>
       <c r="C189" s="2" t="s">
@@ -10169,7 +10315,7 @@
       <c r="A193" s="2">
         <v>176</v>
       </c>
-      <c r="B193" s="53">
+      <c r="B193" s="46">
         <v>3.23</v>
       </c>
       <c r="C193" s="2" t="s">
@@ -10260,7 +10406,7 @@
       <c r="A195" s="2">
         <v>177</v>
       </c>
-      <c r="B195" s="53">
+      <c r="B195" s="46">
         <v>3.25</v>
       </c>
       <c r="C195" s="2" t="s">
@@ -10307,7 +10453,7 @@
       <c r="A196" s="2">
         <v>92</v>
       </c>
-      <c r="B196" s="53">
+      <c r="B196" s="46">
         <v>3.26</v>
       </c>
       <c r="C196" s="2" t="s">
@@ -10395,7 +10541,7 @@
       <c r="A198" s="2">
         <v>178</v>
       </c>
-      <c r="B198" s="53">
+      <c r="B198" s="46">
         <v>3.28</v>
       </c>
       <c r="C198" s="2" t="s">
@@ -10442,7 +10588,7 @@
       <c r="A199" s="2">
         <v>179</v>
       </c>
-      <c r="B199" s="53">
+      <c r="B199" s="46">
         <v>3.29</v>
       </c>
       <c r="C199" s="2" t="s">
@@ -10489,7 +10635,7 @@
       <c r="A200" s="2">
         <v>93</v>
       </c>
-      <c r="B200" s="53">
+      <c r="B200" s="46">
         <v>3.3</v>
       </c>
       <c r="C200" s="2" t="s">
@@ -10621,7 +10767,7 @@
       <c r="A203" s="2">
         <v>180</v>
       </c>
-      <c r="B203" s="53">
+      <c r="B203" s="46">
         <v>3.33</v>
       </c>
       <c r="C203" s="2" t="s">
@@ -10668,7 +10814,7 @@
       <c r="A204" s="2">
         <v>181</v>
       </c>
-      <c r="B204" s="53">
+      <c r="B204" s="46">
         <v>3.34</v>
       </c>
       <c r="C204" s="2" t="s">
@@ -10715,7 +10861,7 @@
       <c r="A205" s="2">
         <v>182</v>
       </c>
-      <c r="B205" s="53">
+      <c r="B205" s="46">
         <v>3.35</v>
       </c>
       <c r="C205" s="2" t="s">
@@ -10994,7 +11140,7 @@
       <c r="A211" s="2">
         <v>81</v>
       </c>
-      <c r="B211" s="53">
+      <c r="B211" s="46">
         <v>3.41</v>
       </c>
       <c r="C211" s="2" t="s">
@@ -11038,7 +11184,7 @@
       <c r="A212" s="2">
         <v>82</v>
       </c>
-      <c r="B212" s="53">
+      <c r="B212" s="46">
         <v>3.42</v>
       </c>
       <c r="C212" s="2" t="s">
@@ -11129,7 +11275,7 @@
       <c r="A214" s="2">
         <v>83</v>
       </c>
-      <c r="B214" s="53">
+      <c r="B214" s="46">
         <v>3.44</v>
       </c>
       <c r="C214" s="2" t="s">
@@ -11173,7 +11319,7 @@
       <c r="A215" s="2">
         <v>183</v>
       </c>
-      <c r="B215" s="53">
+      <c r="B215" s="46">
         <v>3.45</v>
       </c>
       <c r="C215" s="2" t="s">
@@ -12018,7 +12164,7 @@
         <v>4.68</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="36" x14ac:dyDescent="0.3">
       <c r="A9" s="36" t="s">
         <v>449</v>
       </c>
@@ -12097,7 +12243,7 @@
         <v>672.48</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="54" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A14" s="36" t="s">
         <v>451</v>
       </c>
@@ -12114,7 +12260,7 @@
         <v>672.48</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="36" x14ac:dyDescent="0.3">
       <c r="A15" s="36" t="s">
         <v>449</v>
       </c>
@@ -12176,7 +12322,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="36" x14ac:dyDescent="0.3">
       <c r="A19" s="36" t="s">
         <v>449</v>
       </c>
@@ -12255,7 +12401,7 @@
         <v>248.52</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="54" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A24" s="36" t="s">
         <v>451</v>
       </c>
@@ -12272,7 +12418,7 @@
         <v>248.52</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" ht="36" x14ac:dyDescent="0.3">
       <c r="A25" s="36" t="s">
         <v>449</v>
       </c>
@@ -12371,11 +12517,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="68" t="s">
         <v>396</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="49"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="70"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
@@ -12643,6 +12789,611 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" style="63" customWidth="1"/>
+    <col min="2" max="2" width="30.6640625" style="63" customWidth="1"/>
+    <col min="3" max="3" width="12.21875" style="63" customWidth="1"/>
+    <col min="4" max="4" width="9.5546875" style="63" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" style="63" customWidth="1"/>
+    <col min="6" max="6" width="11.44140625" style="63" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="63"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="80" t="s">
+        <v>389</v>
+      </c>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="C2" s="81" t="s">
+        <v>392</v>
+      </c>
+      <c r="D2" s="82"/>
+      <c r="E2" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="51" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="17">
+        <v>1</v>
+      </c>
+      <c r="B3" s="61" t="s">
+        <v>507</v>
+      </c>
+      <c r="C3" s="83" t="s">
+        <v>503</v>
+      </c>
+      <c r="D3" s="84"/>
+      <c r="E3" s="62" t="s">
+        <v>395</v>
+      </c>
+      <c r="F3" s="20">
+        <f>F6+F7</f>
+        <v>431.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="87"/>
+      <c r="B4" s="87"/>
+      <c r="C4" s="87"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="85"/>
+      <c r="B5" s="86"/>
+      <c r="C5" s="17" t="s">
+        <v>506</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>504</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="85"/>
+      <c r="B6" s="86"/>
+      <c r="C6" s="17">
+        <v>1</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>505</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>395</v>
+      </c>
+      <c r="F6" s="17">
+        <v>357.18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="85"/>
+      <c r="B7" s="86"/>
+      <c r="C7" s="17">
+        <v>2</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>475</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>395</v>
+      </c>
+      <c r="F7" s="17">
+        <v>74.12</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="A5:B7"/>
+    <mergeCell ref="A4:F4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.21875" style="50" customWidth="1"/>
+    <col min="2" max="2" width="7.88671875" style="50" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" style="50" customWidth="1"/>
+    <col min="4" max="4" width="4.109375" style="50" customWidth="1"/>
+    <col min="5" max="5" width="7.109375" style="50" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" style="50" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" style="50" customWidth="1"/>
+    <col min="8" max="8" width="5.33203125" style="50" customWidth="1"/>
+    <col min="9" max="9" width="7.88671875" style="50" customWidth="1"/>
+    <col min="10" max="10" width="7.44140625" style="50" customWidth="1"/>
+    <col min="11" max="11" width="11.88671875" style="50" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="50"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="97" t="s">
+        <v>389</v>
+      </c>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="98"/>
+    </row>
+    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="48" t="s">
+        <v>390</v>
+      </c>
+      <c r="B2" s="78" t="s">
+        <v>391</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="99" t="s">
+        <v>392</v>
+      </c>
+      <c r="H2" s="100"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="49" t="s">
+        <v>393</v>
+      </c>
+      <c r="K2" s="66" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="60">
+        <v>1</v>
+      </c>
+      <c r="B3" s="79" t="s">
+        <v>497</v>
+      </c>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="104" t="s">
+        <v>508</v>
+      </c>
+      <c r="H3" s="102"/>
+      <c r="I3" s="103"/>
+      <c r="J3" s="64" t="s">
+        <v>395</v>
+      </c>
+      <c r="K3" s="65">
+        <f>C16+G12+K17</f>
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="74"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="74"/>
+      <c r="K4" s="74"/>
+    </row>
+    <row r="5" spans="1:11" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="88" t="s">
+        <v>496</v>
+      </c>
+      <c r="B5" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="88" t="s">
+        <v>495</v>
+      </c>
+      <c r="D5" s="74"/>
+      <c r="E5" s="88" t="s">
+        <v>496</v>
+      </c>
+      <c r="F5" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="88" t="s">
+        <v>495</v>
+      </c>
+      <c r="H5" s="95"/>
+      <c r="I5" s="88" t="s">
+        <v>496</v>
+      </c>
+      <c r="J5" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" s="88" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="89">
+        <v>1.19</v>
+      </c>
+      <c r="B6" s="90" t="s">
+        <v>499</v>
+      </c>
+      <c r="C6" s="90">
+        <v>20.7</v>
+      </c>
+      <c r="D6" s="74"/>
+      <c r="E6" s="91">
+        <v>2.37</v>
+      </c>
+      <c r="F6" s="92" t="s">
+        <v>499</v>
+      </c>
+      <c r="G6" s="92">
+        <v>21.6</v>
+      </c>
+      <c r="H6" s="95"/>
+      <c r="I6" s="89">
+        <v>3.23</v>
+      </c>
+      <c r="J6" s="90" t="s">
+        <v>499</v>
+      </c>
+      <c r="K6" s="90">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="91">
+        <v>1.61</v>
+      </c>
+      <c r="B7" s="92" t="s">
+        <v>499</v>
+      </c>
+      <c r="C7" s="92">
+        <v>16.8</v>
+      </c>
+      <c r="D7" s="74"/>
+      <c r="E7" s="89">
+        <v>2.4</v>
+      </c>
+      <c r="F7" s="90" t="s">
+        <v>499</v>
+      </c>
+      <c r="G7" s="90">
+        <v>51.3</v>
+      </c>
+      <c r="H7" s="95"/>
+      <c r="I7" s="91">
+        <v>3.25</v>
+      </c>
+      <c r="J7" s="92" t="s">
+        <v>499</v>
+      </c>
+      <c r="K7" s="92">
+        <v>52.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="89">
+        <v>1.64</v>
+      </c>
+      <c r="B8" s="90" t="s">
+        <v>499</v>
+      </c>
+      <c r="C8" s="90">
+        <v>24</v>
+      </c>
+      <c r="D8" s="74"/>
+      <c r="E8" s="91">
+        <v>2.41</v>
+      </c>
+      <c r="F8" s="92" t="s">
+        <v>499</v>
+      </c>
+      <c r="G8" s="92">
+        <v>56.6</v>
+      </c>
+      <c r="H8" s="95"/>
+      <c r="I8" s="89">
+        <v>3.26</v>
+      </c>
+      <c r="J8" s="90" t="s">
+        <v>499</v>
+      </c>
+      <c r="K8" s="90">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="91">
+        <v>1.67</v>
+      </c>
+      <c r="B9" s="92" t="s">
+        <v>499</v>
+      </c>
+      <c r="C9" s="92">
+        <v>51.3</v>
+      </c>
+      <c r="D9" s="74"/>
+      <c r="E9" s="89">
+        <v>2.42</v>
+      </c>
+      <c r="F9" s="90" t="s">
+        <v>499</v>
+      </c>
+      <c r="G9" s="90">
+        <v>21.5</v>
+      </c>
+      <c r="H9" s="95"/>
+      <c r="I9" s="91">
+        <v>3.28</v>
+      </c>
+      <c r="J9" s="92" t="s">
+        <v>499</v>
+      </c>
+      <c r="K9" s="92">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="89">
+        <v>1.68</v>
+      </c>
+      <c r="B10" s="90" t="s">
+        <v>499</v>
+      </c>
+      <c r="C10" s="90">
+        <v>54.6</v>
+      </c>
+      <c r="D10" s="74"/>
+      <c r="E10" s="91">
+        <v>2.44</v>
+      </c>
+      <c r="F10" s="92" t="s">
+        <v>499</v>
+      </c>
+      <c r="G10" s="92">
+        <v>51.3</v>
+      </c>
+      <c r="H10" s="95"/>
+      <c r="I10" s="89">
+        <v>3.29</v>
+      </c>
+      <c r="J10" s="90" t="s">
+        <v>499</v>
+      </c>
+      <c r="K10" s="90">
+        <v>51.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="91">
+        <v>1.69</v>
+      </c>
+      <c r="B11" s="92" t="s">
+        <v>499</v>
+      </c>
+      <c r="C11" s="92">
+        <v>18.5</v>
+      </c>
+      <c r="D11" s="74"/>
+      <c r="E11" s="89">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="F11" s="90" t="s">
+        <v>499</v>
+      </c>
+      <c r="G11" s="90">
+        <v>56.3</v>
+      </c>
+      <c r="H11" s="95"/>
+      <c r="I11" s="91">
+        <v>3.3</v>
+      </c>
+      <c r="J11" s="92" t="s">
+        <v>499</v>
+      </c>
+      <c r="K11" s="92">
+        <v>56.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="89">
+        <v>1.73</v>
+      </c>
+      <c r="B12" s="90" t="s">
+        <v>499</v>
+      </c>
+      <c r="C12" s="90">
+        <v>51.2</v>
+      </c>
+      <c r="D12" s="74"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="94" t="s">
+        <v>492</v>
+      </c>
+      <c r="G12" s="93">
+        <f>SUM(G6:G11)</f>
+        <v>258.60000000000002</v>
+      </c>
+      <c r="H12" s="95"/>
+      <c r="I12" s="89">
+        <v>3.33</v>
+      </c>
+      <c r="J12" s="90" t="s">
+        <v>499</v>
+      </c>
+      <c r="K12" s="90">
+        <v>75.400000000000006</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="91">
+        <v>1.74</v>
+      </c>
+      <c r="B13" s="92" t="s">
+        <v>499</v>
+      </c>
+      <c r="C13" s="92">
+        <v>55.3</v>
+      </c>
+      <c r="D13" s="74"/>
+      <c r="E13" s="96"/>
+      <c r="F13" s="96"/>
+      <c r="G13" s="96"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="91">
+        <v>3.34</v>
+      </c>
+      <c r="J13" s="92" t="s">
+        <v>499</v>
+      </c>
+      <c r="K13" s="92">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="89">
+        <v>1.77</v>
+      </c>
+      <c r="B14" s="90" t="s">
+        <v>499</v>
+      </c>
+      <c r="C14" s="90">
+        <v>41.2</v>
+      </c>
+      <c r="D14" s="74"/>
+      <c r="E14" s="105"/>
+      <c r="F14" s="105"/>
+      <c r="G14" s="105"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="89">
+        <v>3.35</v>
+      </c>
+      <c r="J14" s="90" t="s">
+        <v>499</v>
+      </c>
+      <c r="K14" s="90">
+        <v>74.900000000000006</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="91">
+        <v>1.78</v>
+      </c>
+      <c r="B15" s="92" t="s">
+        <v>499</v>
+      </c>
+      <c r="C15" s="92">
+        <v>59.3</v>
+      </c>
+      <c r="D15" s="74"/>
+      <c r="E15" s="105"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="105"/>
+      <c r="H15" s="95"/>
+      <c r="I15" s="91">
+        <v>3.41</v>
+      </c>
+      <c r="J15" s="92" t="s">
+        <v>499</v>
+      </c>
+      <c r="K15" s="92">
+        <v>36.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="93"/>
+      <c r="B16" s="94" t="s">
+        <v>492</v>
+      </c>
+      <c r="C16" s="93">
+        <f>SUM(C6:C15)</f>
+        <v>392.90000000000003</v>
+      </c>
+      <c r="D16" s="74"/>
+      <c r="E16" s="105"/>
+      <c r="F16" s="105"/>
+      <c r="G16" s="105"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="89">
+        <v>3.42</v>
+      </c>
+      <c r="J16" s="90" t="s">
+        <v>499</v>
+      </c>
+      <c r="K16" s="90">
+        <v>59.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="96"/>
+      <c r="B17" s="96"/>
+      <c r="C17" s="96"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="105"/>
+      <c r="F17" s="105"/>
+      <c r="G17" s="105"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="93"/>
+      <c r="J17" s="94" t="s">
+        <v>492</v>
+      </c>
+      <c r="K17" s="93">
+        <f>SUM(K6:K16)</f>
+        <v>513.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="E13:G17"/>
+    <mergeCell ref="H5:H17"/>
+    <mergeCell ref="D5:D17"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="A4:K4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13005,7 +13756,7 @@
       <c r="B22">
         <v>51</v>
       </c>
-      <c r="C22" s="72">
+      <c r="C22" s="59">
         <v>37.1</v>
       </c>
     </row>
@@ -13061,7 +13812,7 @@
       <c r="B29">
         <v>56</v>
       </c>
-      <c r="C29" s="72">
+      <c r="C29" s="59">
         <v>60.9</v>
       </c>
     </row>
@@ -13077,7 +13828,7 @@
       <c r="B31">
         <v>50</v>
       </c>
-      <c r="C31" s="72">
+      <c r="C31" s="59">
         <v>6.2</v>
       </c>
     </row>
@@ -13085,7 +13836,7 @@
       <c r="B32">
         <v>48</v>
       </c>
-      <c r="C32" s="72">
+      <c r="C32" s="59">
         <v>7</v>
       </c>
     </row>
@@ -13112,11 +13863,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="68" t="s">
         <v>396</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="49"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="70"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
@@ -13354,13 +14105,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="71" t="s">
         <v>389</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="52"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="73"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
@@ -13819,869 +14570,869 @@
   <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.21875" style="57" customWidth="1"/>
-    <col min="2" max="2" width="7.88671875" style="57" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" style="57" customWidth="1"/>
-    <col min="4" max="4" width="4.109375" style="57" customWidth="1"/>
-    <col min="5" max="5" width="7.109375" style="57" customWidth="1"/>
-    <col min="6" max="6" width="7.6640625" style="57" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" style="57" customWidth="1"/>
-    <col min="8" max="8" width="5.33203125" style="57" customWidth="1"/>
-    <col min="9" max="9" width="7.88671875" style="57" customWidth="1"/>
-    <col min="10" max="10" width="8.21875" style="57" customWidth="1"/>
-    <col min="11" max="11" width="9.88671875" style="57" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="57"/>
+    <col min="1" max="1" width="7.21875" style="50" customWidth="1"/>
+    <col min="2" max="2" width="7.88671875" style="50" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" style="50" customWidth="1"/>
+    <col min="4" max="4" width="4.109375" style="50" customWidth="1"/>
+    <col min="5" max="5" width="7.109375" style="50" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" style="50" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" style="50" customWidth="1"/>
+    <col min="8" max="8" width="5.33203125" style="50" customWidth="1"/>
+    <col min="9" max="9" width="7.88671875" style="50" customWidth="1"/>
+    <col min="10" max="10" width="8.21875" style="50" customWidth="1"/>
+    <col min="11" max="11" width="9.88671875" style="50" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="50"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="75" t="s">
         <v>389</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="48" t="s">
         <v>390</v>
       </c>
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="78" t="s">
         <v>391</v>
       </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="56" t="s">
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="49" t="s">
         <v>393</v>
       </c>
-      <c r="H2" s="70" t="s">
+      <c r="H2" s="77" t="s">
         <v>394</v>
       </c>
-      <c r="I2" s="70"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="74"/>
     </row>
     <row r="3" spans="1:11" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="64">
+      <c r="A3" s="57">
         <v>1</v>
       </c>
-      <c r="B3" s="69" t="s">
+      <c r="B3" s="79" t="s">
         <v>497</v>
       </c>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="64" t="s">
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="57" t="s">
         <v>395</v>
       </c>
-      <c r="H3" s="71">
+      <c r="H3" s="76">
         <f>C21+G30+K31</f>
         <v>4099.5</v>
       </c>
-      <c r="I3" s="71"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="74"/>
+      <c r="K3" s="74"/>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="67"/>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
+      <c r="A4" s="74"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="74"/>
+      <c r="K4" s="74"/>
     </row>
     <row r="5" spans="1:11" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="47" t="s">
         <v>496</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="47" t="s">
         <v>495</v>
       </c>
-      <c r="D5" s="67"/>
-      <c r="E5" s="54" t="s">
+      <c r="D5" s="74"/>
+      <c r="E5" s="47" t="s">
         <v>496</v>
       </c>
-      <c r="F5" s="54" t="s">
+      <c r="F5" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="G5" s="54" t="s">
+      <c r="G5" s="47" t="s">
         <v>495</v>
       </c>
-      <c r="H5" s="67"/>
-      <c r="I5" s="54" t="s">
+      <c r="H5" s="74"/>
+      <c r="I5" s="47" t="s">
         <v>496</v>
       </c>
-      <c r="J5" s="54" t="s">
+      <c r="J5" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="K5" s="54" t="s">
+      <c r="K5" s="47" t="s">
         <v>495</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="58">
+      <c r="A6" s="51">
         <v>1.05</v>
       </c>
-      <c r="B6" s="59" t="s">
+      <c r="B6" s="52" t="s">
         <v>498</v>
       </c>
-      <c r="C6" s="59">
+      <c r="C6" s="52">
         <v>22.1</v>
       </c>
-      <c r="D6" s="67"/>
-      <c r="E6" s="60">
+      <c r="D6" s="74"/>
+      <c r="E6" s="53">
         <v>2.0099999999999998</v>
       </c>
-      <c r="F6" s="61" t="s">
+      <c r="F6" s="54" t="s">
         <v>498</v>
       </c>
-      <c r="G6" s="61">
+      <c r="G6" s="54">
         <v>62.6</v>
       </c>
-      <c r="H6" s="67"/>
-      <c r="I6" s="60">
+      <c r="H6" s="74"/>
+      <c r="I6" s="53">
         <v>3.01</v>
       </c>
-      <c r="J6" s="61" t="s">
+      <c r="J6" s="54" t="s">
         <v>498</v>
       </c>
-      <c r="K6" s="61">
+      <c r="K6" s="54">
         <v>62.8</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="60">
+      <c r="A7" s="53">
         <v>1.0900000000000001</v>
       </c>
-      <c r="B7" s="61" t="s">
+      <c r="B7" s="54" t="s">
         <v>498</v>
       </c>
-      <c r="C7" s="61">
+      <c r="C7" s="54">
         <v>61.9</v>
       </c>
-      <c r="D7" s="67"/>
-      <c r="E7" s="58">
+      <c r="D7" s="74"/>
+      <c r="E7" s="51">
         <v>2.02</v>
       </c>
-      <c r="F7" s="59" t="s">
+      <c r="F7" s="52" t="s">
         <v>498</v>
       </c>
-      <c r="G7" s="59">
+      <c r="G7" s="52">
         <v>89</v>
       </c>
-      <c r="H7" s="67"/>
-      <c r="I7" s="58">
+      <c r="H7" s="74"/>
+      <c r="I7" s="51">
         <v>3.02</v>
       </c>
-      <c r="J7" s="59" t="s">
+      <c r="J7" s="52" t="s">
         <v>498</v>
       </c>
-      <c r="K7" s="59">
+      <c r="K7" s="52">
         <v>89.1</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="58">
+      <c r="A8" s="51">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B8" s="59" t="s">
+      <c r="B8" s="52" t="s">
         <v>498</v>
       </c>
-      <c r="C8" s="59">
+      <c r="C8" s="52">
         <v>63.3</v>
       </c>
-      <c r="D8" s="67"/>
-      <c r="E8" s="60">
+      <c r="D8" s="74"/>
+      <c r="E8" s="53">
         <v>2.0299999999999998</v>
       </c>
-      <c r="F8" s="61" t="s">
+      <c r="F8" s="54" t="s">
         <v>498</v>
       </c>
-      <c r="G8" s="61">
+      <c r="G8" s="54">
         <v>39.4</v>
       </c>
-      <c r="H8" s="67"/>
-      <c r="I8" s="60">
+      <c r="H8" s="74"/>
+      <c r="I8" s="53">
         <v>3.03</v>
       </c>
-      <c r="J8" s="61" t="s">
+      <c r="J8" s="54" t="s">
         <v>498</v>
       </c>
-      <c r="K8" s="61">
+      <c r="K8" s="54">
         <v>29.7</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="60">
+      <c r="A9" s="53">
         <v>1.1100000000000001</v>
       </c>
-      <c r="B9" s="61" t="s">
+      <c r="B9" s="54" t="s">
         <v>498</v>
       </c>
-      <c r="C9" s="61">
+      <c r="C9" s="54">
         <v>63.4</v>
       </c>
-      <c r="D9" s="67"/>
-      <c r="E9" s="58">
+      <c r="D9" s="74"/>
+      <c r="E9" s="51">
         <v>2.04</v>
       </c>
-      <c r="F9" s="59" t="s">
+      <c r="F9" s="52" t="s">
         <v>498</v>
       </c>
-      <c r="G9" s="59">
+      <c r="G9" s="52">
         <v>63</v>
       </c>
-      <c r="H9" s="67"/>
-      <c r="I9" s="58">
+      <c r="H9" s="74"/>
+      <c r="I9" s="51">
         <v>3.04</v>
       </c>
-      <c r="J9" s="59" t="s">
+      <c r="J9" s="52" t="s">
         <v>498</v>
       </c>
-      <c r="K9" s="59">
+      <c r="K9" s="52">
         <v>64.599999999999994</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="58">
+      <c r="A10" s="51">
         <v>1.1200000000000001</v>
       </c>
-      <c r="B10" s="59" t="s">
+      <c r="B10" s="52" t="s">
         <v>498</v>
       </c>
-      <c r="C10" s="59">
+      <c r="C10" s="52">
         <v>131.19999999999999</v>
       </c>
-      <c r="D10" s="67"/>
-      <c r="E10" s="60">
+      <c r="D10" s="74"/>
+      <c r="E10" s="53">
         <v>2.0499999999999998</v>
       </c>
-      <c r="F10" s="61" t="s">
+      <c r="F10" s="54" t="s">
         <v>498</v>
       </c>
-      <c r="G10" s="61">
+      <c r="G10" s="54">
         <v>64.400000000000006</v>
       </c>
-      <c r="H10" s="67"/>
-      <c r="I10" s="60">
+      <c r="H10" s="74"/>
+      <c r="I10" s="53">
         <v>3.05</v>
       </c>
-      <c r="J10" s="61" t="s">
+      <c r="J10" s="54" t="s">
         <v>498</v>
       </c>
-      <c r="K10" s="61">
+      <c r="K10" s="54">
         <v>63.8</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="60">
+      <c r="A11" s="53">
         <v>1.19</v>
       </c>
-      <c r="B11" s="61" t="s">
+      <c r="B11" s="54" t="s">
         <v>499</v>
       </c>
-      <c r="C11" s="61">
+      <c r="C11" s="54">
         <v>20.7</v>
       </c>
-      <c r="D11" s="67"/>
-      <c r="E11" s="58">
+      <c r="D11" s="74"/>
+      <c r="E11" s="51">
         <v>2.06</v>
       </c>
-      <c r="F11" s="59" t="s">
+      <c r="F11" s="52" t="s">
         <v>498</v>
       </c>
-      <c r="G11" s="59">
+      <c r="G11" s="52">
         <v>63.3</v>
       </c>
-      <c r="H11" s="67"/>
-      <c r="I11" s="58">
+      <c r="H11" s="74"/>
+      <c r="I11" s="51">
         <v>3.06</v>
       </c>
-      <c r="J11" s="59" t="s">
+      <c r="J11" s="52" t="s">
         <v>498</v>
       </c>
-      <c r="K11" s="59">
+      <c r="K11" s="52">
         <v>65.400000000000006</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="58">
+      <c r="A12" s="51">
         <v>1.61</v>
       </c>
-      <c r="B12" s="59" t="s">
+      <c r="B12" s="52" t="s">
         <v>499</v>
       </c>
-      <c r="C12" s="59">
+      <c r="C12" s="52">
         <v>16.8</v>
       </c>
-      <c r="D12" s="67"/>
-      <c r="E12" s="60">
+      <c r="D12" s="74"/>
+      <c r="E12" s="53">
         <v>2.0699999999999998</v>
       </c>
-      <c r="F12" s="61" t="s">
+      <c r="F12" s="54" t="s">
         <v>498</v>
       </c>
-      <c r="G12" s="61">
+      <c r="G12" s="54">
         <v>63.3</v>
       </c>
-      <c r="H12" s="67"/>
-      <c r="I12" s="60">
+      <c r="H12" s="74"/>
+      <c r="I12" s="53">
         <v>3.07</v>
       </c>
-      <c r="J12" s="61" t="s">
+      <c r="J12" s="54" t="s">
         <v>498</v>
       </c>
-      <c r="K12" s="61">
+      <c r="K12" s="54">
         <v>63.7</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="60">
+      <c r="A13" s="53">
         <v>1.64</v>
       </c>
-      <c r="B13" s="61" t="s">
+      <c r="B13" s="54" t="s">
         <v>499</v>
       </c>
-      <c r="C13" s="61">
+      <c r="C13" s="54">
         <v>24</v>
       </c>
-      <c r="D13" s="67"/>
-      <c r="E13" s="58">
+      <c r="D13" s="74"/>
+      <c r="E13" s="51">
         <v>2.08</v>
       </c>
-      <c r="F13" s="59" t="s">
+      <c r="F13" s="52" t="s">
         <v>498</v>
       </c>
-      <c r="G13" s="59">
+      <c r="G13" s="52">
         <v>78.599999999999994</v>
       </c>
-      <c r="H13" s="67"/>
-      <c r="I13" s="58">
+      <c r="H13" s="74"/>
+      <c r="I13" s="51">
         <v>3.08</v>
       </c>
-      <c r="J13" s="59" t="s">
+      <c r="J13" s="52" t="s">
         <v>498</v>
       </c>
-      <c r="K13" s="59">
+      <c r="K13" s="52">
         <v>64.3</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="58">
+      <c r="A14" s="51">
         <v>1.67</v>
       </c>
-      <c r="B14" s="59" t="s">
+      <c r="B14" s="52" t="s">
         <v>499</v>
       </c>
-      <c r="C14" s="59">
+      <c r="C14" s="52">
         <v>51.3</v>
       </c>
-      <c r="D14" s="67"/>
-      <c r="E14" s="60">
+      <c r="D14" s="74"/>
+      <c r="E14" s="53">
         <v>2.12</v>
       </c>
-      <c r="F14" s="61" t="s">
+      <c r="F14" s="54" t="s">
         <v>498</v>
       </c>
-      <c r="G14" s="61">
+      <c r="G14" s="54">
         <v>27</v>
       </c>
-      <c r="H14" s="67"/>
-      <c r="I14" s="60">
+      <c r="H14" s="74"/>
+      <c r="I14" s="53">
         <v>3.12</v>
       </c>
-      <c r="J14" s="61" t="s">
+      <c r="J14" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="K14" s="61">
+      <c r="K14" s="54">
         <v>244.5</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="60">
+      <c r="A15" s="53">
         <v>1.68</v>
       </c>
-      <c r="B15" s="61" t="s">
+      <c r="B15" s="54" t="s">
         <v>499</v>
       </c>
-      <c r="C15" s="61">
+      <c r="C15" s="54">
         <v>54.6</v>
       </c>
-      <c r="D15" s="67"/>
-      <c r="E15" s="58">
+      <c r="D15" s="74"/>
+      <c r="E15" s="51">
         <v>2.15</v>
       </c>
-      <c r="F15" s="59" t="s">
+      <c r="F15" s="52" t="s">
         <v>498</v>
       </c>
-      <c r="G15" s="59">
+      <c r="G15" s="52">
         <v>28</v>
       </c>
-      <c r="H15" s="67"/>
-      <c r="I15" s="58">
+      <c r="H15" s="74"/>
+      <c r="I15" s="51">
         <v>3.13</v>
       </c>
-      <c r="J15" s="59" t="s">
+      <c r="J15" s="52" t="s">
         <v>498</v>
       </c>
-      <c r="K15" s="59">
+      <c r="K15" s="52">
         <v>13.3</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="58">
+      <c r="A16" s="51">
         <v>1.69</v>
       </c>
-      <c r="B16" s="59" t="s">
+      <c r="B16" s="52" t="s">
         <v>499</v>
       </c>
-      <c r="C16" s="59">
+      <c r="C16" s="52">
         <v>18.5</v>
       </c>
-      <c r="D16" s="67"/>
-      <c r="E16" s="60">
+      <c r="D16" s="74"/>
+      <c r="E16" s="53">
         <v>2.19</v>
       </c>
-      <c r="F16" s="61" t="s">
+      <c r="F16" s="54" t="s">
         <v>500</v>
       </c>
-      <c r="G16" s="61">
+      <c r="G16" s="54">
         <v>359.3</v>
       </c>
-      <c r="H16" s="67"/>
-      <c r="I16" s="60">
+      <c r="H16" s="74"/>
+      <c r="I16" s="53">
         <v>3.18</v>
       </c>
-      <c r="J16" s="61" t="s">
+      <c r="J16" s="54" t="s">
         <v>498</v>
       </c>
-      <c r="K16" s="61">
+      <c r="K16" s="54">
         <v>107.2</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="60">
+      <c r="A17" s="53">
         <v>1.73</v>
       </c>
-      <c r="B17" s="61" t="s">
+      <c r="B17" s="54" t="s">
         <v>499</v>
       </c>
-      <c r="C17" s="61">
+      <c r="C17" s="54">
         <v>51.2</v>
       </c>
-      <c r="D17" s="67"/>
-      <c r="E17" s="58">
+      <c r="D17" s="74"/>
+      <c r="E17" s="51">
         <v>2.21</v>
       </c>
-      <c r="F17" s="59" t="s">
+      <c r="F17" s="52" t="s">
         <v>498</v>
       </c>
-      <c r="G17" s="59">
+      <c r="G17" s="52">
         <v>14</v>
       </c>
-      <c r="H17" s="67"/>
-      <c r="I17" s="58">
+      <c r="H17" s="74"/>
+      <c r="I17" s="51">
         <v>3.19</v>
       </c>
-      <c r="J17" s="59" t="s">
+      <c r="J17" s="52" t="s">
         <v>498</v>
       </c>
-      <c r="K17" s="59">
+      <c r="K17" s="52">
         <v>113.7</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="58">
+      <c r="A18" s="51">
         <v>1.74</v>
       </c>
-      <c r="B18" s="59" t="s">
+      <c r="B18" s="52" t="s">
         <v>499</v>
       </c>
-      <c r="C18" s="59">
+      <c r="C18" s="52">
         <v>55.3</v>
       </c>
-      <c r="D18" s="67"/>
-      <c r="E18" s="60">
+      <c r="D18" s="74"/>
+      <c r="E18" s="53">
         <v>2.27</v>
       </c>
-      <c r="F18" s="61" t="s">
+      <c r="F18" s="54" t="s">
         <v>498</v>
       </c>
-      <c r="G18" s="61">
+      <c r="G18" s="54">
         <v>19.100000000000001</v>
       </c>
-      <c r="H18" s="67"/>
-      <c r="I18" s="60">
+      <c r="H18" s="74"/>
+      <c r="I18" s="53">
         <v>3.23</v>
       </c>
-      <c r="J18" s="61" t="s">
+      <c r="J18" s="54" t="s">
         <v>499</v>
       </c>
-      <c r="K18" s="61">
+      <c r="K18" s="54">
         <v>21.6</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="60">
+      <c r="A19" s="53">
         <v>1.77</v>
       </c>
-      <c r="B19" s="61" t="s">
+      <c r="B19" s="54" t="s">
         <v>499</v>
       </c>
-      <c r="C19" s="61">
+      <c r="C19" s="54">
         <v>41.2</v>
       </c>
-      <c r="D19" s="67"/>
-      <c r="E19" s="58">
+      <c r="D19" s="74"/>
+      <c r="E19" s="51">
         <v>2.2799999999999998</v>
       </c>
-      <c r="F19" s="59" t="s">
+      <c r="F19" s="52" t="s">
         <v>498</v>
       </c>
-      <c r="G19" s="59">
+      <c r="G19" s="52">
         <v>192.9</v>
       </c>
-      <c r="H19" s="67"/>
-      <c r="I19" s="58">
+      <c r="H19" s="74"/>
+      <c r="I19" s="51">
         <v>3.25</v>
       </c>
-      <c r="J19" s="59" t="s">
+      <c r="J19" s="52" t="s">
         <v>499</v>
       </c>
-      <c r="K19" s="59">
+      <c r="K19" s="52">
         <v>52.1</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="58">
+      <c r="A20" s="51">
         <v>1.78</v>
       </c>
-      <c r="B20" s="59" t="s">
+      <c r="B20" s="52" t="s">
         <v>499</v>
       </c>
-      <c r="C20" s="59">
+      <c r="C20" s="52">
         <v>59.3</v>
       </c>
-      <c r="D20" s="67"/>
-      <c r="E20" s="60">
+      <c r="D20" s="74"/>
+      <c r="E20" s="53">
         <v>2.2999999999999998</v>
       </c>
-      <c r="F20" s="61" t="s">
+      <c r="F20" s="54" t="s">
         <v>498</v>
       </c>
-      <c r="G20" s="61">
+      <c r="G20" s="54">
         <v>115.5</v>
       </c>
-      <c r="H20" s="67"/>
-      <c r="I20" s="60">
+      <c r="H20" s="74"/>
+      <c r="I20" s="53">
         <v>3.26</v>
       </c>
-      <c r="J20" s="61" t="s">
+      <c r="J20" s="54" t="s">
         <v>499</v>
       </c>
-      <c r="K20" s="61">
+      <c r="K20" s="54">
         <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B21" s="68" t="s">
+      <c r="B21" s="58" t="s">
         <v>492</v>
       </c>
-      <c r="C21" s="57">
+      <c r="C21" s="50">
         <f>SUM(C6:C20)</f>
         <v>734.8</v>
       </c>
-      <c r="D21" s="67"/>
-      <c r="E21" s="58">
+      <c r="D21" s="74"/>
+      <c r="E21" s="51">
         <v>2.37</v>
       </c>
-      <c r="F21" s="59" t="s">
+      <c r="F21" s="52" t="s">
         <v>499</v>
       </c>
-      <c r="G21" s="59">
+      <c r="G21" s="52">
         <v>21.6</v>
       </c>
-      <c r="H21" s="67"/>
-      <c r="I21" s="58">
+      <c r="H21" s="74"/>
+      <c r="I21" s="51">
         <v>3.28</v>
       </c>
-      <c r="J21" s="59" t="s">
+      <c r="J21" s="52" t="s">
         <v>499</v>
       </c>
-      <c r="K21" s="59">
+      <c r="K21" s="52">
         <v>21.6</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="67"/>
-      <c r="B22" s="67"/>
-      <c r="C22" s="67"/>
-      <c r="D22" s="67"/>
-      <c r="E22" s="60">
+      <c r="A22" s="74"/>
+      <c r="B22" s="74"/>
+      <c r="C22" s="74"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="53">
         <v>2.4</v>
       </c>
-      <c r="F22" s="61" t="s">
+      <c r="F22" s="54" t="s">
         <v>499</v>
       </c>
-      <c r="G22" s="61">
+      <c r="G22" s="54">
         <v>51.3</v>
       </c>
-      <c r="H22" s="67"/>
-      <c r="I22" s="60">
+      <c r="H22" s="74"/>
+      <c r="I22" s="53">
         <v>3.29</v>
       </c>
-      <c r="J22" s="61" t="s">
+      <c r="J22" s="54" t="s">
         <v>499</v>
       </c>
-      <c r="K22" s="61">
+      <c r="K22" s="54">
         <v>51.6</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="67"/>
-      <c r="B23" s="67"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="58">
+      <c r="A23" s="74"/>
+      <c r="B23" s="74"/>
+      <c r="C23" s="74"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="51">
         <v>2.41</v>
       </c>
-      <c r="F23" s="59" t="s">
+      <c r="F23" s="52" t="s">
         <v>499</v>
       </c>
-      <c r="G23" s="59">
+      <c r="G23" s="52">
         <v>56.6</v>
       </c>
-      <c r="H23" s="67"/>
-      <c r="I23" s="58">
+      <c r="H23" s="74"/>
+      <c r="I23" s="51">
         <v>3.3</v>
       </c>
-      <c r="J23" s="59" t="s">
+      <c r="J23" s="52" t="s">
         <v>499</v>
       </c>
-      <c r="K23" s="59">
+      <c r="K23" s="52">
         <v>56.3</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="67"/>
-      <c r="B24" s="67"/>
-      <c r="C24" s="67"/>
-      <c r="D24" s="67"/>
-      <c r="E24" s="60">
+      <c r="A24" s="74"/>
+      <c r="B24" s="74"/>
+      <c r="C24" s="74"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="53">
         <v>2.42</v>
       </c>
-      <c r="F24" s="61" t="s">
+      <c r="F24" s="54" t="s">
         <v>499</v>
       </c>
-      <c r="G24" s="61">
+      <c r="G24" s="54">
         <v>21.5</v>
       </c>
-      <c r="H24" s="67"/>
-      <c r="I24" s="60">
+      <c r="H24" s="74"/>
+      <c r="I24" s="53">
         <v>3.33</v>
       </c>
-      <c r="J24" s="61" t="s">
+      <c r="J24" s="54" t="s">
         <v>499</v>
       </c>
-      <c r="K24" s="61">
+      <c r="K24" s="54">
         <v>75.400000000000006</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="67"/>
-      <c r="B25" s="67"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="67"/>
-      <c r="E25" s="58">
+      <c r="A25" s="74"/>
+      <c r="B25" s="74"/>
+      <c r="C25" s="74"/>
+      <c r="D25" s="74"/>
+      <c r="E25" s="51">
         <v>2.44</v>
       </c>
-      <c r="F25" s="59" t="s">
+      <c r="F25" s="52" t="s">
         <v>499</v>
       </c>
-      <c r="G25" s="59">
+      <c r="G25" s="52">
         <v>51.3</v>
       </c>
-      <c r="H25" s="67"/>
-      <c r="I25" s="58">
+      <c r="H25" s="74"/>
+      <c r="I25" s="51">
         <v>3.34</v>
       </c>
-      <c r="J25" s="59" t="s">
+      <c r="J25" s="52" t="s">
         <v>499</v>
       </c>
-      <c r="K25" s="59">
+      <c r="K25" s="52">
         <v>6.9</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="67"/>
-      <c r="B26" s="67"/>
-      <c r="C26" s="67"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="60">
+      <c r="A26" s="74"/>
+      <c r="B26" s="74"/>
+      <c r="C26" s="74"/>
+      <c r="D26" s="74"/>
+      <c r="E26" s="53">
         <v>2.4500000000000002</v>
       </c>
-      <c r="F26" s="61" t="s">
+      <c r="F26" s="54" t="s">
         <v>499</v>
       </c>
-      <c r="G26" s="61">
+      <c r="G26" s="54">
         <v>56.3</v>
       </c>
-      <c r="H26" s="67"/>
-      <c r="I26" s="60">
+      <c r="H26" s="74"/>
+      <c r="I26" s="53">
         <v>3.35</v>
       </c>
-      <c r="J26" s="61" t="s">
+      <c r="J26" s="54" t="s">
         <v>499</v>
       </c>
-      <c r="K26" s="61">
+      <c r="K26" s="54">
         <v>74.900000000000006</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="67"/>
-      <c r="B27" s="67"/>
-      <c r="C27" s="67"/>
-      <c r="D27" s="67"/>
-      <c r="E27" s="58">
+      <c r="A27" s="74"/>
+      <c r="B27" s="74"/>
+      <c r="C27" s="74"/>
+      <c r="D27" s="74"/>
+      <c r="E27" s="51">
         <v>2.4700000000000002</v>
       </c>
-      <c r="F27" s="59" t="s">
+      <c r="F27" s="52" t="s">
         <v>500</v>
       </c>
-      <c r="G27" s="59">
+      <c r="G27" s="52">
         <v>75.599999999999994</v>
       </c>
-      <c r="H27" s="67"/>
-      <c r="I27" s="58">
+      <c r="H27" s="74"/>
+      <c r="I27" s="51">
         <v>3.41</v>
       </c>
-      <c r="J27" s="59" t="s">
+      <c r="J27" s="52" t="s">
         <v>499</v>
       </c>
-      <c r="K27" s="59">
+      <c r="K27" s="52">
         <v>36.4</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="67"/>
-      <c r="B28" s="67"/>
-      <c r="C28" s="67"/>
-      <c r="D28" s="67"/>
-      <c r="E28" s="58">
+      <c r="A28" s="74"/>
+      <c r="B28" s="74"/>
+      <c r="C28" s="74"/>
+      <c r="D28" s="74"/>
+      <c r="E28" s="51">
         <v>2.4900000000000002</v>
       </c>
-      <c r="F28" s="59" t="s">
+      <c r="F28" s="52" t="s">
         <v>499</v>
       </c>
-      <c r="G28" s="59">
+      <c r="G28" s="52">
         <v>75.2</v>
       </c>
-      <c r="H28" s="67"/>
-      <c r="I28" s="60">
+      <c r="H28" s="74"/>
+      <c r="I28" s="53">
         <v>3.42</v>
       </c>
-      <c r="J28" s="61" t="s">
+      <c r="J28" s="54" t="s">
         <v>499</v>
       </c>
-      <c r="K28" s="61">
+      <c r="K28" s="54">
         <v>59.7</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="67"/>
-      <c r="B29" s="67"/>
-      <c r="C29" s="67"/>
-      <c r="D29" s="67"/>
-      <c r="E29" s="58">
+      <c r="A29" s="74"/>
+      <c r="B29" s="74"/>
+      <c r="C29" s="74"/>
+      <c r="D29" s="74"/>
+      <c r="E29" s="51">
         <v>2.58</v>
       </c>
-      <c r="F29" s="59" t="s">
+      <c r="F29" s="52" t="s">
         <v>498</v>
       </c>
-      <c r="G29" s="59">
+      <c r="G29" s="52">
         <v>76.2</v>
       </c>
-      <c r="H29" s="67"/>
-      <c r="I29" s="58">
+      <c r="H29" s="74"/>
+      <c r="I29" s="51">
         <v>3.44</v>
       </c>
-      <c r="J29" s="59" t="s">
+      <c r="J29" s="52" t="s">
         <v>498</v>
       </c>
-      <c r="K29" s="59">
+      <c r="K29" s="52">
         <v>21.4</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="67"/>
-      <c r="B30" s="67"/>
-      <c r="C30" s="67"/>
-      <c r="D30" s="67"/>
-      <c r="F30" s="68" t="s">
+      <c r="A30" s="74"/>
+      <c r="B30" s="74"/>
+      <c r="C30" s="74"/>
+      <c r="D30" s="74"/>
+      <c r="F30" s="58" t="s">
         <v>492</v>
       </c>
-      <c r="G30" s="57">
+      <c r="G30" s="50">
         <f>SUM(G6:G29)</f>
         <v>1764.9999999999998</v>
       </c>
-      <c r="H30" s="67"/>
-      <c r="I30" s="62">
+      <c r="H30" s="74"/>
+      <c r="I30" s="55">
         <v>3.45</v>
       </c>
-      <c r="J30" s="63" t="s">
+      <c r="J30" s="56" t="s">
         <v>498</v>
       </c>
-      <c r="K30" s="63">
+      <c r="K30" s="56">
         <v>82.7</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="67"/>
-      <c r="B31" s="67"/>
-      <c r="C31" s="67"/>
-      <c r="D31" s="67"/>
-      <c r="E31" s="67"/>
-      <c r="F31" s="67"/>
-      <c r="G31" s="67"/>
-      <c r="H31" s="67"/>
-      <c r="J31" s="68" t="s">
+      <c r="A31" s="74"/>
+      <c r="B31" s="74"/>
+      <c r="C31" s="74"/>
+      <c r="D31" s="74"/>
+      <c r="E31" s="74"/>
+      <c r="F31" s="74"/>
+      <c r="G31" s="74"/>
+      <c r="H31" s="74"/>
+      <c r="J31" s="58" t="s">
         <v>492</v>
       </c>
-      <c r="K31" s="57">
+      <c r="K31" s="50">
         <f>SUM(K6:K30)</f>
         <v>1599.7000000000003</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="H5:H31"/>
-    <mergeCell ref="E31:G31"/>
-    <mergeCell ref="D5:D31"/>
-    <mergeCell ref="A22:C31"/>
-    <mergeCell ref="A4:K4"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="J1:K3"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B3:F3"/>
+    <mergeCell ref="H5:H31"/>
+    <mergeCell ref="E31:G31"/>
+    <mergeCell ref="D5:D31"/>
+    <mergeCell ref="A22:C31"/>
+    <mergeCell ref="A4:K4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/kronshtatsky/floors/floor_table.xlsx
+++ b/kronshtatsky/floors/floor_table.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16056" windowHeight="8520" firstSheet="7" activeTab="12"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16056" windowHeight="8520" firstSheet="9" activeTab="15"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,8 +25,11 @@
     <sheet name="2-пом" sheetId="5" r:id="rId11"/>
     <sheet name="5.1-Л4" sheetId="13" r:id="rId12"/>
     <sheet name="5.2 Л-1" sheetId="15" r:id="rId13"/>
+    <sheet name="2-Пл (2)" sheetId="16" r:id="rId14"/>
+    <sheet name="2.1КР3" sheetId="17" r:id="rId15"/>
+    <sheet name="1.1КР1" sheetId="18" r:id="rId16"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="152511" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="555">
   <si>
     <t>№ пом.</t>
   </si>
@@ -1570,6 +1573,146 @@
   <si>
     <t>1, 2, 3 этажи. 
 Тип: Л-1</t>
+  </si>
+  <si>
+    <t>1.03</t>
+  </si>
+  <si>
+    <t>1.22</t>
+  </si>
+  <si>
+    <t>1.13</t>
+  </si>
+  <si>
+    <t>1.14</t>
+  </si>
+  <si>
+    <t>1.15</t>
+  </si>
+  <si>
+    <t>2.33</t>
+  </si>
+  <si>
+    <t>2.25</t>
+  </si>
+  <si>
+    <t>2.26</t>
+  </si>
+  <si>
+    <t>2.24</t>
+  </si>
+  <si>
+    <t>2.09</t>
+  </si>
+  <si>
+    <t>2.10</t>
+  </si>
+  <si>
+    <t>2.11</t>
+  </si>
+  <si>
+    <t>2.13</t>
+  </si>
+  <si>
+    <t>2.14</t>
+  </si>
+  <si>
+    <t>2.16</t>
+  </si>
+  <si>
+    <t>2.17</t>
+  </si>
+  <si>
+    <t>2.18</t>
+  </si>
+  <si>
+    <t>3.14</t>
+  </si>
+  <si>
+    <t>3.15</t>
+  </si>
+  <si>
+    <t>3.27</t>
+  </si>
+  <si>
+    <t>3.16</t>
+  </si>
+  <si>
+    <t>3.09</t>
+  </si>
+  <si>
+    <t>3.10</t>
+  </si>
+  <si>
+    <t>3.11</t>
+  </si>
+  <si>
+    <t>3.22</t>
+  </si>
+  <si>
+    <t>1.04</t>
+  </si>
+  <si>
+    <t>1.08</t>
+  </si>
+  <si>
+    <t>1.24</t>
+  </si>
+  <si>
+    <t>1.25</t>
+  </si>
+  <si>
+    <t>1.30</t>
+  </si>
+  <si>
+    <t>1.36</t>
+  </si>
+  <si>
+    <t>1.21</t>
+  </si>
+  <si>
+    <t>1.20</t>
+  </si>
+  <si>
+    <t>1.17</t>
+  </si>
+  <si>
+    <t>1.18</t>
+  </si>
+  <si>
+    <t>1.63</t>
+  </si>
+  <si>
+    <t>1.54</t>
+  </si>
+  <si>
+    <t>1.53</t>
+  </si>
+  <si>
+    <t>1.52</t>
+  </si>
+  <si>
+    <t>1.49</t>
+  </si>
+  <si>
+    <t>1.47</t>
+  </si>
+  <si>
+    <t>1.59</t>
+  </si>
+  <si>
+    <t>1.70</t>
+  </si>
+  <si>
+    <t>2.29</t>
+  </si>
+  <si>
+    <t>1, 2, 3 этажи. 
+Тип: КР-4</t>
+  </si>
+  <si>
+    <t>1, 2 этажи. 
+Тип: КР-1</t>
   </si>
 </sst>
 </file>
@@ -1582,7 +1725,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.0\ _₽_-;\-* #,##0.0\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1724,6 +1867,14 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="4" tint="-0.249977111117893"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1757,7 +1908,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1890,12 +2041,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2065,6 +2236,51 @@
     <xf numFmtId="2" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2128,31 +2344,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2168,16 +2359,66 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2617,11 +2858,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="I1" s="67" t="s">
+      <c r="I1" s="84" t="s">
         <v>195</v>
       </c>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="84"/>
       <c r="O1" s="1" t="s">
         <v>378</v>
       </c>
@@ -12164,7 +12405,7 @@
         <v>4.68</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="36" t="s">
         <v>449</v>
       </c>
@@ -12243,7 +12484,7 @@
         <v>672.48</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="54" x14ac:dyDescent="0.3">
       <c r="A14" s="36" t="s">
         <v>451</v>
       </c>
@@ -12260,7 +12501,7 @@
         <v>672.48</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="18" x14ac:dyDescent="0.3">
       <c r="A15" s="36" t="s">
         <v>449</v>
       </c>
@@ -12322,7 +12563,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="36" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="18" x14ac:dyDescent="0.3">
       <c r="A19" s="36" t="s">
         <v>449</v>
       </c>
@@ -12401,7 +12642,7 @@
         <v>248.52</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="54" x14ac:dyDescent="0.3">
       <c r="A24" s="36" t="s">
         <v>451</v>
       </c>
@@ -12418,7 +12659,7 @@
         <v>248.52</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="36" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" ht="18" x14ac:dyDescent="0.3">
       <c r="A25" s="36" t="s">
         <v>449</v>
       </c>
@@ -12517,11 +12758,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="85" t="s">
         <v>396</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="87"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
@@ -12809,14 +13050,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="97" t="s">
         <v>389</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
@@ -12825,10 +13066,10 @@
       <c r="B2" s="16" t="s">
         <v>391</v>
       </c>
-      <c r="C2" s="81" t="s">
+      <c r="C2" s="98" t="s">
         <v>392</v>
       </c>
-      <c r="D2" s="82"/>
+      <c r="D2" s="99"/>
       <c r="E2" s="16" t="s">
         <v>393</v>
       </c>
@@ -12843,10 +13084,10 @@
       <c r="B3" s="61" t="s">
         <v>507</v>
       </c>
-      <c r="C3" s="83" t="s">
+      <c r="C3" s="100" t="s">
         <v>503</v>
       </c>
-      <c r="D3" s="84"/>
+      <c r="D3" s="101"/>
       <c r="E3" s="62" t="s">
         <v>395</v>
       </c>
@@ -12856,16 +13097,16 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="87"/>
-      <c r="B4" s="87"/>
-      <c r="C4" s="87"/>
-      <c r="D4" s="87"/>
-      <c r="E4" s="87"/>
-      <c r="F4" s="87"/>
+      <c r="A4" s="104"/>
+      <c r="B4" s="104"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="85"/>
-      <c r="B5" s="86"/>
+      <c r="A5" s="102"/>
+      <c r="B5" s="103"/>
       <c r="C5" s="17" t="s">
         <v>506</v>
       </c>
@@ -12880,8 +13121,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="85"/>
-      <c r="B6" s="86"/>
+      <c r="A6" s="102"/>
+      <c r="B6" s="103"/>
       <c r="C6" s="17">
         <v>1</v>
       </c>
@@ -12896,8 +13137,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="85"/>
-      <c r="B7" s="86"/>
+      <c r="A7" s="102"/>
+      <c r="B7" s="103"/>
       <c r="C7" s="17">
         <v>2</v>
       </c>
@@ -12944,36 +13185,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="105" t="s">
         <v>389</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
-      <c r="I1" s="98"/>
-      <c r="J1" s="98"/>
-      <c r="K1" s="98"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="48" t="s">
         <v>390</v>
       </c>
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="95" t="s">
         <v>391</v>
       </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="99" t="s">
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="107" t="s">
         <v>392</v>
       </c>
-      <c r="H2" s="100"/>
-      <c r="I2" s="101"/>
+      <c r="H2" s="108"/>
+      <c r="I2" s="109"/>
       <c r="J2" s="49" t="s">
         <v>393</v>
       </c>
@@ -12985,18 +13226,18 @@
       <c r="A3" s="60">
         <v>1</v>
       </c>
-      <c r="B3" s="79" t="s">
+      <c r="B3" s="96" t="s">
         <v>497</v>
       </c>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="104" t="s">
+      <c r="C3" s="96"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="110" t="s">
         <v>508</v>
       </c>
-      <c r="H3" s="102"/>
-      <c r="I3" s="103"/>
+      <c r="H3" s="111"/>
+      <c r="I3" s="112"/>
       <c r="J3" s="64" t="s">
         <v>395</v>
       </c>
@@ -13006,402 +13247,1593 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="74"/>
-      <c r="B4" s="74"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="74"/>
-      <c r="K4" s="74"/>
+      <c r="A4" s="91"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="91"/>
+      <c r="J4" s="91"/>
+      <c r="K4" s="91"/>
     </row>
     <row r="5" spans="1:11" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="88" t="s">
+      <c r="A5" s="68" t="s">
         <v>496</v>
       </c>
-      <c r="B5" s="88" t="s">
+      <c r="B5" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="88" t="s">
+      <c r="C5" s="68" t="s">
         <v>495</v>
       </c>
-      <c r="D5" s="74"/>
-      <c r="E5" s="88" t="s">
+      <c r="D5" s="91"/>
+      <c r="E5" s="68" t="s">
         <v>496</v>
       </c>
-      <c r="F5" s="88" t="s">
+      <c r="F5" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="G5" s="88" t="s">
+      <c r="G5" s="68" t="s">
         <v>495</v>
       </c>
-      <c r="H5" s="95"/>
-      <c r="I5" s="88" t="s">
+      <c r="H5" s="115"/>
+      <c r="I5" s="68" t="s">
         <v>496</v>
       </c>
-      <c r="J5" s="88" t="s">
+      <c r="J5" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="K5" s="88" t="s">
+      <c r="K5" s="68" t="s">
         <v>495</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="89">
+      <c r="A6" s="69">
         <v>1.19</v>
       </c>
-      <c r="B6" s="90" t="s">
+      <c r="B6" s="70" t="s">
         <v>499</v>
       </c>
-      <c r="C6" s="90">
+      <c r="C6" s="70">
         <v>20.7</v>
       </c>
-      <c r="D6" s="74"/>
-      <c r="E6" s="91">
+      <c r="D6" s="91"/>
+      <c r="E6" s="71">
         <v>2.37</v>
       </c>
-      <c r="F6" s="92" t="s">
+      <c r="F6" s="72" t="s">
         <v>499</v>
       </c>
-      <c r="G6" s="92">
+      <c r="G6" s="72">
         <v>21.6</v>
       </c>
-      <c r="H6" s="95"/>
-      <c r="I6" s="89">
+      <c r="H6" s="115"/>
+      <c r="I6" s="69">
         <v>3.23</v>
       </c>
-      <c r="J6" s="90" t="s">
+      <c r="J6" s="70" t="s">
         <v>499</v>
       </c>
-      <c r="K6" s="90">
+      <c r="K6" s="70">
         <v>21.6</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="91">
+      <c r="A7" s="71">
         <v>1.61</v>
       </c>
-      <c r="B7" s="92" t="s">
+      <c r="B7" s="72" t="s">
         <v>499</v>
       </c>
-      <c r="C7" s="92">
+      <c r="C7" s="72">
         <v>16.8</v>
       </c>
-      <c r="D7" s="74"/>
-      <c r="E7" s="89">
+      <c r="D7" s="91"/>
+      <c r="E7" s="69">
         <v>2.4</v>
       </c>
-      <c r="F7" s="90" t="s">
+      <c r="F7" s="70" t="s">
         <v>499</v>
       </c>
-      <c r="G7" s="90">
+      <c r="G7" s="70">
         <v>51.3</v>
       </c>
-      <c r="H7" s="95"/>
-      <c r="I7" s="91">
+      <c r="H7" s="115"/>
+      <c r="I7" s="71">
         <v>3.25</v>
       </c>
-      <c r="J7" s="92" t="s">
+      <c r="J7" s="72" t="s">
         <v>499</v>
       </c>
-      <c r="K7" s="92">
+      <c r="K7" s="72">
         <v>52.1</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="89">
+      <c r="A8" s="69">
         <v>1.64</v>
       </c>
-      <c r="B8" s="90" t="s">
+      <c r="B8" s="70" t="s">
         <v>499</v>
       </c>
-      <c r="C8" s="90">
+      <c r="C8" s="70">
         <v>24</v>
       </c>
-      <c r="D8" s="74"/>
-      <c r="E8" s="91">
+      <c r="D8" s="91"/>
+      <c r="E8" s="71">
         <v>2.41</v>
       </c>
-      <c r="F8" s="92" t="s">
+      <c r="F8" s="72" t="s">
         <v>499</v>
       </c>
-      <c r="G8" s="92">
+      <c r="G8" s="72">
         <v>56.6</v>
       </c>
-      <c r="H8" s="95"/>
-      <c r="I8" s="89">
+      <c r="H8" s="115"/>
+      <c r="I8" s="69">
         <v>3.26</v>
       </c>
-      <c r="J8" s="90" t="s">
+      <c r="J8" s="70" t="s">
         <v>499</v>
       </c>
-      <c r="K8" s="90">
+      <c r="K8" s="70">
         <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="91">
+      <c r="A9" s="71">
         <v>1.67</v>
       </c>
-      <c r="B9" s="92" t="s">
+      <c r="B9" s="72" t="s">
         <v>499</v>
       </c>
-      <c r="C9" s="92">
+      <c r="C9" s="72">
         <v>51.3</v>
       </c>
-      <c r="D9" s="74"/>
-      <c r="E9" s="89">
+      <c r="D9" s="91"/>
+      <c r="E9" s="69">
         <v>2.42</v>
       </c>
-      <c r="F9" s="90" t="s">
+      <c r="F9" s="70" t="s">
         <v>499</v>
       </c>
-      <c r="G9" s="90">
+      <c r="G9" s="70">
         <v>21.5</v>
       </c>
-      <c r="H9" s="95"/>
-      <c r="I9" s="91">
+      <c r="H9" s="115"/>
+      <c r="I9" s="71">
         <v>3.28</v>
       </c>
-      <c r="J9" s="92" t="s">
+      <c r="J9" s="72" t="s">
         <v>499</v>
       </c>
-      <c r="K9" s="92">
+      <c r="K9" s="72">
         <v>21.6</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="89">
+      <c r="A10" s="69">
         <v>1.68</v>
       </c>
-      <c r="B10" s="90" t="s">
+      <c r="B10" s="70" t="s">
         <v>499</v>
       </c>
-      <c r="C10" s="90">
+      <c r="C10" s="70">
         <v>54.6</v>
       </c>
-      <c r="D10" s="74"/>
-      <c r="E10" s="91">
+      <c r="D10" s="91"/>
+      <c r="E10" s="71">
         <v>2.44</v>
       </c>
-      <c r="F10" s="92" t="s">
+      <c r="F10" s="72" t="s">
         <v>499</v>
       </c>
-      <c r="G10" s="92">
+      <c r="G10" s="72">
         <v>51.3</v>
       </c>
-      <c r="H10" s="95"/>
-      <c r="I10" s="89">
+      <c r="H10" s="115"/>
+      <c r="I10" s="69">
         <v>3.29</v>
       </c>
-      <c r="J10" s="90" t="s">
+      <c r="J10" s="70" t="s">
         <v>499</v>
       </c>
-      <c r="K10" s="90">
+      <c r="K10" s="70">
         <v>51.6</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="91">
+      <c r="A11" s="71">
         <v>1.69</v>
       </c>
-      <c r="B11" s="92" t="s">
+      <c r="B11" s="72" t="s">
         <v>499</v>
       </c>
-      <c r="C11" s="92">
+      <c r="C11" s="72">
         <v>18.5</v>
       </c>
-      <c r="D11" s="74"/>
-      <c r="E11" s="89">
+      <c r="D11" s="91"/>
+      <c r="E11" s="69">
         <v>2.4500000000000002</v>
       </c>
-      <c r="F11" s="90" t="s">
+      <c r="F11" s="70" t="s">
         <v>499</v>
       </c>
-      <c r="G11" s="90">
+      <c r="G11" s="70">
         <v>56.3</v>
       </c>
-      <c r="H11" s="95"/>
-      <c r="I11" s="91">
+      <c r="H11" s="115"/>
+      <c r="I11" s="71">
         <v>3.3</v>
       </c>
-      <c r="J11" s="92" t="s">
+      <c r="J11" s="72" t="s">
         <v>499</v>
       </c>
-      <c r="K11" s="92">
+      <c r="K11" s="72">
         <v>56.3</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="89">
+      <c r="A12" s="69">
         <v>1.73</v>
       </c>
-      <c r="B12" s="90" t="s">
+      <c r="B12" s="70" t="s">
         <v>499</v>
       </c>
-      <c r="C12" s="90">
+      <c r="C12" s="70">
         <v>51.2</v>
       </c>
-      <c r="D12" s="74"/>
-      <c r="E12" s="93"/>
-      <c r="F12" s="94" t="s">
+      <c r="D12" s="91"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="74" t="s">
         <v>492</v>
       </c>
-      <c r="G12" s="93">
+      <c r="G12" s="73">
         <f>SUM(G6:G11)</f>
         <v>258.60000000000002</v>
       </c>
-      <c r="H12" s="95"/>
-      <c r="I12" s="89">
+      <c r="H12" s="115"/>
+      <c r="I12" s="69">
         <v>3.33</v>
       </c>
-      <c r="J12" s="90" t="s">
+      <c r="J12" s="70" t="s">
         <v>499</v>
       </c>
-      <c r="K12" s="90">
+      <c r="K12" s="70">
         <v>75.400000000000006</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="91">
+      <c r="A13" s="71">
         <v>1.74</v>
       </c>
-      <c r="B13" s="92" t="s">
+      <c r="B13" s="72" t="s">
         <v>499</v>
       </c>
-      <c r="C13" s="92">
+      <c r="C13" s="72">
         <v>55.3</v>
       </c>
-      <c r="D13" s="74"/>
-      <c r="E13" s="96"/>
-      <c r="F13" s="96"/>
-      <c r="G13" s="96"/>
-      <c r="H13" s="95"/>
-      <c r="I13" s="91">
+      <c r="D13" s="91"/>
+      <c r="E13" s="113"/>
+      <c r="F13" s="113"/>
+      <c r="G13" s="113"/>
+      <c r="H13" s="115"/>
+      <c r="I13" s="71">
         <v>3.34</v>
       </c>
-      <c r="J13" s="92" t="s">
+      <c r="J13" s="72" t="s">
         <v>499</v>
       </c>
-      <c r="K13" s="92">
+      <c r="K13" s="72">
         <v>6.9</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="89">
+      <c r="A14" s="69">
         <v>1.77</v>
       </c>
-      <c r="B14" s="90" t="s">
+      <c r="B14" s="70" t="s">
         <v>499</v>
       </c>
-      <c r="C14" s="90">
+      <c r="C14" s="70">
         <v>41.2</v>
       </c>
-      <c r="D14" s="74"/>
-      <c r="E14" s="105"/>
-      <c r="F14" s="105"/>
-      <c r="G14" s="105"/>
-      <c r="H14" s="95"/>
-      <c r="I14" s="89">
+      <c r="D14" s="91"/>
+      <c r="E14" s="114"/>
+      <c r="F14" s="114"/>
+      <c r="G14" s="114"/>
+      <c r="H14" s="115"/>
+      <c r="I14" s="69">
         <v>3.35</v>
       </c>
-      <c r="J14" s="90" t="s">
+      <c r="J14" s="70" t="s">
         <v>499</v>
       </c>
-      <c r="K14" s="90">
+      <c r="K14" s="70">
         <v>74.900000000000006</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="91">
+      <c r="A15" s="71">
         <v>1.78</v>
       </c>
-      <c r="B15" s="92" t="s">
+      <c r="B15" s="72" t="s">
         <v>499</v>
       </c>
-      <c r="C15" s="92">
+      <c r="C15" s="72">
         <v>59.3</v>
       </c>
-      <c r="D15" s="74"/>
-      <c r="E15" s="105"/>
-      <c r="F15" s="105"/>
-      <c r="G15" s="105"/>
-      <c r="H15" s="95"/>
-      <c r="I15" s="91">
+      <c r="D15" s="91"/>
+      <c r="E15" s="114"/>
+      <c r="F15" s="114"/>
+      <c r="G15" s="114"/>
+      <c r="H15" s="115"/>
+      <c r="I15" s="71">
         <v>3.41</v>
       </c>
-      <c r="J15" s="92" t="s">
+      <c r="J15" s="72" t="s">
         <v>499</v>
       </c>
-      <c r="K15" s="92">
+      <c r="K15" s="72">
         <v>36.4</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="93"/>
-      <c r="B16" s="94" t="s">
+      <c r="A16" s="73"/>
+      <c r="B16" s="74" t="s">
         <v>492</v>
       </c>
-      <c r="C16" s="93">
+      <c r="C16" s="73">
         <f>SUM(C6:C15)</f>
         <v>392.90000000000003</v>
       </c>
-      <c r="D16" s="74"/>
-      <c r="E16" s="105"/>
-      <c r="F16" s="105"/>
-      <c r="G16" s="105"/>
-      <c r="H16" s="95"/>
-      <c r="I16" s="89">
+      <c r="D16" s="91"/>
+      <c r="E16" s="114"/>
+      <c r="F16" s="114"/>
+      <c r="G16" s="114"/>
+      <c r="H16" s="115"/>
+      <c r="I16" s="69">
         <v>3.42</v>
       </c>
-      <c r="J16" s="90" t="s">
+      <c r="J16" s="70" t="s">
         <v>499</v>
       </c>
-      <c r="K16" s="90">
+      <c r="K16" s="70">
         <v>59.7</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="96"/>
-      <c r="B17" s="96"/>
-      <c r="C17" s="96"/>
-      <c r="D17" s="74"/>
-      <c r="E17" s="105"/>
-      <c r="F17" s="105"/>
-      <c r="G17" s="105"/>
-      <c r="H17" s="95"/>
-      <c r="I17" s="93"/>
-      <c r="J17" s="94" t="s">
+      <c r="A17" s="113"/>
+      <c r="B17" s="113"/>
+      <c r="C17" s="113"/>
+      <c r="D17" s="91"/>
+      <c r="E17" s="114"/>
+      <c r="F17" s="114"/>
+      <c r="G17" s="114"/>
+      <c r="H17" s="115"/>
+      <c r="I17" s="73"/>
+      <c r="J17" s="74" t="s">
         <v>492</v>
       </c>
-      <c r="K17" s="93">
+      <c r="K17" s="73">
         <f>SUM(K6:K16)</f>
         <v>513.5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="A4:K4"/>
     <mergeCell ref="E13:G17"/>
     <mergeCell ref="H5:H17"/>
     <mergeCell ref="D5:D17"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="A4:K4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" customWidth="1"/>
+    <col min="2" max="2" width="37.88671875" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" customWidth="1"/>
+    <col min="5" max="5" width="9.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="12"/>
+      <c r="B1" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="15"/>
+    </row>
+    <row r="2" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>392</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="54" x14ac:dyDescent="0.3">
+      <c r="A3" s="67">
+        <v>1</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>428</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>429</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="E3" s="20">
+        <f>'2-пом'!C25</f>
+        <v>256.98</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K24"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7.21875" style="63" customWidth="1"/>
+    <col min="2" max="2" width="7.88671875" style="63" customWidth="1"/>
+    <col min="3" max="3" width="10.77734375" style="63" customWidth="1"/>
+    <col min="4" max="4" width="4.109375" style="63" customWidth="1"/>
+    <col min="5" max="5" width="7.109375" style="63" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" style="63" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" style="63" customWidth="1"/>
+    <col min="8" max="8" width="5.33203125" style="63" customWidth="1"/>
+    <col min="9" max="9" width="7.88671875" style="63" customWidth="1"/>
+    <col min="10" max="10" width="7.44140625" style="63" customWidth="1"/>
+    <col min="11" max="11" width="11.88671875" style="63" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="63"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="118" t="s">
+        <v>389</v>
+      </c>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+    </row>
+    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="B2" s="120" t="s">
+        <v>391</v>
+      </c>
+      <c r="C2" s="120"/>
+      <c r="D2" s="120"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="98" t="s">
+        <v>392</v>
+      </c>
+      <c r="H2" s="121"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="73.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="67">
+        <v>1</v>
+      </c>
+      <c r="B3" s="122" t="s">
+        <v>446</v>
+      </c>
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="122"/>
+      <c r="G3" s="123" t="s">
+        <v>429</v>
+      </c>
+      <c r="H3" s="89"/>
+      <c r="I3" s="90"/>
+      <c r="J3" s="67" t="s">
+        <v>395</v>
+      </c>
+      <c r="K3" s="124">
+        <f>C12+G19+K15</f>
+        <v>256.52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="73.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="75">
+        <v>1</v>
+      </c>
+      <c r="B4" s="122" t="s">
+        <v>446</v>
+      </c>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="123" t="s">
+        <v>553</v>
+      </c>
+      <c r="H4" s="89"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="75" t="s">
+        <v>395</v>
+      </c>
+      <c r="K4" s="124">
+        <f>C24+G24+K24</f>
+        <v>27.87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="104"/>
+      <c r="B5" s="104"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="104"/>
+      <c r="E5" s="104"/>
+      <c r="F5" s="104"/>
+      <c r="G5" s="104"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="104"/>
+      <c r="K5" s="104"/>
+    </row>
+    <row r="6" spans="1:11" ht="32.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="76" t="s">
+        <v>496</v>
+      </c>
+      <c r="B6" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="76" t="s">
+        <v>495</v>
+      </c>
+      <c r="D6" s="103"/>
+      <c r="E6" s="76" t="s">
+        <v>496</v>
+      </c>
+      <c r="F6" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="76" t="s">
+        <v>495</v>
+      </c>
+      <c r="H6" s="117"/>
+      <c r="I6" s="76" t="s">
+        <v>496</v>
+      </c>
+      <c r="J6" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="76" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7" s="77" t="s">
+        <v>509</v>
+      </c>
+      <c r="B7" s="78" t="s">
+        <v>430</v>
+      </c>
+      <c r="C7" s="78">
+        <v>5.01</v>
+      </c>
+      <c r="D7" s="103"/>
+      <c r="E7" s="79" t="s">
+        <v>514</v>
+      </c>
+      <c r="F7" s="80" t="s">
+        <v>430</v>
+      </c>
+      <c r="G7" s="80">
+        <v>6.47</v>
+      </c>
+      <c r="H7" s="117"/>
+      <c r="I7" s="77" t="s">
+        <v>526</v>
+      </c>
+      <c r="J7" s="78" t="s">
+        <v>430</v>
+      </c>
+      <c r="K7" s="78">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" s="79" t="s">
+        <v>510</v>
+      </c>
+      <c r="B8" s="80" t="s">
+        <v>430</v>
+      </c>
+      <c r="C8" s="80">
+        <v>3.76</v>
+      </c>
+      <c r="D8" s="103"/>
+      <c r="E8" s="77" t="s">
+        <v>517</v>
+      </c>
+      <c r="F8" s="78" t="s">
+        <v>430</v>
+      </c>
+      <c r="G8" s="78">
+        <v>10.18</v>
+      </c>
+      <c r="H8" s="117"/>
+      <c r="I8" s="79" t="s">
+        <v>527</v>
+      </c>
+      <c r="J8" s="80" t="s">
+        <v>430</v>
+      </c>
+      <c r="K8" s="80">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" s="77" t="s">
+        <v>511</v>
+      </c>
+      <c r="B9" s="78" t="s">
+        <v>430</v>
+      </c>
+      <c r="C9" s="78">
+        <v>10.18</v>
+      </c>
+      <c r="D9" s="103"/>
+      <c r="E9" s="79" t="s">
+        <v>515</v>
+      </c>
+      <c r="F9" s="80" t="s">
+        <v>430</v>
+      </c>
+      <c r="G9" s="80">
+        <v>10.23</v>
+      </c>
+      <c r="H9" s="117"/>
+      <c r="I9" s="77" t="s">
+        <v>528</v>
+      </c>
+      <c r="J9" s="78" t="s">
+        <v>430</v>
+      </c>
+      <c r="K9" s="78">
+        <v>29.24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" s="79" t="s">
+        <v>512</v>
+      </c>
+      <c r="B10" s="80" t="s">
+        <v>430</v>
+      </c>
+      <c r="C10" s="80">
+        <v>5.14</v>
+      </c>
+      <c r="D10" s="103"/>
+      <c r="E10" s="77" t="s">
+        <v>516</v>
+      </c>
+      <c r="F10" s="78" t="s">
+        <v>430</v>
+      </c>
+      <c r="G10" s="78">
+        <v>5.24</v>
+      </c>
+      <c r="H10" s="117"/>
+      <c r="I10" s="79" t="s">
+        <v>529</v>
+      </c>
+      <c r="J10" s="80" t="s">
+        <v>430</v>
+      </c>
+      <c r="K10" s="80">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11" s="77" t="s">
+        <v>513</v>
+      </c>
+      <c r="B11" s="78" t="s">
+        <v>430</v>
+      </c>
+      <c r="C11" s="78">
+        <v>10.23</v>
+      </c>
+      <c r="D11" s="103"/>
+      <c r="E11" s="79" t="s">
+        <v>518</v>
+      </c>
+      <c r="F11" s="80" t="s">
+        <v>430</v>
+      </c>
+      <c r="G11" s="80">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="H11" s="117"/>
+      <c r="I11" s="77" t="s">
+        <v>530</v>
+      </c>
+      <c r="J11" s="78" t="s">
+        <v>430</v>
+      </c>
+      <c r="K11" s="78">
+        <v>5.48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" s="81"/>
+      <c r="B12" s="82" t="s">
+        <v>492</v>
+      </c>
+      <c r="C12" s="83">
+        <f>SUM(C7:C11)</f>
+        <v>34.32</v>
+      </c>
+      <c r="D12" s="103"/>
+      <c r="E12" s="77" t="s">
+        <v>519</v>
+      </c>
+      <c r="F12" s="78" t="s">
+        <v>430</v>
+      </c>
+      <c r="G12" s="78">
+        <v>11.06</v>
+      </c>
+      <c r="H12" s="117"/>
+      <c r="I12" s="79" t="s">
+        <v>531</v>
+      </c>
+      <c r="J12" s="80" t="s">
+        <v>430</v>
+      </c>
+      <c r="K12" s="80">
+        <v>10.53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" s="104"/>
+      <c r="B13" s="104"/>
+      <c r="C13" s="104"/>
+      <c r="D13" s="103"/>
+      <c r="E13" s="79" t="s">
+        <v>520</v>
+      </c>
+      <c r="F13" s="80" t="s">
+        <v>430</v>
+      </c>
+      <c r="G13" s="80">
+        <v>11.17</v>
+      </c>
+      <c r="H13" s="117"/>
+      <c r="I13" s="77" t="s">
+        <v>532</v>
+      </c>
+      <c r="J13" s="78" t="s">
+        <v>430</v>
+      </c>
+      <c r="K13" s="78">
+        <v>10.56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14" s="116"/>
+      <c r="B14" s="116"/>
+      <c r="C14" s="116"/>
+      <c r="D14" s="103"/>
+      <c r="E14" s="77" t="s">
+        <v>521</v>
+      </c>
+      <c r="F14" s="78" t="s">
+        <v>430</v>
+      </c>
+      <c r="G14" s="78">
+        <v>13.28</v>
+      </c>
+      <c r="H14" s="117"/>
+      <c r="I14" s="79" t="s">
+        <v>533</v>
+      </c>
+      <c r="J14" s="80" t="s">
+        <v>430</v>
+      </c>
+      <c r="K14" s="80">
+        <v>8.51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15" s="116"/>
+      <c r="B15" s="116"/>
+      <c r="C15" s="116"/>
+      <c r="D15" s="103"/>
+      <c r="E15" s="79" t="s">
+        <v>522</v>
+      </c>
+      <c r="F15" s="80" t="s">
+        <v>430</v>
+      </c>
+      <c r="G15" s="80">
+        <v>8.24</v>
+      </c>
+      <c r="H15" s="117"/>
+      <c r="I15" s="81"/>
+      <c r="J15" s="82" t="s">
+        <v>492</v>
+      </c>
+      <c r="K15" s="83">
+        <f>SUM(K7:K14)</f>
+        <v>88.11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16" s="116"/>
+      <c r="B16" s="116"/>
+      <c r="C16" s="116"/>
+      <c r="D16" s="103"/>
+      <c r="E16" s="77" t="s">
+        <v>523</v>
+      </c>
+      <c r="F16" s="78" t="s">
+        <v>430</v>
+      </c>
+      <c r="G16" s="78">
+        <v>10.49</v>
+      </c>
+      <c r="H16" s="117"/>
+      <c r="I16" s="104"/>
+      <c r="J16" s="104"/>
+      <c r="K16" s="104"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" s="116"/>
+      <c r="B17" s="116"/>
+      <c r="C17" s="116"/>
+      <c r="D17" s="103"/>
+      <c r="E17" s="79" t="s">
+        <v>524</v>
+      </c>
+      <c r="F17" s="80" t="s">
+        <v>430</v>
+      </c>
+      <c r="G17" s="80">
+        <v>11.84</v>
+      </c>
+      <c r="H17" s="117"/>
+      <c r="I17" s="116"/>
+      <c r="J17" s="116"/>
+      <c r="K17" s="116"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18" s="116"/>
+      <c r="B18" s="116"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="103"/>
+      <c r="E18" s="77" t="s">
+        <v>525</v>
+      </c>
+      <c r="F18" s="78" t="s">
+        <v>430</v>
+      </c>
+      <c r="G18" s="78">
+        <v>30.78</v>
+      </c>
+      <c r="H18" s="117"/>
+      <c r="I18" s="116"/>
+      <c r="J18" s="116"/>
+      <c r="K18" s="116"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A19" s="116"/>
+      <c r="B19" s="116"/>
+      <c r="C19" s="116"/>
+      <c r="D19" s="103"/>
+      <c r="E19" s="81"/>
+      <c r="F19" s="82" t="s">
+        <v>492</v>
+      </c>
+      <c r="G19" s="83">
+        <f>SUM(G7:G18)</f>
+        <v>134.08999999999997</v>
+      </c>
+      <c r="H19" s="117"/>
+      <c r="I19" s="116"/>
+      <c r="J19" s="116"/>
+      <c r="K19" s="116"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A20" s="102"/>
+      <c r="B20" s="102"/>
+      <c r="C20" s="102"/>
+      <c r="D20" s="102"/>
+      <c r="E20" s="102"/>
+      <c r="F20" s="102"/>
+      <c r="G20" s="102"/>
+      <c r="H20" s="102"/>
+      <c r="I20" s="102"/>
+      <c r="J20" s="102"/>
+      <c r="K20" s="102"/>
+    </row>
+    <row r="21" spans="1:11" ht="46.8" x14ac:dyDescent="0.35">
+      <c r="A21" s="68" t="s">
+        <v>496</v>
+      </c>
+      <c r="B21" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="68" t="s">
+        <v>495</v>
+      </c>
+      <c r="D21" s="131"/>
+      <c r="E21" s="68" t="s">
+        <v>496</v>
+      </c>
+      <c r="F21" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="G21" s="68" t="s">
+        <v>495</v>
+      </c>
+      <c r="H21" s="131"/>
+      <c r="I21" s="68" t="s">
+        <v>496</v>
+      </c>
+      <c r="J21" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="K21" s="68" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A22" s="129" t="s">
+        <v>511</v>
+      </c>
+      <c r="B22" s="70" t="s">
+        <v>431</v>
+      </c>
+      <c r="C22" s="70">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="D22" s="131"/>
+      <c r="E22" s="129" t="s">
+        <v>517</v>
+      </c>
+      <c r="F22" s="70" t="s">
+        <v>431</v>
+      </c>
+      <c r="G22" s="70">
+        <v>4.58</v>
+      </c>
+      <c r="H22" s="131"/>
+      <c r="I22" s="129" t="s">
+        <v>531</v>
+      </c>
+      <c r="J22" s="70" t="s">
+        <v>431</v>
+      </c>
+      <c r="K22" s="70">
+        <v>4.6900000000000004</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A23" s="129" t="s">
+        <v>513</v>
+      </c>
+      <c r="B23" s="70" t="s">
+        <v>431</v>
+      </c>
+      <c r="C23" s="70">
+        <v>4.62</v>
+      </c>
+      <c r="D23" s="131"/>
+      <c r="E23" s="129" t="s">
+        <v>515</v>
+      </c>
+      <c r="F23" s="70" t="s">
+        <v>431</v>
+      </c>
+      <c r="G23" s="70">
+        <v>4.62</v>
+      </c>
+      <c r="H23" s="131"/>
+      <c r="I23" s="129" t="s">
+        <v>532</v>
+      </c>
+      <c r="J23" s="70" t="s">
+        <v>431</v>
+      </c>
+      <c r="K23" s="70">
+        <v>4.63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A24" s="130"/>
+      <c r="B24" s="74" t="s">
+        <v>492</v>
+      </c>
+      <c r="C24" s="73">
+        <f>SUM(C22:C23)</f>
+        <v>9.3500000000000014</v>
+      </c>
+      <c r="D24" s="131"/>
+      <c r="E24" s="130"/>
+      <c r="F24" s="74" t="s">
+        <v>492</v>
+      </c>
+      <c r="G24" s="73">
+        <f>SUM(G22:G23)</f>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="H24" s="131"/>
+      <c r="I24" s="130"/>
+      <c r="J24" s="74" t="s">
+        <v>492</v>
+      </c>
+      <c r="K24" s="73">
+        <f>SUM(K22:K23)</f>
+        <v>9.32</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="H21:H24"/>
+    <mergeCell ref="D21:D24"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A13:C19"/>
+    <mergeCell ref="D6:D19"/>
+    <mergeCell ref="H6:H19"/>
+    <mergeCell ref="I16:K19"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7.21875" style="63" customWidth="1"/>
+    <col min="2" max="2" width="7.88671875" style="63" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" style="63" customWidth="1"/>
+    <col min="4" max="4" width="4.109375" style="63" customWidth="1"/>
+    <col min="5" max="5" width="7.109375" style="63" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" style="63" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" style="63" customWidth="1"/>
+    <col min="8" max="8" width="5.33203125" style="63" customWidth="1"/>
+    <col min="9" max="9" width="7.88671875" style="63" customWidth="1"/>
+    <col min="10" max="10" width="7.44140625" style="63" customWidth="1"/>
+    <col min="11" max="11" width="11.88671875" style="63" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="63"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="118" t="s">
+        <v>389</v>
+      </c>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+    </row>
+    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="B2" s="120" t="s">
+        <v>391</v>
+      </c>
+      <c r="C2" s="120"/>
+      <c r="D2" s="120"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="98" t="s">
+        <v>392</v>
+      </c>
+      <c r="H2" s="121"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="73.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="75">
+        <v>1</v>
+      </c>
+      <c r="B3" s="122" t="s">
+        <v>446</v>
+      </c>
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="122"/>
+      <c r="G3" s="123" t="s">
+        <v>554</v>
+      </c>
+      <c r="H3" s="89"/>
+      <c r="I3" s="90"/>
+      <c r="J3" s="75" t="s">
+        <v>395</v>
+      </c>
+      <c r="K3" s="124">
+        <f>C25+G8</f>
+        <v>678.8599999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="104"/>
+      <c r="B4" s="104"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="104"/>
+      <c r="K4" s="104"/>
+    </row>
+    <row r="5" spans="1:11" ht="32.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="76" t="s">
+        <v>496</v>
+      </c>
+      <c r="B5" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="76" t="s">
+        <v>495</v>
+      </c>
+      <c r="D5" s="117"/>
+      <c r="E5" s="76" t="s">
+        <v>496</v>
+      </c>
+      <c r="F5" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="76" t="s">
+        <v>495</v>
+      </c>
+      <c r="H5" s="117"/>
+      <c r="I5" s="116"/>
+      <c r="J5" s="116"/>
+      <c r="K5" s="116"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6" s="79" t="s">
+        <v>534</v>
+      </c>
+      <c r="B6" s="80"/>
+      <c r="C6" s="125">
+        <v>257.98</v>
+      </c>
+      <c r="D6" s="117"/>
+      <c r="E6" s="79" t="s">
+        <v>534</v>
+      </c>
+      <c r="F6" s="80"/>
+      <c r="G6" s="125">
+        <v>57.94</v>
+      </c>
+      <c r="H6" s="117"/>
+      <c r="I6" s="116"/>
+      <c r="J6" s="116"/>
+      <c r="K6" s="116"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7" s="77" t="s">
+        <v>535</v>
+      </c>
+      <c r="B7" s="78"/>
+      <c r="C7" s="126">
+        <v>98.23</v>
+      </c>
+      <c r="D7" s="117"/>
+      <c r="E7" s="77" t="s">
+        <v>552</v>
+      </c>
+      <c r="F7" s="78"/>
+      <c r="G7" s="126">
+        <v>14.96</v>
+      </c>
+      <c r="H7" s="117"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="116"/>
+      <c r="K7" s="116"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" s="79" t="s">
+        <v>536</v>
+      </c>
+      <c r="B8" s="80"/>
+      <c r="C8" s="125">
+        <v>10.039999999999999</v>
+      </c>
+      <c r="D8" s="117"/>
+      <c r="E8" s="127"/>
+      <c r="F8" s="128" t="s">
+        <v>492</v>
+      </c>
+      <c r="G8" s="127">
+        <f>SUM(G6:G7)</f>
+        <v>72.900000000000006</v>
+      </c>
+      <c r="H8" s="117"/>
+      <c r="I8" s="116"/>
+      <c r="J8" s="116"/>
+      <c r="K8" s="116"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" s="77" t="s">
+        <v>537</v>
+      </c>
+      <c r="B9" s="78"/>
+      <c r="C9" s="126">
+        <v>10.51</v>
+      </c>
+      <c r="D9" s="117"/>
+      <c r="E9" s="116"/>
+      <c r="F9" s="116"/>
+      <c r="G9" s="116"/>
+      <c r="H9" s="116"/>
+      <c r="I9" s="116"/>
+      <c r="J9" s="116"/>
+      <c r="K9" s="116"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" s="79" t="s">
+        <v>462</v>
+      </c>
+      <c r="B10" s="80"/>
+      <c r="C10" s="125">
+        <v>10.06</v>
+      </c>
+      <c r="D10" s="117"/>
+      <c r="E10" s="116"/>
+      <c r="F10" s="116"/>
+      <c r="G10" s="116"/>
+      <c r="H10" s="116"/>
+      <c r="I10" s="116"/>
+      <c r="J10" s="116"/>
+      <c r="K10" s="116"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11" s="77" t="s">
+        <v>538</v>
+      </c>
+      <c r="B11" s="78"/>
+      <c r="C11" s="126">
+        <v>98.59</v>
+      </c>
+      <c r="D11" s="117"/>
+      <c r="E11" s="116"/>
+      <c r="F11" s="116"/>
+      <c r="G11" s="116"/>
+      <c r="H11" s="116"/>
+      <c r="I11" s="116"/>
+      <c r="J11" s="116"/>
+      <c r="K11" s="116"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" s="79" t="s">
+        <v>539</v>
+      </c>
+      <c r="B12" s="80"/>
+      <c r="C12" s="125">
+        <v>7.25</v>
+      </c>
+      <c r="D12" s="117"/>
+      <c r="E12" s="116"/>
+      <c r="F12" s="116"/>
+      <c r="G12" s="116"/>
+      <c r="H12" s="116"/>
+      <c r="I12" s="116"/>
+      <c r="J12" s="116"/>
+      <c r="K12" s="116"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" s="77" t="s">
+        <v>540</v>
+      </c>
+      <c r="B13" s="78"/>
+      <c r="C13" s="126">
+        <v>5.76</v>
+      </c>
+      <c r="D13" s="117"/>
+      <c r="E13" s="116"/>
+      <c r="F13" s="116"/>
+      <c r="G13" s="116"/>
+      <c r="H13" s="116"/>
+      <c r="I13" s="116"/>
+      <c r="J13" s="116"/>
+      <c r="K13" s="116"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14" s="79" t="s">
+        <v>541</v>
+      </c>
+      <c r="B14" s="80"/>
+      <c r="C14" s="125">
+        <v>20</v>
+      </c>
+      <c r="D14" s="117"/>
+      <c r="E14" s="116"/>
+      <c r="F14" s="116"/>
+      <c r="G14" s="116"/>
+      <c r="H14" s="116"/>
+      <c r="I14" s="116"/>
+      <c r="J14" s="116"/>
+      <c r="K14" s="116"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15" s="77" t="s">
+        <v>542</v>
+      </c>
+      <c r="B15" s="78"/>
+      <c r="C15" s="126">
+        <v>13.53</v>
+      </c>
+      <c r="D15" s="117"/>
+      <c r="E15" s="116"/>
+      <c r="F15" s="116"/>
+      <c r="G15" s="116"/>
+      <c r="H15" s="116"/>
+      <c r="I15" s="116"/>
+      <c r="J15" s="116"/>
+      <c r="K15" s="116"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16" s="79" t="s">
+        <v>543</v>
+      </c>
+      <c r="B16" s="80"/>
+      <c r="C16" s="125">
+        <v>13.3</v>
+      </c>
+      <c r="D16" s="117"/>
+      <c r="E16" s="116"/>
+      <c r="F16" s="116"/>
+      <c r="G16" s="116"/>
+      <c r="H16" s="116"/>
+      <c r="I16" s="116"/>
+      <c r="J16" s="116"/>
+      <c r="K16" s="116"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" s="77" t="s">
+        <v>544</v>
+      </c>
+      <c r="B17" s="78"/>
+      <c r="C17" s="126">
+        <v>11.67</v>
+      </c>
+      <c r="D17" s="117"/>
+      <c r="E17" s="116"/>
+      <c r="F17" s="116"/>
+      <c r="G17" s="116"/>
+      <c r="H17" s="116"/>
+      <c r="I17" s="116"/>
+      <c r="J17" s="116"/>
+      <c r="K17" s="116"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18" s="79" t="s">
+        <v>545</v>
+      </c>
+      <c r="B18" s="80"/>
+      <c r="C18" s="125">
+        <v>9.7200000000000006</v>
+      </c>
+      <c r="D18" s="117"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="116"/>
+      <c r="G18" s="116"/>
+      <c r="H18" s="116"/>
+      <c r="I18" s="116"/>
+      <c r="J18" s="116"/>
+      <c r="K18" s="116"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A19" s="77" t="s">
+        <v>546</v>
+      </c>
+      <c r="B19" s="78"/>
+      <c r="C19" s="126">
+        <v>3.38</v>
+      </c>
+      <c r="D19" s="117"/>
+      <c r="E19" s="116"/>
+      <c r="F19" s="116"/>
+      <c r="G19" s="116"/>
+      <c r="H19" s="116"/>
+      <c r="I19" s="116"/>
+      <c r="J19" s="116"/>
+      <c r="K19" s="116"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A20" s="79" t="s">
+        <v>547</v>
+      </c>
+      <c r="B20" s="80"/>
+      <c r="C20" s="125">
+        <v>3.04</v>
+      </c>
+      <c r="D20" s="117"/>
+      <c r="E20" s="116"/>
+      <c r="F20" s="116"/>
+      <c r="G20" s="116"/>
+      <c r="H20" s="116"/>
+      <c r="I20" s="116"/>
+      <c r="J20" s="116"/>
+      <c r="K20" s="116"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21" s="77" t="s">
+        <v>548</v>
+      </c>
+      <c r="B21" s="78"/>
+      <c r="C21" s="126">
+        <v>2.85</v>
+      </c>
+      <c r="D21" s="117"/>
+      <c r="E21" s="116"/>
+      <c r="F21" s="116"/>
+      <c r="G21" s="116"/>
+      <c r="H21" s="116"/>
+      <c r="I21" s="116"/>
+      <c r="J21" s="116"/>
+      <c r="K21" s="116"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A22" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="B22" s="80"/>
+      <c r="C22" s="125">
+        <v>9.0399999999999991</v>
+      </c>
+      <c r="D22" s="117"/>
+      <c r="E22" s="116"/>
+      <c r="F22" s="116"/>
+      <c r="G22" s="116"/>
+      <c r="H22" s="116"/>
+      <c r="I22" s="116"/>
+      <c r="J22" s="116"/>
+      <c r="K22" s="116"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A23" s="77" t="s">
+        <v>550</v>
+      </c>
+      <c r="B23" s="78"/>
+      <c r="C23" s="126">
+        <v>16.38</v>
+      </c>
+      <c r="D23" s="117"/>
+      <c r="E23" s="116"/>
+      <c r="F23" s="116"/>
+      <c r="G23" s="116"/>
+      <c r="H23" s="116"/>
+      <c r="I23" s="116"/>
+      <c r="J23" s="116"/>
+      <c r="K23" s="116"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A24" s="79" t="s">
+        <v>551</v>
+      </c>
+      <c r="B24" s="80"/>
+      <c r="C24" s="125">
+        <v>4.63</v>
+      </c>
+      <c r="D24" s="117"/>
+      <c r="E24" s="116"/>
+      <c r="F24" s="116"/>
+      <c r="G24" s="116"/>
+      <c r="H24" s="116"/>
+      <c r="I24" s="116"/>
+      <c r="J24" s="116"/>
+      <c r="K24" s="116"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A25" s="81"/>
+      <c r="B25" s="82" t="s">
+        <v>492</v>
+      </c>
+      <c r="C25" s="127">
+        <f>SUM(C6:C24)</f>
+        <v>605.95999999999992</v>
+      </c>
+      <c r="D25" s="117"/>
+      <c r="E25" s="116"/>
+      <c r="F25" s="116"/>
+      <c r="G25" s="116"/>
+      <c r="H25" s="116"/>
+      <c r="I25" s="116"/>
+      <c r="J25" s="116"/>
+      <c r="K25" s="116"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="H5:K25"/>
+    <mergeCell ref="E9:G25"/>
+    <mergeCell ref="D5:D25"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="A4:K4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="11.44140625" customWidth="1"/>
@@ -13561,6 +14993,168 @@
         <v>206.89999999999998</v>
       </c>
       <c r="G9" s="30">
+        <v>207.1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A16" s="29" t="s">
+        <v>436</v>
+      </c>
+      <c r="B16">
+        <v>1056.5999999999999</v>
+      </c>
+      <c r="C16">
+        <v>75.7</v>
+      </c>
+      <c r="D16" s="29">
+        <v>0</v>
+      </c>
+      <c r="E16" s="29">
+        <f>SUM(B16:D16)</f>
+        <v>1132.3</v>
+      </c>
+      <c r="G16" s="30">
+        <v>1132.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A17" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="B17" s="29">
+        <v>31.2</v>
+      </c>
+      <c r="C17" s="29">
+        <v>0</v>
+      </c>
+      <c r="D17" s="29">
+        <v>0</v>
+      </c>
+      <c r="E17" s="29">
+        <f t="shared" ref="E17:E23" si="1">SUM(B17:D17)</f>
+        <v>31.2</v>
+      </c>
+      <c r="G17" s="30">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A18" s="29" t="s">
+        <v>430</v>
+      </c>
+      <c r="B18" s="29">
+        <v>127.2</v>
+      </c>
+      <c r="C18" s="29">
+        <v>277.5</v>
+      </c>
+      <c r="D18" s="29">
+        <v>155.69999999999999</v>
+      </c>
+      <c r="E18" s="29">
+        <f t="shared" si="1"/>
+        <v>560.4</v>
+      </c>
+      <c r="G18" s="30">
+        <v>560.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A19" s="29" t="s">
+        <v>431</v>
+      </c>
+      <c r="B19" s="29">
+        <v>9.4</v>
+      </c>
+      <c r="C19" s="29">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="D19" s="29">
+        <v>9.4</v>
+      </c>
+      <c r="E19" s="29">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="G19" s="30">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A20" s="29" t="s">
+        <v>437</v>
+      </c>
+      <c r="B20" s="29">
+        <v>370.9</v>
+      </c>
+      <c r="C20" s="29">
+        <v>0</v>
+      </c>
+      <c r="D20" s="29">
+        <v>0</v>
+      </c>
+      <c r="E20" s="29">
+        <f t="shared" si="1"/>
+        <v>370.9</v>
+      </c>
+      <c r="G20" s="30">
+        <v>370.9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="29" t="s">
+        <v>433</v>
+      </c>
+      <c r="B21" s="29">
+        <v>0</v>
+      </c>
+      <c r="C21" s="29">
+        <v>0</v>
+      </c>
+      <c r="D21" s="29">
+        <v>0</v>
+      </c>
+      <c r="E21" s="29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="29" t="s">
+        <v>434</v>
+      </c>
+      <c r="B22" s="29">
+        <v>0</v>
+      </c>
+      <c r="C22" s="29">
+        <v>0</v>
+      </c>
+      <c r="D22" s="29">
+        <v>0</v>
+      </c>
+      <c r="E22" s="29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A23" s="29" t="s">
+        <v>432</v>
+      </c>
+      <c r="B23" s="29">
+        <v>121.1</v>
+      </c>
+      <c r="C23" s="29">
+        <v>43.3</v>
+      </c>
+      <c r="D23" s="29">
+        <v>42.7</v>
+      </c>
+      <c r="E23" s="29">
+        <f t="shared" si="1"/>
+        <v>207.09999999999997</v>
+      </c>
+      <c r="G23" s="30">
         <v>207.1</v>
       </c>
     </row>
@@ -13863,11 +15457,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="85" t="s">
         <v>396</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="87"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
@@ -14105,13 +15699,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="88" t="s">
         <v>389</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="73"/>
+      <c r="B1" s="89"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="90"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
@@ -14585,75 +16179,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="92" t="s">
         <v>389</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="48" t="s">
         <v>390</v>
       </c>
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="95" t="s">
         <v>391</v>
       </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
       <c r="G2" s="49" t="s">
         <v>393</v>
       </c>
-      <c r="H2" s="77" t="s">
+      <c r="H2" s="94" t="s">
         <v>394</v>
       </c>
-      <c r="I2" s="77"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="74"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="91"/>
+      <c r="K2" s="91"/>
     </row>
     <row r="3" spans="1:11" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="57">
         <v>1</v>
       </c>
-      <c r="B3" s="79" t="s">
+      <c r="B3" s="96" t="s">
         <v>497</v>
       </c>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="96"/>
       <c r="G3" s="57" t="s">
         <v>395</v>
       </c>
-      <c r="H3" s="76">
+      <c r="H3" s="93">
         <f>C21+G30+K31</f>
         <v>4099.5</v>
       </c>
-      <c r="I3" s="76"/>
-      <c r="J3" s="74"/>
-      <c r="K3" s="74"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="91"/>
+      <c r="K3" s="91"/>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="74"/>
-      <c r="B4" s="74"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="74"/>
-      <c r="K4" s="74"/>
+      <c r="A4" s="91"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="91"/>
+      <c r="J4" s="91"/>
+      <c r="K4" s="91"/>
     </row>
     <row r="5" spans="1:11" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="47" t="s">
@@ -14665,7 +16259,7 @@
       <c r="C5" s="47" t="s">
         <v>495</v>
       </c>
-      <c r="D5" s="74"/>
+      <c r="D5" s="91"/>
       <c r="E5" s="47" t="s">
         <v>496</v>
       </c>
@@ -14675,7 +16269,7 @@
       <c r="G5" s="47" t="s">
         <v>495</v>
       </c>
-      <c r="H5" s="74"/>
+      <c r="H5" s="91"/>
       <c r="I5" s="47" t="s">
         <v>496</v>
       </c>
@@ -14696,7 +16290,7 @@
       <c r="C6" s="52">
         <v>22.1</v>
       </c>
-      <c r="D6" s="74"/>
+      <c r="D6" s="91"/>
       <c r="E6" s="53">
         <v>2.0099999999999998</v>
       </c>
@@ -14706,7 +16300,7 @@
       <c r="G6" s="54">
         <v>62.6</v>
       </c>
-      <c r="H6" s="74"/>
+      <c r="H6" s="91"/>
       <c r="I6" s="53">
         <v>3.01</v>
       </c>
@@ -14727,7 +16321,7 @@
       <c r="C7" s="54">
         <v>61.9</v>
       </c>
-      <c r="D7" s="74"/>
+      <c r="D7" s="91"/>
       <c r="E7" s="51">
         <v>2.02</v>
       </c>
@@ -14737,7 +16331,7 @@
       <c r="G7" s="52">
         <v>89</v>
       </c>
-      <c r="H7" s="74"/>
+      <c r="H7" s="91"/>
       <c r="I7" s="51">
         <v>3.02</v>
       </c>
@@ -14758,7 +16352,7 @@
       <c r="C8" s="52">
         <v>63.3</v>
       </c>
-      <c r="D8" s="74"/>
+      <c r="D8" s="91"/>
       <c r="E8" s="53">
         <v>2.0299999999999998</v>
       </c>
@@ -14768,7 +16362,7 @@
       <c r="G8" s="54">
         <v>39.4</v>
       </c>
-      <c r="H8" s="74"/>
+      <c r="H8" s="91"/>
       <c r="I8" s="53">
         <v>3.03</v>
       </c>
@@ -14789,7 +16383,7 @@
       <c r="C9" s="54">
         <v>63.4</v>
       </c>
-      <c r="D9" s="74"/>
+      <c r="D9" s="91"/>
       <c r="E9" s="51">
         <v>2.04</v>
       </c>
@@ -14799,7 +16393,7 @@
       <c r="G9" s="52">
         <v>63</v>
       </c>
-      <c r="H9" s="74"/>
+      <c r="H9" s="91"/>
       <c r="I9" s="51">
         <v>3.04</v>
       </c>
@@ -14820,7 +16414,7 @@
       <c r="C10" s="52">
         <v>131.19999999999999</v>
       </c>
-      <c r="D10" s="74"/>
+      <c r="D10" s="91"/>
       <c r="E10" s="53">
         <v>2.0499999999999998</v>
       </c>
@@ -14830,7 +16424,7 @@
       <c r="G10" s="54">
         <v>64.400000000000006</v>
       </c>
-      <c r="H10" s="74"/>
+      <c r="H10" s="91"/>
       <c r="I10" s="53">
         <v>3.05</v>
       </c>
@@ -14851,7 +16445,7 @@
       <c r="C11" s="54">
         <v>20.7</v>
       </c>
-      <c r="D11" s="74"/>
+      <c r="D11" s="91"/>
       <c r="E11" s="51">
         <v>2.06</v>
       </c>
@@ -14861,7 +16455,7 @@
       <c r="G11" s="52">
         <v>63.3</v>
       </c>
-      <c r="H11" s="74"/>
+      <c r="H11" s="91"/>
       <c r="I11" s="51">
         <v>3.06</v>
       </c>
@@ -14882,7 +16476,7 @@
       <c r="C12" s="52">
         <v>16.8</v>
       </c>
-      <c r="D12" s="74"/>
+      <c r="D12" s="91"/>
       <c r="E12" s="53">
         <v>2.0699999999999998</v>
       </c>
@@ -14892,7 +16486,7 @@
       <c r="G12" s="54">
         <v>63.3</v>
       </c>
-      <c r="H12" s="74"/>
+      <c r="H12" s="91"/>
       <c r="I12" s="53">
         <v>3.07</v>
       </c>
@@ -14913,7 +16507,7 @@
       <c r="C13" s="54">
         <v>24</v>
       </c>
-      <c r="D13" s="74"/>
+      <c r="D13" s="91"/>
       <c r="E13" s="51">
         <v>2.08</v>
       </c>
@@ -14923,7 +16517,7 @@
       <c r="G13" s="52">
         <v>78.599999999999994</v>
       </c>
-      <c r="H13" s="74"/>
+      <c r="H13" s="91"/>
       <c r="I13" s="51">
         <v>3.08</v>
       </c>
@@ -14944,7 +16538,7 @@
       <c r="C14" s="52">
         <v>51.3</v>
       </c>
-      <c r="D14" s="74"/>
+      <c r="D14" s="91"/>
       <c r="E14" s="53">
         <v>2.12</v>
       </c>
@@ -14954,7 +16548,7 @@
       <c r="G14" s="54">
         <v>27</v>
       </c>
-      <c r="H14" s="74"/>
+      <c r="H14" s="91"/>
       <c r="I14" s="53">
         <v>3.12</v>
       </c>
@@ -14975,7 +16569,7 @@
       <c r="C15" s="54">
         <v>54.6</v>
       </c>
-      <c r="D15" s="74"/>
+      <c r="D15" s="91"/>
       <c r="E15" s="51">
         <v>2.15</v>
       </c>
@@ -14985,7 +16579,7 @@
       <c r="G15" s="52">
         <v>28</v>
       </c>
-      <c r="H15" s="74"/>
+      <c r="H15" s="91"/>
       <c r="I15" s="51">
         <v>3.13</v>
       </c>
@@ -15006,7 +16600,7 @@
       <c r="C16" s="52">
         <v>18.5</v>
       </c>
-      <c r="D16" s="74"/>
+      <c r="D16" s="91"/>
       <c r="E16" s="53">
         <v>2.19</v>
       </c>
@@ -15016,7 +16610,7 @@
       <c r="G16" s="54">
         <v>359.3</v>
       </c>
-      <c r="H16" s="74"/>
+      <c r="H16" s="91"/>
       <c r="I16" s="53">
         <v>3.18</v>
       </c>
@@ -15037,7 +16631,7 @@
       <c r="C17" s="54">
         <v>51.2</v>
       </c>
-      <c r="D17" s="74"/>
+      <c r="D17" s="91"/>
       <c r="E17" s="51">
         <v>2.21</v>
       </c>
@@ -15047,7 +16641,7 @@
       <c r="G17" s="52">
         <v>14</v>
       </c>
-      <c r="H17" s="74"/>
+      <c r="H17" s="91"/>
       <c r="I17" s="51">
         <v>3.19</v>
       </c>
@@ -15068,7 +16662,7 @@
       <c r="C18" s="52">
         <v>55.3</v>
       </c>
-      <c r="D18" s="74"/>
+      <c r="D18" s="91"/>
       <c r="E18" s="53">
         <v>2.27</v>
       </c>
@@ -15078,7 +16672,7 @@
       <c r="G18" s="54">
         <v>19.100000000000001</v>
       </c>
-      <c r="H18" s="74"/>
+      <c r="H18" s="91"/>
       <c r="I18" s="53">
         <v>3.23</v>
       </c>
@@ -15099,7 +16693,7 @@
       <c r="C19" s="54">
         <v>41.2</v>
       </c>
-      <c r="D19" s="74"/>
+      <c r="D19" s="91"/>
       <c r="E19" s="51">
         <v>2.2799999999999998</v>
       </c>
@@ -15109,7 +16703,7 @@
       <c r="G19" s="52">
         <v>192.9</v>
       </c>
-      <c r="H19" s="74"/>
+      <c r="H19" s="91"/>
       <c r="I19" s="51">
         <v>3.25</v>
       </c>
@@ -15130,7 +16724,7 @@
       <c r="C20" s="52">
         <v>59.3</v>
       </c>
-      <c r="D20" s="74"/>
+      <c r="D20" s="91"/>
       <c r="E20" s="53">
         <v>2.2999999999999998</v>
       </c>
@@ -15140,7 +16734,7 @@
       <c r="G20" s="54">
         <v>115.5</v>
       </c>
-      <c r="H20" s="74"/>
+      <c r="H20" s="91"/>
       <c r="I20" s="53">
         <v>3.26</v>
       </c>
@@ -15159,7 +16753,7 @@
         <f>SUM(C6:C20)</f>
         <v>734.8</v>
       </c>
-      <c r="D21" s="74"/>
+      <c r="D21" s="91"/>
       <c r="E21" s="51">
         <v>2.37</v>
       </c>
@@ -15169,7 +16763,7 @@
       <c r="G21" s="52">
         <v>21.6</v>
       </c>
-      <c r="H21" s="74"/>
+      <c r="H21" s="91"/>
       <c r="I21" s="51">
         <v>3.28</v>
       </c>
@@ -15181,10 +16775,10 @@
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="74"/>
-      <c r="B22" s="74"/>
-      <c r="C22" s="74"/>
-      <c r="D22" s="74"/>
+      <c r="A22" s="91"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="91"/>
+      <c r="D22" s="91"/>
       <c r="E22" s="53">
         <v>2.4</v>
       </c>
@@ -15194,7 +16788,7 @@
       <c r="G22" s="54">
         <v>51.3</v>
       </c>
-      <c r="H22" s="74"/>
+      <c r="H22" s="91"/>
       <c r="I22" s="53">
         <v>3.29</v>
       </c>
@@ -15206,10 +16800,10 @@
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="74"/>
-      <c r="B23" s="74"/>
-      <c r="C23" s="74"/>
-      <c r="D23" s="74"/>
+      <c r="A23" s="91"/>
+      <c r="B23" s="91"/>
+      <c r="C23" s="91"/>
+      <c r="D23" s="91"/>
       <c r="E23" s="51">
         <v>2.41</v>
       </c>
@@ -15219,7 +16813,7 @@
       <c r="G23" s="52">
         <v>56.6</v>
       </c>
-      <c r="H23" s="74"/>
+      <c r="H23" s="91"/>
       <c r="I23" s="51">
         <v>3.3</v>
       </c>
@@ -15231,10 +16825,10 @@
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="74"/>
-      <c r="B24" s="74"/>
-      <c r="C24" s="74"/>
-      <c r="D24" s="74"/>
+      <c r="A24" s="91"/>
+      <c r="B24" s="91"/>
+      <c r="C24" s="91"/>
+      <c r="D24" s="91"/>
       <c r="E24" s="53">
         <v>2.42</v>
       </c>
@@ -15244,7 +16838,7 @@
       <c r="G24" s="54">
         <v>21.5</v>
       </c>
-      <c r="H24" s="74"/>
+      <c r="H24" s="91"/>
       <c r="I24" s="53">
         <v>3.33</v>
       </c>
@@ -15256,10 +16850,10 @@
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="74"/>
-      <c r="B25" s="74"/>
-      <c r="C25" s="74"/>
-      <c r="D25" s="74"/>
+      <c r="A25" s="91"/>
+      <c r="B25" s="91"/>
+      <c r="C25" s="91"/>
+      <c r="D25" s="91"/>
       <c r="E25" s="51">
         <v>2.44</v>
       </c>
@@ -15269,7 +16863,7 @@
       <c r="G25" s="52">
         <v>51.3</v>
       </c>
-      <c r="H25" s="74"/>
+      <c r="H25" s="91"/>
       <c r="I25" s="51">
         <v>3.34</v>
       </c>
@@ -15281,10 +16875,10 @@
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="74"/>
-      <c r="B26" s="74"/>
-      <c r="C26" s="74"/>
-      <c r="D26" s="74"/>
+      <c r="A26" s="91"/>
+      <c r="B26" s="91"/>
+      <c r="C26" s="91"/>
+      <c r="D26" s="91"/>
       <c r="E26" s="53">
         <v>2.4500000000000002</v>
       </c>
@@ -15294,7 +16888,7 @@
       <c r="G26" s="54">
         <v>56.3</v>
       </c>
-      <c r="H26" s="74"/>
+      <c r="H26" s="91"/>
       <c r="I26" s="53">
         <v>3.35</v>
       </c>
@@ -15306,10 +16900,10 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="74"/>
-      <c r="B27" s="74"/>
-      <c r="C27" s="74"/>
-      <c r="D27" s="74"/>
+      <c r="A27" s="91"/>
+      <c r="B27" s="91"/>
+      <c r="C27" s="91"/>
+      <c r="D27" s="91"/>
       <c r="E27" s="51">
         <v>2.4700000000000002</v>
       </c>
@@ -15319,7 +16913,7 @@
       <c r="G27" s="52">
         <v>75.599999999999994</v>
       </c>
-      <c r="H27" s="74"/>
+      <c r="H27" s="91"/>
       <c r="I27" s="51">
         <v>3.41</v>
       </c>
@@ -15331,10 +16925,10 @@
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="74"/>
-      <c r="B28" s="74"/>
-      <c r="C28" s="74"/>
-      <c r="D28" s="74"/>
+      <c r="A28" s="91"/>
+      <c r="B28" s="91"/>
+      <c r="C28" s="91"/>
+      <c r="D28" s="91"/>
       <c r="E28" s="51">
         <v>2.4900000000000002</v>
       </c>
@@ -15344,7 +16938,7 @@
       <c r="G28" s="52">
         <v>75.2</v>
       </c>
-      <c r="H28" s="74"/>
+      <c r="H28" s="91"/>
       <c r="I28" s="53">
         <v>3.42</v>
       </c>
@@ -15356,10 +16950,10 @@
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="74"/>
-      <c r="B29" s="74"/>
-      <c r="C29" s="74"/>
-      <c r="D29" s="74"/>
+      <c r="A29" s="91"/>
+      <c r="B29" s="91"/>
+      <c r="C29" s="91"/>
+      <c r="D29" s="91"/>
       <c r="E29" s="51">
         <v>2.58</v>
       </c>
@@ -15369,7 +16963,7 @@
       <c r="G29" s="52">
         <v>76.2</v>
       </c>
-      <c r="H29" s="74"/>
+      <c r="H29" s="91"/>
       <c r="I29" s="51">
         <v>3.44</v>
       </c>
@@ -15381,10 +16975,10 @@
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="74"/>
-      <c r="B30" s="74"/>
-      <c r="C30" s="74"/>
-      <c r="D30" s="74"/>
+      <c r="A30" s="91"/>
+      <c r="B30" s="91"/>
+      <c r="C30" s="91"/>
+      <c r="D30" s="91"/>
       <c r="F30" s="58" t="s">
         <v>492</v>
       </c>
@@ -15392,7 +16986,7 @@
         <f>SUM(G6:G29)</f>
         <v>1764.9999999999998</v>
       </c>
-      <c r="H30" s="74"/>
+      <c r="H30" s="91"/>
       <c r="I30" s="55">
         <v>3.45</v>
       </c>
@@ -15404,14 +16998,14 @@
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="74"/>
-      <c r="B31" s="74"/>
-      <c r="C31" s="74"/>
-      <c r="D31" s="74"/>
-      <c r="E31" s="74"/>
-      <c r="F31" s="74"/>
-      <c r="G31" s="74"/>
-      <c r="H31" s="74"/>
+      <c r="A31" s="91"/>
+      <c r="B31" s="91"/>
+      <c r="C31" s="91"/>
+      <c r="D31" s="91"/>
+      <c r="E31" s="91"/>
+      <c r="F31" s="91"/>
+      <c r="G31" s="91"/>
+      <c r="H31" s="91"/>
       <c r="J31" s="58" t="s">
         <v>492</v>
       </c>
